--- a/서버정보/20260422_리소스배포_개발.xlsx
+++ b/서버정보/20260422_리소스배포_개발.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEFCA98C-5593-4E38-92AF-0EC3E0D226FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38959A98-6B06-4DEF-AE0A-F80352388172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1653,7 +1653,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2461" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2462" uniqueCount="539">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -12808,14 +12808,11 @@
       <c r="R9" s="56"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A10" s="102"/>
+      <c r="A10" s="95"/>
       <c r="B10" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="88" t="str" cm="1">
-        <f t="array" ref="C10">UPPER(INDEX(_xlfn.TEXTSPLIT($D10, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
+      <c r="C10" s="88"/>
       <c r="D10" s="88" t="s">
         <v>310</v>
       </c>
@@ -12863,11 +12860,13 @@
       <c r="R10" s="86"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A11" s="93"/>
+      <c r="A11" s="103"/>
       <c r="B11" s="89" t="s">
         <v>81</v>
       </c>
-      <c r="C11" s="89"/>
+      <c r="C11" s="89" t="s">
+        <v>479</v>
+      </c>
       <c r="D11" s="89" t="s">
         <v>310</v>
       </c>
@@ -18478,9 +18477,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18628,26 +18630,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -18671,9 +18662,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260422_리소스배포_개발.xlsx
+++ b/서버정보/20260422_리소스배포_개발.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38959A98-6B06-4DEF-AE0A-F80352388172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{659E04C8-5D41-4F8D-8292-62014530DD05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -1653,7 +1653,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2462" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2461" uniqueCount="540">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3582,6 +3582,10 @@
   </si>
   <si>
     <t>hazr-d-bdp-crkweb01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dis-cmbsap01</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3721,7 +3725,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3767,12 +3771,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4062,7 +4060,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4318,9 +4316,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -4354,29 +4349,26 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6066,7 +6058,7 @@
   <dimension ref="A1:AF71"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.375" customWidth="1"/>
+    <col min="1" max="1" width="8.375" style="89" customWidth="1"/>
     <col min="2" max="2" width="7.25" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
     <col min="4" max="4" width="16.125" bestFit="1" customWidth="1"/>
@@ -6099,7 +6091,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A1" s="52"/>
+      <c r="A1" s="98"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6195,11 +6187,14 @@
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A2" s="100"/>
+      <c r="A2" s="99"/>
       <c r="B2" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C2" s="1"/>
+      <c r="C2" s="1" t="str" cm="1">
+        <f t="array" ref="C2">UPPER(INDEX(_xlfn.TEXTSPLIT($D2, "-"), 3))</f>
+        <v>DIS</v>
+      </c>
       <c r="D2" s="1" t="s">
         <v>176</v>
       </c>
@@ -6281,7 +6276,7 @@
       <c r="AF2" s="1"/>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A3" s="101"/>
+      <c r="A3" s="99"/>
       <c r="B3" s="1" t="s">
         <v>81</v>
       </c>
@@ -6370,7 +6365,7 @@
       <c r="AF3" s="1"/>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A4" s="101"/>
+      <c r="A4" s="99"/>
       <c r="B4" s="1" t="s">
         <v>81</v>
       </c>
@@ -6459,11 +6454,14 @@
       <c r="AF4" s="1"/>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A5" s="100"/>
+      <c r="A5" s="99"/>
       <c r="B5" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C5" s="1"/>
+      <c r="C5" s="1" t="str" cm="1">
+        <f t="array" ref="C5">UPPER(INDEX(_xlfn.TEXTSPLIT($D5, "-"), 3))</f>
+        <v>DIS</v>
+      </c>
       <c r="D5" s="1" t="s">
         <v>310</v>
       </c>
@@ -6545,11 +6543,14 @@
       <c r="AF5" s="1"/>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A6" s="82"/>
+      <c r="A6" s="100"/>
       <c r="B6" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C6" s="1"/>
+      <c r="C6" s="1" t="str" cm="1">
+        <f t="array" ref="C6">UPPER(INDEX(_xlfn.TEXTSPLIT($D6, "-"), 3))</f>
+        <v>DIS</v>
+      </c>
       <c r="D6" s="1" t="s">
         <v>310</v>
       </c>
@@ -6631,11 +6632,14 @@
       <c r="AF6" s="1"/>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A7" s="82"/>
+      <c r="A7" s="100"/>
       <c r="B7" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C7" s="1"/>
+      <c r="C7" s="1" t="str" cm="1">
+        <f t="array" ref="C7">UPPER(INDEX(_xlfn.TEXTSPLIT($D7, "-"), 3))</f>
+        <v>DIS</v>
+      </c>
       <c r="D7" s="1" t="s">
         <v>310</v>
       </c>
@@ -6717,11 +6721,14 @@
       <c r="AF7" s="1"/>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A8" s="82"/>
+      <c r="A8" s="100"/>
       <c r="B8" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C8" s="1"/>
+      <c r="C8" s="1" t="str" cm="1">
+        <f t="array" ref="C8">UPPER(INDEX(_xlfn.TEXTSPLIT($D8, "-"), 3))</f>
+        <v>DIS</v>
+      </c>
       <c r="D8" s="1" t="s">
         <v>310</v>
       </c>
@@ -6803,13 +6810,16 @@
       <c r="AF8" s="1"/>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A9" s="97" t="s">
+      <c r="A9" s="101" t="s">
         <v>508</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C9" s="1"/>
+      <c r="C9" s="1" t="str" cm="1">
+        <f t="array" ref="C9">UPPER(INDEX(_xlfn.TEXTSPLIT($D9, "-"), 3))</f>
+        <v>DIS</v>
+      </c>
       <c r="D9" s="1" t="s">
         <v>310</v>
       </c>
@@ -6891,11 +6901,14 @@
       <c r="AF9" s="1"/>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A10" s="100"/>
+      <c r="A10" s="99"/>
       <c r="B10" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="1"/>
+      <c r="C10" s="1" t="str" cm="1">
+        <f t="array" ref="C10">UPPER(INDEX(_xlfn.TEXTSPLIT($D10, "-"), 3))</f>
+        <v>DIS</v>
+      </c>
       <c r="D10" s="1" t="s">
         <v>310</v>
       </c>
@@ -6977,7 +6990,7 @@
       <c r="AF10" s="1"/>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A11" s="101"/>
+      <c r="A11" s="99"/>
       <c r="B11" s="1" t="s">
         <v>81</v>
       </c>
@@ -7066,11 +7079,14 @@
       <c r="AF11" s="1"/>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A12" s="100"/>
+      <c r="A12" s="99"/>
       <c r="B12" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="1"/>
+      <c r="C12" s="1" t="str" cm="1">
+        <f t="array" ref="C12">UPPER(INDEX(_xlfn.TEXTSPLIT($D12, "-"), 3))</f>
+        <v>DIS</v>
+      </c>
       <c r="D12" s="1" t="s">
         <v>310</v>
       </c>
@@ -7152,7 +7168,7 @@
       <c r="AF12" s="1"/>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A13" s="101"/>
+      <c r="A13" s="99"/>
       <c r="B13" s="1" t="s">
         <v>81</v>
       </c>
@@ -7241,7 +7257,7 @@
       <c r="AF13" s="1"/>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A14" s="104"/>
+      <c r="A14" s="100"/>
       <c r="B14" s="1" t="s">
         <v>81</v>
       </c>
@@ -7330,11 +7346,14 @@
       <c r="AF14" s="1"/>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A15" s="82"/>
+      <c r="A15" s="100"/>
       <c r="B15" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C15" s="1"/>
+      <c r="C15" s="1" t="str" cm="1">
+        <f t="array" ref="C15">UPPER(INDEX(_xlfn.TEXTSPLIT($D15, "-"), 3))</f>
+        <v>DIS</v>
+      </c>
       <c r="D15" s="1" t="s">
         <v>310</v>
       </c>
@@ -7416,7 +7435,7 @@
       <c r="AF15" s="1"/>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A16" s="104"/>
+      <c r="A16" s="100"/>
       <c r="B16" s="1" t="s">
         <v>81</v>
       </c>
@@ -7505,11 +7524,14 @@
       <c r="AF16" s="1"/>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A17" s="82"/>
+      <c r="A17" s="100"/>
       <c r="B17" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C17" s="1"/>
+      <c r="C17" s="1" t="str" cm="1">
+        <f t="array" ref="C17">UPPER(INDEX(_xlfn.TEXTSPLIT($D17, "-"), 3))</f>
+        <v>DIS</v>
+      </c>
       <c r="D17" s="1" t="s">
         <v>310</v>
       </c>
@@ -7517,7 +7539,7 @@
         <v>24</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>349</v>
+        <v>539</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>350</v>
@@ -7591,11 +7613,14 @@
       <c r="AF17" s="1"/>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A18" s="82"/>
+      <c r="A18" s="100"/>
       <c r="B18" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C18" s="1"/>
+      <c r="C18" s="1" t="str" cm="1">
+        <f t="array" ref="C18">UPPER(INDEX(_xlfn.TEXTSPLIT($D18, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
       <c r="D18" s="1" t="s">
         <v>351</v>
       </c>
@@ -7677,11 +7702,14 @@
       <c r="AF18" s="1"/>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A19" s="82"/>
+      <c r="A19" s="100"/>
       <c r="B19" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C19" s="1"/>
+      <c r="C19" s="1" t="str" cm="1">
+        <f t="array" ref="C19">UPPER(INDEX(_xlfn.TEXTSPLIT($D19, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
       <c r="D19" s="1" t="s">
         <v>351</v>
       </c>
@@ -7763,11 +7791,14 @@
       <c r="AF19" s="1"/>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A20" s="82"/>
+      <c r="A20" s="100"/>
       <c r="B20" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C20" s="1"/>
+      <c r="C20" s="1" t="str" cm="1">
+        <f t="array" ref="C20">UPPER(INDEX(_xlfn.TEXTSPLIT($D20, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
       <c r="D20" s="1" t="s">
         <v>351</v>
       </c>
@@ -7849,11 +7880,14 @@
       <c r="AF20" s="1"/>
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A21" s="82"/>
+      <c r="A21" s="100"/>
       <c r="B21" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C21" s="1"/>
+      <c r="C21" s="1" t="str" cm="1">
+        <f t="array" ref="C21">UPPER(INDEX(_xlfn.TEXTSPLIT($D21, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
       <c r="D21" s="1" t="s">
         <v>351</v>
       </c>
@@ -7935,11 +7969,14 @@
       <c r="AF21" s="1"/>
     </row>
     <row r="22" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A22" s="82"/>
+      <c r="A22" s="100"/>
       <c r="B22" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C22" s="1"/>
+      <c r="C22" s="1" t="str" cm="1">
+        <f t="array" ref="C22">UPPER(INDEX(_xlfn.TEXTSPLIT($D22, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
       <c r="D22" s="1" t="s">
         <v>351</v>
       </c>
@@ -8021,7 +8058,7 @@
       <c r="AF22" s="1"/>
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A23" s="104"/>
+      <c r="A23" s="100"/>
       <c r="B23" s="1" t="s">
         <v>81</v>
       </c>
@@ -8110,7 +8147,7 @@
       <c r="AF23" s="1"/>
     </row>
     <row r="24" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A24" s="104"/>
+      <c r="A24" s="100"/>
       <c r="B24" s="1" t="s">
         <v>81</v>
       </c>
@@ -8199,11 +8236,14 @@
       <c r="AF24" s="1"/>
     </row>
     <row r="25" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A25" s="82"/>
+      <c r="A25" s="100"/>
       <c r="B25" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C25" s="1"/>
+      <c r="C25" s="1" t="str" cm="1">
+        <f t="array" ref="C25">UPPER(INDEX(_xlfn.TEXTSPLIT($D25, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
       <c r="D25" s="1" t="s">
         <v>351</v>
       </c>
@@ -8285,11 +8325,14 @@
       <c r="AF25" s="1"/>
     </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A26" s="82"/>
+      <c r="A26" s="100"/>
       <c r="B26" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C26" s="1"/>
+      <c r="C26" s="1" t="str" cm="1">
+        <f t="array" ref="C26">UPPER(INDEX(_xlfn.TEXTSPLIT($D26, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
       <c r="D26" s="1" t="s">
         <v>351</v>
       </c>
@@ -8371,7 +8414,7 @@
       <c r="AF26" s="1"/>
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A27" s="104"/>
+      <c r="A27" s="100"/>
       <c r="B27" s="1" t="s">
         <v>81</v>
       </c>
@@ -8460,11 +8503,14 @@
       <c r="AF27" s="1"/>
     </row>
     <row r="28" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A28" s="82"/>
+      <c r="A28" s="100"/>
       <c r="B28" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C28" s="1"/>
+      <c r="C28" s="1" t="str" cm="1">
+        <f t="array" ref="C28">UPPER(INDEX(_xlfn.TEXTSPLIT($D28, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
       <c r="D28" s="1" t="s">
         <v>351</v>
       </c>
@@ -8546,11 +8592,14 @@
       <c r="AF28" s="1"/>
     </row>
     <row r="29" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A29" s="82"/>
+      <c r="A29" s="100"/>
       <c r="B29" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C29" s="1"/>
+      <c r="C29" s="1" t="str" cm="1">
+        <f t="array" ref="C29">UPPER(INDEX(_xlfn.TEXTSPLIT($D29, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
       <c r="D29" s="1" t="s">
         <v>351</v>
       </c>
@@ -8632,11 +8681,14 @@
       <c r="AF29" s="1"/>
     </row>
     <row r="30" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A30" s="82"/>
+      <c r="A30" s="100"/>
       <c r="B30" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C30" s="1"/>
+      <c r="C30" s="1" t="str" cm="1">
+        <f t="array" ref="C30">UPPER(INDEX(_xlfn.TEXTSPLIT($D30, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
       <c r="D30" s="1" t="s">
         <v>351</v>
       </c>
@@ -8718,11 +8770,14 @@
       <c r="AF30" s="1"/>
     </row>
     <row r="31" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A31" s="82"/>
+      <c r="A31" s="100"/>
       <c r="B31" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C31" s="1"/>
+      <c r="C31" s="1" t="str" cm="1">
+        <f t="array" ref="C31">UPPER(INDEX(_xlfn.TEXTSPLIT($D31, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
       <c r="D31" s="1" t="s">
         <v>351</v>
       </c>
@@ -8804,11 +8859,14 @@
       <c r="AF31" s="1"/>
     </row>
     <row r="32" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A32" s="82"/>
+      <c r="A32" s="100"/>
       <c r="B32" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C32" s="1"/>
+      <c r="C32" s="1" t="str" cm="1">
+        <f t="array" ref="C32">UPPER(INDEX(_xlfn.TEXTSPLIT($D32, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
       <c r="D32" s="1" t="s">
         <v>351</v>
       </c>
@@ -8890,11 +8948,14 @@
       <c r="AF32" s="1"/>
     </row>
     <row r="33" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A33" s="82"/>
+      <c r="A33" s="100"/>
       <c r="B33" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C33" s="1"/>
+      <c r="C33" s="1" t="str" cm="1">
+        <f t="array" ref="C33">UPPER(INDEX(_xlfn.TEXTSPLIT($D33, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
       <c r="D33" s="1" t="s">
         <v>351</v>
       </c>
@@ -8976,7 +9037,7 @@
       <c r="AF33" s="1"/>
     </row>
     <row r="34" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A34" s="104"/>
+      <c r="A34" s="100"/>
       <c r="B34" s="1" t="s">
         <v>81</v>
       </c>
@@ -9065,11 +9126,14 @@
       <c r="AF34" s="1"/>
     </row>
     <row r="35" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A35" s="82"/>
+      <c r="A35" s="100"/>
       <c r="B35" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C35" s="1"/>
+      <c r="C35" s="1" t="str" cm="1">
+        <f t="array" ref="C35">UPPER(INDEX(_xlfn.TEXTSPLIT($D35, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
       <c r="D35" s="1" t="s">
         <v>351</v>
       </c>
@@ -9151,11 +9215,14 @@
       <c r="AF35" s="1"/>
     </row>
     <row r="36" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A36" s="82"/>
+      <c r="A36" s="100"/>
       <c r="B36" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C36" s="1"/>
+      <c r="C36" s="1" t="str" cm="1">
+        <f t="array" ref="C36">UPPER(INDEX(_xlfn.TEXTSPLIT($D36, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
       <c r="D36" s="1" t="s">
         <v>351</v>
       </c>
@@ -9237,7 +9304,7 @@
       <c r="AF36" s="1"/>
     </row>
     <row r="37" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A37" s="104"/>
+      <c r="A37" s="100"/>
       <c r="B37" s="1" t="s">
         <v>81</v>
       </c>
@@ -9326,11 +9393,14 @@
       <c r="AF37" s="1"/>
     </row>
     <row r="38" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A38" s="82"/>
+      <c r="A38" s="100"/>
       <c r="B38" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C38" s="1"/>
+      <c r="C38" s="1" t="str" cm="1">
+        <f t="array" ref="C38">UPPER(INDEX(_xlfn.TEXTSPLIT($D38, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
       <c r="D38" s="1" t="s">
         <v>351</v>
       </c>
@@ -9412,7 +9482,7 @@
       <c r="AF38" s="1"/>
     </row>
     <row r="39" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A39" s="104"/>
+      <c r="A39" s="100"/>
       <c r="B39" s="1" t="s">
         <v>81</v>
       </c>
@@ -9501,7 +9571,7 @@
       <c r="AF39" s="1"/>
     </row>
     <row r="40" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A40" s="104"/>
+      <c r="A40" s="100"/>
       <c r="B40" s="1" t="s">
         <v>81</v>
       </c>
@@ -9590,11 +9660,14 @@
       <c r="AF40" s="1"/>
     </row>
     <row r="41" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A41" s="82"/>
+      <c r="A41" s="100"/>
       <c r="B41" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C41" s="1"/>
+      <c r="C41" s="1" t="str" cm="1">
+        <f t="array" ref="C41">UPPER(INDEX(_xlfn.TEXTSPLIT($D41, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
       <c r="D41" s="1" t="s">
         <v>351</v>
       </c>
@@ -9676,7 +9749,7 @@
       <c r="AF41" s="1"/>
     </row>
     <row r="42" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A42" s="104"/>
+      <c r="A42" s="100"/>
       <c r="B42" s="1" t="s">
         <v>81</v>
       </c>
@@ -9765,7 +9838,7 @@
       <c r="AF42" s="1"/>
     </row>
     <row r="43" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A43" s="104"/>
+      <c r="A43" s="100"/>
       <c r="B43" s="1" t="s">
         <v>81</v>
       </c>
@@ -9854,7 +9927,7 @@
       <c r="AF43" s="1"/>
     </row>
     <row r="44" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A44" s="104"/>
+      <c r="A44" s="100"/>
       <c r="B44" s="1" t="s">
         <v>81</v>
       </c>
@@ -9943,7 +10016,7 @@
       <c r="AF44" s="1"/>
     </row>
     <row r="45" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A45" s="104"/>
+      <c r="A45" s="100"/>
       <c r="B45" s="1" t="s">
         <v>81</v>
       </c>
@@ -10032,7 +10105,7 @@
       <c r="AF45" s="1"/>
     </row>
     <row r="46" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A46" s="104"/>
+      <c r="A46" s="100"/>
       <c r="B46" s="1" t="s">
         <v>81</v>
       </c>
@@ -10121,7 +10194,7 @@
       <c r="AF46" s="1"/>
     </row>
     <row r="47" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A47" s="104"/>
+      <c r="A47" s="100"/>
       <c r="B47" s="1" t="s">
         <v>81</v>
       </c>
@@ -10210,11 +10283,14 @@
       <c r="AF47" s="1"/>
     </row>
     <row r="48" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A48" s="82"/>
+      <c r="A48" s="100"/>
       <c r="B48" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C48" s="1"/>
+      <c r="C48" s="1" t="str" cm="1">
+        <f t="array" ref="C48">UPPER(INDEX(_xlfn.TEXTSPLIT($D48, "-"), 3))</f>
+        <v>DIP</v>
+      </c>
       <c r="D48" s="1" t="s">
         <v>473</v>
       </c>
@@ -10296,11 +10372,14 @@
       <c r="AF48" s="1"/>
     </row>
     <row r="49" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A49" s="82"/>
+      <c r="A49" s="100"/>
       <c r="B49" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C49" s="1"/>
+      <c r="C49" s="1" t="str" cm="1">
+        <f t="array" ref="C49">UPPER(INDEX(_xlfn.TEXTSPLIT($D49, "-"), 3))</f>
+        <v>DIP</v>
+      </c>
       <c r="D49" s="1" t="s">
         <v>473</v>
       </c>
@@ -10382,11 +10461,14 @@
       <c r="AF49" s="1"/>
     </row>
     <row r="50" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A50" s="82"/>
+      <c r="A50" s="100"/>
       <c r="B50" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C50" s="1"/>
+      <c r="C50" s="1" t="str" cm="1">
+        <f t="array" ref="C50">UPPER(INDEX(_xlfn.TEXTSPLIT($D50, "-"), 3))</f>
+        <v>DIP</v>
+      </c>
       <c r="D50" s="1" t="s">
         <v>473</v>
       </c>
@@ -10468,11 +10550,14 @@
       <c r="AF50" s="1"/>
     </row>
     <row r="51" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A51" s="82"/>
+      <c r="A51" s="100"/>
       <c r="B51" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C51" s="1"/>
+      <c r="C51" s="1" t="str" cm="1">
+        <f t="array" ref="C51">UPPER(INDEX(_xlfn.TEXTSPLIT($D51, "-"), 3))</f>
+        <v>DIP</v>
+      </c>
       <c r="D51" s="1" t="s">
         <v>473</v>
       </c>
@@ -10554,11 +10639,14 @@
       <c r="AF51" s="1"/>
     </row>
     <row r="52" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A52" s="82"/>
+      <c r="A52" s="100"/>
       <c r="B52" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C52" s="1"/>
+      <c r="C52" s="1" t="str" cm="1">
+        <f t="array" ref="C52">UPPER(INDEX(_xlfn.TEXTSPLIT($D52, "-"), 3))</f>
+        <v>DIP</v>
+      </c>
       <c r="D52" s="1" t="s">
         <v>473</v>
       </c>
@@ -10640,11 +10728,14 @@
       <c r="AF52" s="1"/>
     </row>
     <row r="53" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A53" s="82"/>
+      <c r="A53" s="100"/>
       <c r="B53" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C53" s="1"/>
+      <c r="C53" s="1" t="str" cm="1">
+        <f t="array" ref="C53">UPPER(INDEX(_xlfn.TEXTSPLIT($D53, "-"), 3))</f>
+        <v>DIP</v>
+      </c>
       <c r="D53" s="1" t="s">
         <v>473</v>
       </c>
@@ -10726,11 +10817,14 @@
       <c r="AF53" s="1"/>
     </row>
     <row r="54" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A54" s="82"/>
+      <c r="A54" s="100"/>
       <c r="B54" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C54" s="1"/>
+      <c r="C54" s="1" t="str" cm="1">
+        <f t="array" ref="C54">UPPER(INDEX(_xlfn.TEXTSPLIT($D54, "-"), 3))</f>
+        <v>DIP</v>
+      </c>
       <c r="D54" s="1" t="s">
         <v>473</v>
       </c>
@@ -10812,11 +10906,14 @@
       <c r="AF54" s="1"/>
     </row>
     <row r="55" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A55" s="82"/>
+      <c r="A55" s="100"/>
       <c r="B55" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C55" s="1"/>
+      <c r="C55" s="1" t="str" cm="1">
+        <f t="array" ref="C55">UPPER(INDEX(_xlfn.TEXTSPLIT($D55, "-"), 3))</f>
+        <v>DIP</v>
+      </c>
       <c r="D55" s="1" t="s">
         <v>473</v>
       </c>
@@ -10900,7 +10997,7 @@
       <c r="AF55" s="1"/>
     </row>
     <row r="56" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A56" s="104"/>
+      <c r="A56" s="100"/>
       <c r="B56" s="1" t="s">
         <v>81</v>
       </c>
@@ -10989,7 +11086,7 @@
       <c r="AF56" s="1"/>
     </row>
     <row r="57" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A57" s="104"/>
+      <c r="A57" s="100"/>
       <c r="B57" s="1" t="s">
         <v>81</v>
       </c>
@@ -11081,7 +11178,7 @@
       <c r="AF57" s="1"/>
     </row>
     <row r="58" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A58" s="104"/>
+      <c r="A58" s="100"/>
       <c r="B58" s="1" t="s">
         <v>81</v>
       </c>
@@ -11170,7 +11267,7 @@
       <c r="AF58" s="1"/>
     </row>
     <row r="59" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A59" s="104"/>
+      <c r="A59" s="100"/>
       <c r="B59" s="1" t="s">
         <v>81</v>
       </c>
@@ -11259,7 +11356,7 @@
       <c r="AF59" s="1"/>
     </row>
     <row r="60" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A60" s="104"/>
+      <c r="A60" s="100"/>
       <c r="B60" s="1" t="s">
         <v>81</v>
       </c>
@@ -11348,11 +11445,14 @@
       <c r="AF60" s="1"/>
     </row>
     <row r="61" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A61" s="82"/>
+      <c r="A61" s="100"/>
       <c r="B61" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C61" s="1"/>
+      <c r="C61" s="1" t="str" cm="1">
+        <f t="array" ref="C61">UPPER(INDEX(_xlfn.TEXTSPLIT($D61, "-"), 3))</f>
+        <v>IF</v>
+      </c>
       <c r="D61" s="1" t="s">
         <v>444</v>
       </c>
@@ -11434,13 +11534,16 @@
       <c r="AF61" s="1"/>
     </row>
     <row r="62" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A62" s="97" t="s">
+      <c r="A62" s="101" t="s">
         <v>508</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C62" s="1"/>
+      <c r="C62" s="1" t="str" cm="1">
+        <f t="array" ref="C62">UPPER(INDEX(_xlfn.TEXTSPLIT($D62, "-"), 3))</f>
+        <v>CS</v>
+      </c>
       <c r="D62" s="1" t="s">
         <v>175</v>
       </c>
@@ -11522,13 +11625,16 @@
       <c r="AF62" s="1"/>
     </row>
     <row r="63" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A63" s="97" t="s">
+      <c r="A63" s="101" t="s">
         <v>508</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C63" s="1"/>
+      <c r="C63" s="1" t="str" cm="1">
+        <f t="array" ref="C63">UPPER(INDEX(_xlfn.TEXTSPLIT($D63, "-"), 3))</f>
+        <v>CS</v>
+      </c>
       <c r="D63" s="1" t="s">
         <v>451</v>
       </c>
@@ -11610,13 +11716,16 @@
       <c r="AF63" s="1"/>
     </row>
     <row r="64" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A64" s="97" t="s">
+      <c r="A64" s="101" t="s">
         <v>508</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C64" s="1"/>
+      <c r="C64" s="1" t="str" cm="1">
+        <f t="array" ref="C64">UPPER(INDEX(_xlfn.TEXTSPLIT($D64, "-"), 3))</f>
+        <v>CS</v>
+      </c>
       <c r="D64" s="1" t="s">
         <v>451</v>
       </c>
@@ -11698,11 +11807,14 @@
       <c r="AF64" s="1"/>
     </row>
     <row r="65" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A65" s="82"/>
+      <c r="A65" s="100"/>
       <c r="B65" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C65" s="1"/>
+      <c r="C65" s="1" t="str" cm="1">
+        <f t="array" ref="C65">UPPER(INDEX(_xlfn.TEXTSPLIT($D65, "-"), 3))</f>
+        <v>DOIP</v>
+      </c>
       <c r="D65" s="1" t="s">
         <v>457</v>
       </c>
@@ -11784,11 +11896,14 @@
       <c r="AF65" s="1"/>
     </row>
     <row r="66" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A66" s="82"/>
+      <c r="A66" s="100"/>
       <c r="B66" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C66" s="1"/>
+      <c r="C66" s="1" t="str" cm="1">
+        <f t="array" ref="C66">UPPER(INDEX(_xlfn.TEXTSPLIT($D66, "-"), 3))</f>
+        <v>DOIP</v>
+      </c>
       <c r="D66" s="1" t="s">
         <v>457</v>
       </c>
@@ -11870,11 +11985,14 @@
       <c r="AF66" s="1"/>
     </row>
     <row r="67" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A67" s="82"/>
+      <c r="A67" s="100"/>
       <c r="B67" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C67" s="1"/>
+      <c r="C67" s="1" t="str" cm="1">
+        <f t="array" ref="C67">UPPER(INDEX(_xlfn.TEXTSPLIT($D67, "-"), 3))</f>
+        <v>DOIP</v>
+      </c>
       <c r="D67" s="1" t="s">
         <v>457</v>
       </c>
@@ -11956,7 +12074,7 @@
       <c r="AF67" s="1"/>
     </row>
     <row r="68" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A68" s="104"/>
+      <c r="A68" s="100"/>
       <c r="B68" s="1" t="s">
         <v>81</v>
       </c>
@@ -12045,11 +12163,14 @@
       <c r="AF68" s="1"/>
     </row>
     <row r="69" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A69" s="82"/>
+      <c r="A69" s="100"/>
       <c r="B69" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C69" s="1"/>
+      <c r="C69" s="1" t="str" cm="1">
+        <f t="array" ref="C69">UPPER(INDEX(_xlfn.TEXTSPLIT($D69, "-"), 3))</f>
+        <v>BDP</v>
+      </c>
       <c r="D69" s="1" t="s">
         <v>403</v>
       </c>
@@ -12131,11 +12252,14 @@
       <c r="AF69" s="1"/>
     </row>
     <row r="70" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A70" s="82"/>
+      <c r="A70" s="100"/>
       <c r="B70" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C70" s="1"/>
+      <c r="C70" s="1" t="str" cm="1">
+        <f t="array" ref="C70">UPPER(INDEX(_xlfn.TEXTSPLIT($D70, "-"), 3))</f>
+        <v>BDP</v>
+      </c>
       <c r="D70" s="1" t="s">
         <v>403</v>
       </c>
@@ -12217,11 +12341,14 @@
       <c r="AF70" s="1"/>
     </row>
     <row r="71" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A71" s="85"/>
+      <c r="A71" s="102"/>
       <c r="B71" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C71" s="1"/>
+      <c r="C71" s="1" t="str" cm="1">
+        <f t="array" ref="C71">UPPER(INDEX(_xlfn.TEXTSPLIT($D71, "-"), 3))</f>
+        <v>DIS</v>
+      </c>
       <c r="D71" s="1" t="s">
         <v>310</v>
       </c>
@@ -12317,68 +12444,68 @@
   <dimension ref="A1:R71"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.625" style="90" customWidth="1"/>
-    <col min="2" max="2" width="5.75" style="90" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="90" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.625" style="90" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.625" style="90" customWidth="1"/>
-    <col min="6" max="6" width="19.875" style="90" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.5" style="90" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15" style="90" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.25" style="90" customWidth="1"/>
-    <col min="10" max="10" width="21.5" style="90" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15" style="90" bestFit="1" customWidth="1"/>
-    <col min="12" max="17" width="14.125" style="90" customWidth="1"/>
+    <col min="1" max="1" width="4.625" style="89" customWidth="1"/>
+    <col min="2" max="2" width="5.75" style="89" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="89" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.625" style="89" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.625" style="89" customWidth="1"/>
+    <col min="6" max="6" width="19.875" style="89" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.5" style="89" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15" style="89" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.25" style="89" customWidth="1"/>
+    <col min="10" max="10" width="21.5" style="89" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15" style="89" bestFit="1" customWidth="1"/>
+    <col min="12" max="17" width="14.125" style="89" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="91"/>
-      <c r="B1" s="92" t="s">
+      <c r="A1" s="90"/>
+      <c r="B1" s="91" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="92" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="87" t="s">
+      <c r="C1" s="91" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="87" t="s">
+      <c r="E1" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="87" t="s">
+      <c r="F1" s="86" t="s">
         <v>491</v>
       </c>
-      <c r="G1" s="87" t="s">
+      <c r="G1" s="86" t="s">
         <v>493</v>
       </c>
-      <c r="H1" s="87" t="s">
+      <c r="H1" s="86" t="s">
         <v>495</v>
       </c>
-      <c r="I1" s="87" t="s">
+      <c r="I1" s="86" t="s">
         <v>496</v>
       </c>
-      <c r="J1" s="87" t="s">
+      <c r="J1" s="86" t="s">
         <v>494</v>
       </c>
-      <c r="K1" s="87" t="s">
+      <c r="K1" s="86" t="s">
         <v>497</v>
       </c>
-      <c r="L1" s="87" t="s">
+      <c r="L1" s="86" t="s">
         <v>498</v>
       </c>
-      <c r="M1" s="87" t="s">
+      <c r="M1" s="86" t="s">
         <v>492</v>
       </c>
-      <c r="N1" s="87" t="s">
+      <c r="N1" s="86" t="s">
         <v>501</v>
       </c>
-      <c r="O1" s="87" t="s">
+      <c r="O1" s="86" t="s">
         <v>503</v>
       </c>
-      <c r="P1" s="87" t="s">
+      <c r="P1" s="86" t="s">
         <v>172</v>
       </c>
-      <c r="Q1" s="87" t="s">
+      <c r="Q1" s="86" t="s">
         <v>500</v>
       </c>
       <c r="R1" s="55" t="s">
@@ -12386,3713 +12513,3849 @@
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" s="93"/>
-      <c r="B2" s="88" t="s">
+      <c r="A2" s="92"/>
+      <c r="B2" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88" t="s">
+      <c r="C2" s="87" t="str" cm="1">
+        <f t="array" ref="C2">UPPER(INDEX(_xlfn.TEXTSPLIT($D2, "-"), 3))</f>
+        <v>DIS</v>
+      </c>
+      <c r="D2" s="87" t="s">
         <v>176</v>
       </c>
-      <c r="E2" s="94" t="s">
+      <c r="E2" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="88" t="s">
+      <c r="F2" s="87" t="s">
         <v>311</v>
       </c>
-      <c r="G2" s="88" t="str">
+      <c r="G2" s="87" t="str">
         <f>SUBSTITUTE($F2,"hazr-","")&amp;"-disk01"</f>
         <v>d-dis-ap01-disk01</v>
       </c>
-      <c r="H2" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="I2" s="88">
-        <v>64</v>
-      </c>
-      <c r="J2" s="88" t="str">
+      <c r="H2" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="I2" s="87">
+        <v>64</v>
+      </c>
+      <c r="J2" s="87" t="str">
         <f>SUBSTITUTE($F2,"hazr-","")&amp;"-disk02"</f>
         <v>d-dis-ap01-disk02</v>
       </c>
-      <c r="K2" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="L2" s="88">
-        <v>64</v>
-      </c>
-      <c r="M2" s="88">
-        <v>1</v>
-      </c>
-      <c r="N2" s="88" t="s">
+      <c r="K2" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="L2" s="87">
+        <v>64</v>
+      </c>
+      <c r="M2" s="87">
+        <v>1</v>
+      </c>
+      <c r="N2" s="87" t="s">
         <v>502</v>
       </c>
-      <c r="O2" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="P2" s="88" t="s">
+      <c r="O2" s="87" t="s">
+        <v>173</v>
+      </c>
+      <c r="P2" s="87" t="s">
         <v>499</v>
       </c>
-      <c r="Q2" s="88" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" s="86"/>
+      <c r="Q2" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" s="85"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A3" s="102"/>
-      <c r="B3" s="89" t="s">
+      <c r="A3" s="94"/>
+      <c r="B3" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C3" s="89" t="str" cm="1">
+      <c r="C3" s="88" t="str" cm="1">
         <f t="array" ref="C3">UPPER(INDEX(_xlfn.TEXTSPLIT($D3, "-"), 3))</f>
         <v>DIS</v>
       </c>
-      <c r="D3" s="89" t="s">
+      <c r="D3" s="88" t="s">
         <v>310</v>
       </c>
-      <c r="E3" s="96" t="s">
+      <c r="E3" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="89" t="s">
+      <c r="F3" s="88" t="s">
         <v>317</v>
       </c>
-      <c r="G3" s="89" t="str">
+      <c r="G3" s="88" t="str">
         <f t="shared" ref="G3:G66" si="0">SUBSTITUTE($F3,"hazr-","")&amp;"-disk01"</f>
         <v>d-dis-adm01-disk01</v>
       </c>
-      <c r="H3" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="I3" s="89">
-        <v>64</v>
-      </c>
-      <c r="J3" s="89" t="str">
+      <c r="H3" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="I3" s="88">
+        <v>64</v>
+      </c>
+      <c r="J3" s="88" t="str">
         <f t="shared" ref="J3:J66" si="1">SUBSTITUTE($F3,"hazr-","")&amp;"-disk02"</f>
         <v>d-dis-adm01-disk02</v>
       </c>
-      <c r="K3" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="L3" s="89">
-        <v>64</v>
-      </c>
-      <c r="M3" s="89">
-        <v>1</v>
-      </c>
-      <c r="N3" s="89" t="s">
+      <c r="K3" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="L3" s="88">
+        <v>64</v>
+      </c>
+      <c r="M3" s="88">
+        <v>1</v>
+      </c>
+      <c r="N3" s="88" t="s">
         <v>502</v>
       </c>
-      <c r="O3" s="89" t="s">
-        <v>173</v>
-      </c>
-      <c r="P3" s="89" t="s">
+      <c r="O3" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="P3" s="88" t="s">
         <v>499</v>
       </c>
-      <c r="Q3" s="89" t="b">
+      <c r="Q3" s="88" t="b">
         <v>1</v>
       </c>
       <c r="R3" s="56"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="103"/>
-      <c r="B4" s="88" t="s">
+      <c r="A4" s="92"/>
+      <c r="B4" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C4" s="88" t="str" cm="1">
+      <c r="C4" s="87" t="str" cm="1">
         <f t="array" ref="C4">UPPER(INDEX(_xlfn.TEXTSPLIT($D4, "-"), 3))</f>
         <v>DIS</v>
       </c>
-      <c r="D4" s="88" t="s">
+      <c r="D4" s="87" t="s">
         <v>310</v>
       </c>
-      <c r="E4" s="94" t="s">
+      <c r="E4" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="88" t="s">
+      <c r="F4" s="87" t="s">
         <v>319</v>
       </c>
-      <c r="G4" s="88" t="str">
+      <c r="G4" s="87" t="str">
         <f t="shared" si="0"/>
         <v>d-dis-bbiweb01-disk01</v>
       </c>
-      <c r="H4" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="I4" s="88">
-        <v>64</v>
-      </c>
-      <c r="J4" s="88" t="str">
+      <c r="H4" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="I4" s="87">
+        <v>64</v>
+      </c>
+      <c r="J4" s="87" t="str">
         <f t="shared" si="1"/>
         <v>d-dis-bbiweb01-disk02</v>
       </c>
-      <c r="K4" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="L4" s="88">
-        <v>64</v>
-      </c>
-      <c r="M4" s="88">
-        <v>1</v>
-      </c>
-      <c r="N4" s="88" t="s">
+      <c r="K4" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="L4" s="87">
+        <v>64</v>
+      </c>
+      <c r="M4" s="87">
+        <v>1</v>
+      </c>
+      <c r="N4" s="87" t="s">
         <v>502</v>
       </c>
-      <c r="O4" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="P4" s="88" t="s">
+      <c r="O4" s="87" t="s">
+        <v>173</v>
+      </c>
+      <c r="P4" s="87" t="s">
         <v>499</v>
       </c>
-      <c r="Q4" s="88" t="b">
-        <v>1</v>
-      </c>
-      <c r="R4" s="86"/>
+      <c r="Q4" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="R4" s="85"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A5" s="95"/>
-      <c r="B5" s="89" t="s">
+      <c r="A5" s="94"/>
+      <c r="B5" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89" t="s">
+      <c r="C5" s="88" t="str" cm="1">
+        <f t="array" ref="C5">UPPER(INDEX(_xlfn.TEXTSPLIT($D5, "-"), 3))</f>
+        <v>DIS</v>
+      </c>
+      <c r="D5" s="88" t="s">
         <v>310</v>
       </c>
-      <c r="E5" s="96" t="s">
+      <c r="E5" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="89" t="s">
+      <c r="F5" s="88" t="s">
         <v>325</v>
       </c>
-      <c r="G5" s="89" t="str">
+      <c r="G5" s="88" t="str">
         <f t="shared" si="0"/>
         <v>d-dis-bbicltap01-disk01</v>
       </c>
-      <c r="H5" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="I5" s="89">
-        <v>64</v>
-      </c>
-      <c r="J5" s="89" t="str">
+      <c r="H5" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="I5" s="88">
+        <v>64</v>
+      </c>
+      <c r="J5" s="88" t="str">
         <f t="shared" si="1"/>
         <v>d-dis-bbicltap01-disk02</v>
       </c>
-      <c r="K5" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="L5" s="89">
-        <v>64</v>
-      </c>
-      <c r="M5" s="89">
-        <v>1</v>
-      </c>
-      <c r="N5" s="89" t="s">
+      <c r="K5" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="L5" s="88">
+        <v>64</v>
+      </c>
+      <c r="M5" s="88">
+        <v>1</v>
+      </c>
+      <c r="N5" s="88" t="s">
         <v>502</v>
       </c>
-      <c r="O5" s="89" t="s">
-        <v>173</v>
-      </c>
-      <c r="P5" s="89" t="s">
+      <c r="O5" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="P5" s="88" t="s">
         <v>499</v>
       </c>
-      <c r="Q5" s="89" t="b">
+      <c r="Q5" s="88" t="b">
         <v>1</v>
       </c>
       <c r="R5" s="56"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" s="93"/>
-      <c r="B6" s="88" t="s">
+      <c r="A6" s="92"/>
+      <c r="B6" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C6" s="88"/>
-      <c r="D6" s="88" t="s">
+      <c r="C6" s="87" t="str" cm="1">
+        <f t="array" ref="C6">UPPER(INDEX(_xlfn.TEXTSPLIT($D6, "-"), 3))</f>
+        <v>DIS</v>
+      </c>
+      <c r="D6" s="87" t="s">
         <v>310</v>
       </c>
-      <c r="E6" s="94" t="s">
+      <c r="E6" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="88" t="s">
+      <c r="F6" s="87" t="s">
         <v>327</v>
       </c>
-      <c r="G6" s="88" t="str">
+      <c r="G6" s="87" t="str">
         <f t="shared" si="0"/>
         <v>d-dis-bbimsgap01-disk01</v>
       </c>
-      <c r="H6" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="I6" s="88">
-        <v>64</v>
-      </c>
-      <c r="J6" s="88" t="str">
+      <c r="H6" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="I6" s="87">
+        <v>64</v>
+      </c>
+      <c r="J6" s="87" t="str">
         <f t="shared" si="1"/>
         <v>d-dis-bbimsgap01-disk02</v>
       </c>
-      <c r="K6" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="L6" s="88">
-        <v>64</v>
-      </c>
-      <c r="M6" s="88">
-        <v>1</v>
-      </c>
-      <c r="N6" s="88" t="s">
+      <c r="K6" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="L6" s="87">
+        <v>64</v>
+      </c>
+      <c r="M6" s="87">
+        <v>1</v>
+      </c>
+      <c r="N6" s="87" t="s">
         <v>502</v>
       </c>
-      <c r="O6" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="P6" s="88" t="s">
+      <c r="O6" s="87" t="s">
+        <v>173</v>
+      </c>
+      <c r="P6" s="87" t="s">
         <v>499</v>
       </c>
-      <c r="Q6" s="88" t="b">
-        <v>1</v>
-      </c>
-      <c r="R6" s="86"/>
+      <c r="Q6" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" s="85"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A7" s="95"/>
-      <c r="B7" s="89" t="s">
+      <c r="A7" s="94"/>
+      <c r="B7" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C7" s="89"/>
-      <c r="D7" s="89" t="s">
+      <c r="C7" s="88" t="str" cm="1">
+        <f t="array" ref="C7">UPPER(INDEX(_xlfn.TEXTSPLIT($D7, "-"), 3))</f>
+        <v>DIS</v>
+      </c>
+      <c r="D7" s="88" t="s">
         <v>310</v>
       </c>
-      <c r="E7" s="96" t="s">
+      <c r="E7" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="89" t="s">
+      <c r="F7" s="88" t="s">
         <v>329</v>
       </c>
-      <c r="G7" s="89" t="str">
+      <c r="G7" s="88" t="str">
         <f t="shared" si="0"/>
         <v>d-dis-walkap01-disk01</v>
       </c>
-      <c r="H7" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="I7" s="89">
-        <v>64</v>
-      </c>
-      <c r="J7" s="89" t="str">
+      <c r="H7" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="I7" s="88">
+        <v>64</v>
+      </c>
+      <c r="J7" s="88" t="str">
         <f t="shared" si="1"/>
         <v>d-dis-walkap01-disk02</v>
       </c>
-      <c r="K7" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="L7" s="89">
-        <v>64</v>
-      </c>
-      <c r="M7" s="89">
-        <v>1</v>
-      </c>
-      <c r="N7" s="89" t="s">
+      <c r="K7" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="L7" s="88">
+        <v>64</v>
+      </c>
+      <c r="M7" s="88">
+        <v>1</v>
+      </c>
+      <c r="N7" s="88" t="s">
         <v>502</v>
       </c>
-      <c r="O7" s="89" t="s">
-        <v>173</v>
-      </c>
-      <c r="P7" s="89" t="s">
+      <c r="O7" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="P7" s="88" t="s">
         <v>499</v>
       </c>
-      <c r="Q7" s="89" t="b">
+      <c r="Q7" s="88" t="b">
         <v>1</v>
       </c>
       <c r="R7" s="56"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A8" s="93"/>
-      <c r="B8" s="88" t="s">
+      <c r="A8" s="92"/>
+      <c r="B8" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C8" s="88"/>
-      <c r="D8" s="88" t="s">
+      <c r="C8" s="87" t="str" cm="1">
+        <f t="array" ref="C8">UPPER(INDEX(_xlfn.TEXTSPLIT($D8, "-"), 3))</f>
+        <v>DIS</v>
+      </c>
+      <c r="D8" s="87" t="s">
         <v>310</v>
       </c>
-      <c r="E8" s="94" t="s">
+      <c r="E8" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="88" t="s">
+      <c r="F8" s="87" t="s">
         <v>331</v>
       </c>
-      <c r="G8" s="88" t="str">
+      <c r="G8" s="87" t="str">
         <f t="shared" si="0"/>
         <v>d-dis-bat01-disk01</v>
       </c>
-      <c r="H8" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="I8" s="88">
-        <v>64</v>
-      </c>
-      <c r="J8" s="88" t="str">
+      <c r="H8" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="I8" s="87">
+        <v>64</v>
+      </c>
+      <c r="J8" s="87" t="str">
         <f t="shared" si="1"/>
         <v>d-dis-bat01-disk02</v>
       </c>
-      <c r="K8" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="L8" s="88">
-        <v>64</v>
-      </c>
-      <c r="M8" s="88">
-        <v>1</v>
-      </c>
-      <c r="N8" s="88" t="s">
+      <c r="K8" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="L8" s="87">
+        <v>64</v>
+      </c>
+      <c r="M8" s="87">
+        <v>1</v>
+      </c>
+      <c r="N8" s="87" t="s">
         <v>502</v>
       </c>
-      <c r="O8" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="P8" s="88" t="s">
+      <c r="O8" s="87" t="s">
+        <v>173</v>
+      </c>
+      <c r="P8" s="87" t="s">
         <v>499</v>
       </c>
-      <c r="Q8" s="88" t="b">
-        <v>1</v>
-      </c>
-      <c r="R8" s="86"/>
+      <c r="Q8" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" s="85"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A9" s="98"/>
-      <c r="B9" s="89" t="s">
+      <c r="A9" s="96"/>
+      <c r="B9" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C9" s="89"/>
-      <c r="D9" s="89" t="s">
+      <c r="C9" s="88" t="str" cm="1">
+        <f t="array" ref="C9">UPPER(INDEX(_xlfn.TEXTSPLIT($D9, "-"), 3))</f>
+        <v>DIS</v>
+      </c>
+      <c r="D9" s="88" t="s">
         <v>310</v>
       </c>
-      <c r="E9" s="96" t="s">
+      <c r="E9" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="F9" s="89" t="s">
+      <c r="F9" s="88" t="s">
         <v>333</v>
       </c>
-      <c r="G9" s="89" t="str">
+      <c r="G9" s="88" t="str">
         <f t="shared" si="0"/>
         <v>d-dis-bat02-disk01</v>
       </c>
-      <c r="H9" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="I9" s="89">
-        <v>64</v>
-      </c>
-      <c r="J9" s="89" t="str">
+      <c r="H9" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="I9" s="88">
+        <v>64</v>
+      </c>
+      <c r="J9" s="88" t="str">
         <f t="shared" si="1"/>
         <v>d-dis-bat02-disk02</v>
       </c>
-      <c r="K9" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="L9" s="89">
-        <v>64</v>
-      </c>
-      <c r="M9" s="89">
-        <v>1</v>
-      </c>
-      <c r="N9" s="89" t="s">
+      <c r="K9" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="L9" s="88">
+        <v>64</v>
+      </c>
+      <c r="M9" s="88">
+        <v>1</v>
+      </c>
+      <c r="N9" s="88" t="s">
         <v>502</v>
       </c>
-      <c r="O9" s="89" t="s">
-        <v>173</v>
-      </c>
-      <c r="P9" s="89" t="s">
+      <c r="O9" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="P9" s="88" t="s">
         <v>499</v>
       </c>
-      <c r="Q9" s="89" t="b">
+      <c r="Q9" s="88" t="b">
         <v>1</v>
       </c>
       <c r="R9" s="56"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A10" s="95"/>
-      <c r="B10" s="88" t="s">
+      <c r="A10" s="94"/>
+      <c r="B10" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="88"/>
-      <c r="D10" s="88" t="s">
+      <c r="C10" s="87" t="str" cm="1">
+        <f t="array" ref="C10">UPPER(INDEX(_xlfn.TEXTSPLIT($D10, "-"), 3))</f>
+        <v>DIS</v>
+      </c>
+      <c r="D10" s="87" t="s">
         <v>310</v>
       </c>
-      <c r="E10" s="94" t="s">
+      <c r="E10" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="88" t="s">
+      <c r="F10" s="87" t="s">
         <v>335</v>
       </c>
-      <c r="G10" s="88" t="str">
+      <c r="G10" s="87" t="str">
         <f t="shared" si="0"/>
         <v>d-dis-drvcltap01-disk01</v>
       </c>
-      <c r="H10" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="I10" s="88">
-        <v>64</v>
-      </c>
-      <c r="J10" s="88" t="str">
+      <c r="H10" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="I10" s="87">
+        <v>64</v>
+      </c>
+      <c r="J10" s="87" t="str">
         <f t="shared" si="1"/>
         <v>d-dis-drvcltap01-disk02</v>
       </c>
-      <c r="K10" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="L10" s="88">
-        <v>64</v>
-      </c>
-      <c r="M10" s="88">
-        <v>1</v>
-      </c>
-      <c r="N10" s="88" t="s">
+      <c r="K10" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="L10" s="87">
+        <v>64</v>
+      </c>
+      <c r="M10" s="87">
+        <v>1</v>
+      </c>
+      <c r="N10" s="87" t="s">
         <v>502</v>
       </c>
-      <c r="O10" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="P10" s="88" t="s">
+      <c r="O10" s="87" t="s">
+        <v>173</v>
+      </c>
+      <c r="P10" s="87" t="s">
         <v>499</v>
       </c>
-      <c r="Q10" s="88" t="b">
-        <v>1</v>
-      </c>
-      <c r="R10" s="86"/>
+      <c r="Q10" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" s="85"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A11" s="103"/>
-      <c r="B11" s="89" t="s">
+      <c r="A11" s="92"/>
+      <c r="B11" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C11" s="89" t="s">
-        <v>479</v>
-      </c>
-      <c r="D11" s="89" t="s">
+      <c r="C11" s="88" t="str" cm="1">
+        <f t="array" ref="C11">UPPER(INDEX(_xlfn.TEXTSPLIT($D11, "-"), 3))</f>
+        <v>DIS</v>
+      </c>
+      <c r="D11" s="88" t="s">
         <v>310</v>
       </c>
-      <c r="E11" s="96" t="s">
+      <c r="E11" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="89" t="s">
+      <c r="F11" s="88" t="s">
         <v>337</v>
       </c>
-      <c r="G11" s="89" t="str">
+      <c r="G11" s="88" t="str">
         <f t="shared" si="0"/>
         <v>d-dis-walkweb01-disk01</v>
       </c>
-      <c r="H11" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="I11" s="89">
-        <v>64</v>
-      </c>
-      <c r="J11" s="89" t="str">
+      <c r="H11" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="I11" s="88">
+        <v>64</v>
+      </c>
+      <c r="J11" s="88" t="str">
         <f t="shared" si="1"/>
         <v>d-dis-walkweb01-disk02</v>
       </c>
-      <c r="K11" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="L11" s="89">
-        <v>64</v>
-      </c>
-      <c r="M11" s="89">
-        <v>1</v>
-      </c>
-      <c r="N11" s="89" t="s">
+      <c r="K11" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="L11" s="88">
+        <v>64</v>
+      </c>
+      <c r="M11" s="88">
+        <v>1</v>
+      </c>
+      <c r="N11" s="88" t="s">
         <v>502</v>
       </c>
-      <c r="O11" s="89" t="s">
-        <v>173</v>
-      </c>
-      <c r="P11" s="89" t="s">
+      <c r="O11" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="P11" s="88" t="s">
         <v>499</v>
       </c>
-      <c r="Q11" s="89" t="b">
+      <c r="Q11" s="88" t="b">
         <v>1</v>
       </c>
       <c r="R11" s="56"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A12" s="95"/>
-      <c r="B12" s="88" t="s">
+      <c r="A12" s="94"/>
+      <c r="B12" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="88"/>
-      <c r="D12" s="88" t="s">
+      <c r="C12" s="87" t="str" cm="1">
+        <f t="array" ref="C12">UPPER(INDEX(_xlfn.TEXTSPLIT($D12, "-"), 3))</f>
+        <v>DIS</v>
+      </c>
+      <c r="D12" s="87" t="s">
         <v>310</v>
       </c>
-      <c r="E12" s="94" t="s">
+      <c r="E12" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="F12" s="88" t="s">
+      <c r="F12" s="87" t="s">
         <v>339</v>
       </c>
-      <c r="G12" s="88" t="str">
+      <c r="G12" s="87" t="str">
         <f t="shared" si="0"/>
         <v>d-dis-drvmsgap01-disk01</v>
       </c>
-      <c r="H12" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="I12" s="88">
-        <v>64</v>
-      </c>
-      <c r="J12" s="88" t="str">
+      <c r="H12" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="I12" s="87">
+        <v>64</v>
+      </c>
+      <c r="J12" s="87" t="str">
         <f t="shared" si="1"/>
         <v>d-dis-drvmsgap01-disk02</v>
       </c>
-      <c r="K12" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="L12" s="88">
-        <v>64</v>
-      </c>
-      <c r="M12" s="88">
-        <v>1</v>
-      </c>
-      <c r="N12" s="88" t="s">
+      <c r="K12" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="L12" s="87">
+        <v>64</v>
+      </c>
+      <c r="M12" s="87">
+        <v>1</v>
+      </c>
+      <c r="N12" s="87" t="s">
         <v>502</v>
       </c>
-      <c r="O12" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="P12" s="88" t="s">
+      <c r="O12" s="87" t="s">
+        <v>173</v>
+      </c>
+      <c r="P12" s="87" t="s">
         <v>499</v>
       </c>
-      <c r="Q12" s="88" t="b">
-        <v>1</v>
-      </c>
-      <c r="R12" s="86"/>
+      <c r="Q12" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="R12" s="85"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" s="103"/>
-      <c r="B13" s="89" t="s">
+      <c r="A13" s="92"/>
+      <c r="B13" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C13" s="89" t="str" cm="1">
+      <c r="C13" s="88" t="str" cm="1">
         <f t="array" ref="C13">UPPER(INDEX(_xlfn.TEXTSPLIT($D13, "-"), 3))</f>
         <v>DIS</v>
       </c>
-      <c r="D13" s="89" t="s">
+      <c r="D13" s="88" t="s">
         <v>310</v>
       </c>
-      <c r="E13" s="96" t="s">
+      <c r="E13" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="89" t="s">
+      <c r="F13" s="88" t="s">
         <v>341</v>
       </c>
-      <c r="G13" s="89" t="str">
+      <c r="G13" s="88" t="str">
         <f t="shared" si="0"/>
         <v>d-dis-web01-disk01</v>
       </c>
-      <c r="H13" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="I13" s="89">
-        <v>64</v>
-      </c>
-      <c r="J13" s="89" t="str">
+      <c r="H13" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="I13" s="88">
+        <v>64</v>
+      </c>
+      <c r="J13" s="88" t="str">
         <f t="shared" si="1"/>
         <v>d-dis-web01-disk02</v>
       </c>
-      <c r="K13" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="L13" s="89">
-        <v>64</v>
-      </c>
-      <c r="M13" s="89">
-        <v>1</v>
-      </c>
-      <c r="N13" s="89" t="s">
+      <c r="K13" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="L13" s="88">
+        <v>64</v>
+      </c>
+      <c r="M13" s="88">
+        <v>1</v>
+      </c>
+      <c r="N13" s="88" t="s">
         <v>502</v>
       </c>
-      <c r="O13" s="89" t="s">
-        <v>173</v>
-      </c>
-      <c r="P13" s="89" t="s">
+      <c r="O13" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="P13" s="88" t="s">
         <v>499</v>
       </c>
-      <c r="Q13" s="89" t="b">
+      <c r="Q13" s="88" t="b">
         <v>1</v>
       </c>
       <c r="R13" s="56"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A14" s="102"/>
-      <c r="B14" s="88" t="s">
+      <c r="A14" s="94"/>
+      <c r="B14" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C14" s="88" t="str" cm="1">
+      <c r="C14" s="87" t="str" cm="1">
         <f t="array" ref="C14">UPPER(INDEX(_xlfn.TEXTSPLIT($D14, "-"), 3))</f>
         <v>DIS</v>
       </c>
-      <c r="D14" s="88" t="s">
+      <c r="D14" s="87" t="s">
         <v>310</v>
       </c>
-      <c r="E14" s="94" t="s">
+      <c r="E14" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="88" t="s">
+      <c r="F14" s="87" t="s">
         <v>343</v>
       </c>
-      <c r="G14" s="88" t="str">
+      <c r="G14" s="87" t="str">
         <f t="shared" si="0"/>
         <v>d-dis-cmsadm01-disk01</v>
       </c>
-      <c r="H14" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="I14" s="88">
-        <v>64</v>
-      </c>
-      <c r="J14" s="88" t="str">
+      <c r="H14" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="I14" s="87">
+        <v>64</v>
+      </c>
+      <c r="J14" s="87" t="str">
         <f t="shared" si="1"/>
         <v>d-dis-cmsadm01-disk02</v>
       </c>
-      <c r="K14" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="L14" s="88">
-        <v>64</v>
-      </c>
-      <c r="M14" s="88">
-        <v>1</v>
-      </c>
-      <c r="N14" s="88" t="s">
+      <c r="K14" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="L14" s="87">
+        <v>64</v>
+      </c>
+      <c r="M14" s="87">
+        <v>1</v>
+      </c>
+      <c r="N14" s="87" t="s">
         <v>502</v>
       </c>
-      <c r="O14" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="P14" s="88" t="s">
+      <c r="O14" s="87" t="s">
+        <v>173</v>
+      </c>
+      <c r="P14" s="87" t="s">
         <v>499</v>
       </c>
-      <c r="Q14" s="88" t="b">
-        <v>1</v>
-      </c>
-      <c r="R14" s="86"/>
+      <c r="Q14" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="R14" s="85"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A15" s="93"/>
-      <c r="B15" s="89" t="s">
+      <c r="A15" s="92"/>
+      <c r="B15" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C15" s="89"/>
-      <c r="D15" s="89" t="s">
+      <c r="C15" s="88" t="str" cm="1">
+        <f t="array" ref="C15">UPPER(INDEX(_xlfn.TEXTSPLIT($D15, "-"), 3))</f>
+        <v>DIS</v>
+      </c>
+      <c r="D15" s="88" t="s">
         <v>310</v>
       </c>
-      <c r="E15" s="96" t="s">
+      <c r="E15" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="F15" s="89" t="s">
+      <c r="F15" s="88" t="s">
         <v>345</v>
       </c>
-      <c r="G15" s="89" t="str">
+      <c r="G15" s="88" t="str">
         <f t="shared" si="0"/>
         <v>d-dis-cmsap01-disk01</v>
       </c>
-      <c r="H15" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="I15" s="89">
-        <v>64</v>
-      </c>
-      <c r="J15" s="89" t="str">
+      <c r="H15" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="I15" s="88">
+        <v>64</v>
+      </c>
+      <c r="J15" s="88" t="str">
         <f t="shared" si="1"/>
         <v>d-dis-cmsap01-disk02</v>
       </c>
-      <c r="K15" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="L15" s="89">
-        <v>64</v>
-      </c>
-      <c r="M15" s="89">
-        <v>1</v>
-      </c>
-      <c r="N15" s="89" t="s">
+      <c r="K15" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="L15" s="88">
+        <v>64</v>
+      </c>
+      <c r="M15" s="88">
+        <v>1</v>
+      </c>
+      <c r="N15" s="88" t="s">
         <v>502</v>
       </c>
-      <c r="O15" s="89" t="s">
-        <v>173</v>
-      </c>
-      <c r="P15" s="89" t="s">
+      <c r="O15" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="P15" s="88" t="s">
         <v>499</v>
       </c>
-      <c r="Q15" s="89" t="b">
+      <c r="Q15" s="88" t="b">
         <v>1</v>
       </c>
       <c r="R15" s="56"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A16" s="102"/>
-      <c r="B16" s="88" t="s">
+      <c r="A16" s="94"/>
+      <c r="B16" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C16" s="88" t="str" cm="1">
+      <c r="C16" s="87" t="str" cm="1">
         <f t="array" ref="C16">UPPER(INDEX(_xlfn.TEXTSPLIT($D16, "-"), 3))</f>
         <v>DIS</v>
       </c>
-      <c r="D16" s="88" t="s">
+      <c r="D16" s="87" t="s">
         <v>310</v>
       </c>
-      <c r="E16" s="94" t="s">
+      <c r="E16" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="F16" s="88" t="s">
+      <c r="F16" s="87" t="s">
         <v>347</v>
       </c>
-      <c r="G16" s="88" t="str">
+      <c r="G16" s="87" t="str">
         <f t="shared" si="0"/>
         <v>d-dis-cmsweb01-disk01</v>
       </c>
-      <c r="H16" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="I16" s="88">
-        <v>64</v>
-      </c>
-      <c r="J16" s="88" t="str">
+      <c r="H16" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="I16" s="87">
+        <v>64</v>
+      </c>
+      <c r="J16" s="87" t="str">
         <f t="shared" si="1"/>
         <v>d-dis-cmsweb01-disk02</v>
       </c>
-      <c r="K16" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="L16" s="88">
-        <v>64</v>
-      </c>
-      <c r="M16" s="88">
-        <v>1</v>
-      </c>
-      <c r="N16" s="88" t="s">
+      <c r="K16" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="L16" s="87">
+        <v>64</v>
+      </c>
+      <c r="M16" s="87">
+        <v>1</v>
+      </c>
+      <c r="N16" s="87" t="s">
         <v>502</v>
       </c>
-      <c r="O16" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="P16" s="88" t="s">
+      <c r="O16" s="87" t="s">
+        <v>173</v>
+      </c>
+      <c r="P16" s="87" t="s">
         <v>499</v>
       </c>
-      <c r="Q16" s="88" t="b">
-        <v>1</v>
-      </c>
-      <c r="R16" s="86"/>
+      <c r="Q16" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="R16" s="85"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A17" s="93"/>
-      <c r="B17" s="89" t="s">
+      <c r="A17" s="92"/>
+      <c r="B17" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C17" s="89"/>
-      <c r="D17" s="89" t="s">
+      <c r="C17" s="88" t="str" cm="1">
+        <f t="array" ref="C17">UPPER(INDEX(_xlfn.TEXTSPLIT($D17, "-"), 3))</f>
+        <v>DIS</v>
+      </c>
+      <c r="D17" s="88" t="s">
         <v>310</v>
       </c>
-      <c r="E17" s="96" t="s">
+      <c r="E17" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="89" t="s">
+      <c r="F17" s="88" t="s">
         <v>349</v>
       </c>
-      <c r="G17" s="89" t="str">
+      <c r="G17" s="88" t="str">
         <f t="shared" si="0"/>
         <v>d-dis-cmbsap01-disk01</v>
       </c>
-      <c r="H17" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="I17" s="89">
-        <v>64</v>
-      </c>
-      <c r="J17" s="89" t="str">
+      <c r="H17" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="I17" s="88">
+        <v>64</v>
+      </c>
+      <c r="J17" s="88" t="str">
         <f t="shared" si="1"/>
         <v>d-dis-cmbsap01-disk02</v>
       </c>
-      <c r="K17" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="L17" s="89">
-        <v>64</v>
-      </c>
-      <c r="M17" s="89">
-        <v>1</v>
-      </c>
-      <c r="N17" s="89" t="s">
+      <c r="K17" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="L17" s="88">
+        <v>64</v>
+      </c>
+      <c r="M17" s="88">
+        <v>1</v>
+      </c>
+      <c r="N17" s="88" t="s">
         <v>502</v>
       </c>
-      <c r="O17" s="89" t="s">
-        <v>173</v>
-      </c>
-      <c r="P17" s="89" t="s">
+      <c r="O17" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="P17" s="88" t="s">
         <v>499</v>
       </c>
-      <c r="Q17" s="89" t="b">
+      <c r="Q17" s="88" t="b">
         <v>1</v>
       </c>
       <c r="R17" s="56"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A18" s="93"/>
-      <c r="B18" s="88" t="s">
+      <c r="A18" s="92"/>
+      <c r="B18" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C18" s="88"/>
-      <c r="D18" s="88" t="s">
+      <c r="C18" s="87" t="str" cm="1">
+        <f t="array" ref="C18">UPPER(INDEX(_xlfn.TEXTSPLIT($D18, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="D18" s="87" t="s">
         <v>351</v>
       </c>
-      <c r="E18" s="94" t="s">
+      <c r="E18" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="F18" s="88" t="s">
+      <c r="F18" s="87" t="s">
         <v>352</v>
       </c>
-      <c r="G18" s="88" t="str">
+      <c r="G18" s="87" t="str">
         <f t="shared" si="0"/>
         <v>d-dtg-ingap01-disk01</v>
       </c>
-      <c r="H18" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="I18" s="88">
-        <v>64</v>
-      </c>
-      <c r="J18" s="88" t="str">
+      <c r="H18" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="I18" s="87">
+        <v>64</v>
+      </c>
+      <c r="J18" s="87" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-ingap01-disk02</v>
       </c>
-      <c r="K18" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="L18" s="88">
-        <v>64</v>
-      </c>
-      <c r="M18" s="88">
-        <v>1</v>
-      </c>
-      <c r="N18" s="88" t="s">
+      <c r="K18" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="L18" s="87">
+        <v>64</v>
+      </c>
+      <c r="M18" s="87">
+        <v>1</v>
+      </c>
+      <c r="N18" s="87" t="s">
         <v>502</v>
       </c>
-      <c r="O18" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="P18" s="88" t="s">
+      <c r="O18" s="87" t="s">
+        <v>173</v>
+      </c>
+      <c r="P18" s="87" t="s">
         <v>499</v>
       </c>
-      <c r="Q18" s="88" t="b">
-        <v>1</v>
-      </c>
-      <c r="R18" s="86"/>
+      <c r="Q18" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="R18" s="85"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A19" s="95"/>
-      <c r="B19" s="89" t="s">
+      <c r="A19" s="94"/>
+      <c r="B19" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C19" s="89"/>
-      <c r="D19" s="89" t="s">
+      <c r="C19" s="88" t="str" cm="1">
+        <f t="array" ref="C19">UPPER(INDEX(_xlfn.TEXTSPLIT($D19, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="D19" s="88" t="s">
         <v>351</v>
       </c>
-      <c r="E19" s="96" t="s">
+      <c r="E19" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="F19" s="89" t="s">
+      <c r="F19" s="88" t="s">
         <v>355</v>
       </c>
-      <c r="G19" s="89" t="str">
+      <c r="G19" s="88" t="str">
         <f t="shared" si="0"/>
         <v>d-dtg-ap01-disk01</v>
       </c>
-      <c r="H19" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="I19" s="89">
-        <v>64</v>
-      </c>
-      <c r="J19" s="89" t="str">
+      <c r="H19" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="I19" s="88">
+        <v>64</v>
+      </c>
+      <c r="J19" s="88" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-ap01-disk02</v>
       </c>
-      <c r="K19" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="L19" s="89">
-        <v>64</v>
-      </c>
-      <c r="M19" s="89">
-        <v>1</v>
-      </c>
-      <c r="N19" s="89" t="s">
+      <c r="K19" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="L19" s="88">
+        <v>64</v>
+      </c>
+      <c r="M19" s="88">
+        <v>1</v>
+      </c>
+      <c r="N19" s="88" t="s">
         <v>502</v>
       </c>
-      <c r="O19" s="89" t="s">
-        <v>173</v>
-      </c>
-      <c r="P19" s="89" t="s">
+      <c r="O19" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="P19" s="88" t="s">
         <v>499</v>
       </c>
-      <c r="Q19" s="89" t="b">
+      <c r="Q19" s="88" t="b">
         <v>1</v>
       </c>
       <c r="R19" s="56"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A20" s="93"/>
-      <c r="B20" s="88" t="s">
+      <c r="A20" s="92"/>
+      <c r="B20" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C20" s="88"/>
-      <c r="D20" s="88" t="s">
+      <c r="C20" s="87" t="str" cm="1">
+        <f t="array" ref="C20">UPPER(INDEX(_xlfn.TEXTSPLIT($D20, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="D20" s="87" t="s">
         <v>351</v>
       </c>
-      <c r="E20" s="94" t="s">
+      <c r="E20" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="F20" s="88" t="s">
+      <c r="F20" s="87" t="s">
         <v>357</v>
       </c>
-      <c r="G20" s="88" t="str">
+      <c r="G20" s="87" t="str">
         <f t="shared" si="0"/>
         <v>d-dtg-extgeoap01-disk01</v>
       </c>
-      <c r="H20" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="I20" s="88">
-        <v>64</v>
-      </c>
-      <c r="J20" s="88" t="str">
+      <c r="H20" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="I20" s="87">
+        <v>64</v>
+      </c>
+      <c r="J20" s="87" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-extgeoap01-disk02</v>
       </c>
-      <c r="K20" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="L20" s="88">
-        <v>64</v>
-      </c>
-      <c r="M20" s="88">
-        <v>1</v>
-      </c>
-      <c r="N20" s="88" t="s">
+      <c r="K20" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="L20" s="87">
+        <v>64</v>
+      </c>
+      <c r="M20" s="87">
+        <v>1</v>
+      </c>
+      <c r="N20" s="87" t="s">
         <v>502</v>
       </c>
-      <c r="O20" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="P20" s="88" t="s">
+      <c r="O20" s="87" t="s">
+        <v>173</v>
+      </c>
+      <c r="P20" s="87" t="s">
         <v>499</v>
       </c>
-      <c r="Q20" s="88" t="b">
-        <v>1</v>
-      </c>
-      <c r="R20" s="86"/>
+      <c r="Q20" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="R20" s="85"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A21" s="95"/>
-      <c r="B21" s="89" t="s">
+      <c r="A21" s="94"/>
+      <c r="B21" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C21" s="89"/>
-      <c r="D21" s="89" t="s">
+      <c r="C21" s="88" t="str" cm="1">
+        <f t="array" ref="C21">UPPER(INDEX(_xlfn.TEXTSPLIT($D21, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="D21" s="88" t="s">
         <v>351</v>
       </c>
-      <c r="E21" s="96" t="s">
+      <c r="E21" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="F21" s="89" t="s">
+      <c r="F21" s="88" t="s">
         <v>359</v>
       </c>
-      <c r="G21" s="89" t="str">
+      <c r="G21" s="88" t="str">
         <f t="shared" si="0"/>
         <v>d-dtg-geoap01-disk01</v>
       </c>
-      <c r="H21" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="I21" s="89">
-        <v>64</v>
-      </c>
-      <c r="J21" s="89" t="str">
+      <c r="H21" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="I21" s="88">
+        <v>64</v>
+      </c>
+      <c r="J21" s="88" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-geoap01-disk02</v>
       </c>
-      <c r="K21" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="L21" s="89">
-        <v>64</v>
-      </c>
-      <c r="M21" s="89">
-        <v>1</v>
-      </c>
-      <c r="N21" s="89" t="s">
+      <c r="K21" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="L21" s="88">
+        <v>64</v>
+      </c>
+      <c r="M21" s="88">
+        <v>1</v>
+      </c>
+      <c r="N21" s="88" t="s">
         <v>502</v>
       </c>
-      <c r="O21" s="89" t="s">
-        <v>173</v>
-      </c>
-      <c r="P21" s="89" t="s">
+      <c r="O21" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="P21" s="88" t="s">
         <v>499</v>
       </c>
-      <c r="Q21" s="89" t="b">
+      <c r="Q21" s="88" t="b">
         <v>1</v>
       </c>
       <c r="R21" s="56"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A22" s="93"/>
-      <c r="B22" s="88" t="s">
+      <c r="A22" s="92"/>
+      <c r="B22" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C22" s="88"/>
-      <c r="D22" s="88" t="s">
+      <c r="C22" s="87" t="str" cm="1">
+        <f t="array" ref="C22">UPPER(INDEX(_xlfn.TEXTSPLIT($D22, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="D22" s="87" t="s">
         <v>351</v>
       </c>
-      <c r="E22" s="94" t="s">
+      <c r="E22" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="F22" s="88" t="s">
+      <c r="F22" s="87" t="s">
         <v>361</v>
       </c>
-      <c r="G22" s="88" t="str">
+      <c r="G22" s="87" t="str">
         <f t="shared" si="0"/>
         <v>d-dtg-mq01-disk01</v>
       </c>
-      <c r="H22" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="I22" s="88">
-        <v>64</v>
-      </c>
-      <c r="J22" s="88" t="str">
+      <c r="H22" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="I22" s="87">
+        <v>64</v>
+      </c>
+      <c r="J22" s="87" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-mq01-disk02</v>
       </c>
-      <c r="K22" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="L22" s="88">
-        <v>64</v>
-      </c>
-      <c r="M22" s="88">
-        <v>1</v>
-      </c>
-      <c r="N22" s="88" t="s">
+      <c r="K22" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="L22" s="87">
+        <v>64</v>
+      </c>
+      <c r="M22" s="87">
+        <v>1</v>
+      </c>
+      <c r="N22" s="87" t="s">
         <v>502</v>
       </c>
-      <c r="O22" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="P22" s="88" t="s">
+      <c r="O22" s="87" t="s">
+        <v>173</v>
+      </c>
+      <c r="P22" s="87" t="s">
         <v>499</v>
       </c>
-      <c r="Q22" s="88" t="b">
-        <v>1</v>
-      </c>
-      <c r="R22" s="86"/>
+      <c r="Q22" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="R22" s="85"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A23" s="102"/>
-      <c r="B23" s="89" t="s">
+      <c r="A23" s="94"/>
+      <c r="B23" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C23" s="89" t="str" cm="1">
+      <c r="C23" s="88" t="str" cm="1">
         <f t="array" ref="C23">UPPER(INDEX(_xlfn.TEXTSPLIT($D23, "-"), 3))</f>
         <v>DTG</v>
       </c>
-      <c r="D23" s="89" t="s">
+      <c r="D23" s="88" t="s">
         <v>351</v>
       </c>
-      <c r="E23" s="96" t="s">
+      <c r="E23" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="F23" s="89" t="s">
+      <c r="F23" s="88" t="s">
         <v>364</v>
       </c>
-      <c r="G23" s="89" t="str">
+      <c r="G23" s="88" t="str">
         <f t="shared" si="0"/>
         <v>d-dtg-admweb01-disk01</v>
       </c>
-      <c r="H23" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="I23" s="89">
-        <v>64</v>
-      </c>
-      <c r="J23" s="89" t="str">
+      <c r="H23" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="I23" s="88">
+        <v>64</v>
+      </c>
+      <c r="J23" s="88" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-admweb01-disk02</v>
       </c>
-      <c r="K23" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="L23" s="89">
-        <v>64</v>
-      </c>
-      <c r="M23" s="89">
-        <v>1</v>
-      </c>
-      <c r="N23" s="89" t="s">
+      <c r="K23" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="L23" s="88">
+        <v>64</v>
+      </c>
+      <c r="M23" s="88">
+        <v>1</v>
+      </c>
+      <c r="N23" s="88" t="s">
         <v>502</v>
       </c>
-      <c r="O23" s="89" t="s">
-        <v>173</v>
-      </c>
-      <c r="P23" s="89" t="s">
+      <c r="O23" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="P23" s="88" t="s">
         <v>499</v>
       </c>
-      <c r="Q23" s="89" t="b">
+      <c r="Q23" s="88" t="b">
         <v>1</v>
       </c>
       <c r="R23" s="56"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A24" s="103"/>
-      <c r="B24" s="88" t="s">
+      <c r="A24" s="92"/>
+      <c r="B24" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C24" s="88" t="str" cm="1">
+      <c r="C24" s="87" t="str" cm="1">
         <f t="array" ref="C24">UPPER(INDEX(_xlfn.TEXTSPLIT($D24, "-"), 3))</f>
         <v>DTG</v>
       </c>
-      <c r="D24" s="88" t="s">
+      <c r="D24" s="87" t="s">
         <v>351</v>
       </c>
-      <c r="E24" s="94" t="s">
+      <c r="E24" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="F24" s="88" t="s">
+      <c r="F24" s="87" t="s">
         <v>366</v>
       </c>
-      <c r="G24" s="88" t="str">
+      <c r="G24" s="87" t="str">
         <f t="shared" si="0"/>
         <v>d-dtg-admap01-disk01</v>
       </c>
-      <c r="H24" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="I24" s="88">
-        <v>64</v>
-      </c>
-      <c r="J24" s="88" t="str">
+      <c r="H24" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="I24" s="87">
+        <v>64</v>
+      </c>
+      <c r="J24" s="87" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-admap01-disk02</v>
       </c>
-      <c r="K24" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="L24" s="88">
-        <v>64</v>
-      </c>
-      <c r="M24" s="88">
-        <v>1</v>
-      </c>
-      <c r="N24" s="88" t="s">
+      <c r="K24" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="L24" s="87">
+        <v>64</v>
+      </c>
+      <c r="M24" s="87">
+        <v>1</v>
+      </c>
+      <c r="N24" s="87" t="s">
         <v>502</v>
       </c>
-      <c r="O24" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="P24" s="88" t="s">
+      <c r="O24" s="87" t="s">
+        <v>173</v>
+      </c>
+      <c r="P24" s="87" t="s">
         <v>499</v>
       </c>
-      <c r="Q24" s="88" t="b">
-        <v>1</v>
-      </c>
-      <c r="R24" s="86"/>
+      <c r="Q24" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="R24" s="85"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A25" s="95"/>
-      <c r="B25" s="89" t="s">
+      <c r="A25" s="94"/>
+      <c r="B25" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C25" s="89"/>
-      <c r="D25" s="89" t="s">
+      <c r="C25" s="88" t="str" cm="1">
+        <f t="array" ref="C25">UPPER(INDEX(_xlfn.TEXTSPLIT($D25, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="D25" s="88" t="s">
         <v>351</v>
       </c>
-      <c r="E25" s="96" t="s">
+      <c r="E25" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="F25" s="89" t="s">
+      <c r="F25" s="88" t="s">
         <v>368</v>
       </c>
-      <c r="G25" s="89" t="str">
+      <c r="G25" s="88" t="str">
         <f t="shared" si="0"/>
         <v>d-dtg-dtoms01-disk01</v>
       </c>
-      <c r="H25" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="I25" s="89">
-        <v>64</v>
-      </c>
-      <c r="J25" s="89" t="str">
+      <c r="H25" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="I25" s="88">
+        <v>64</v>
+      </c>
+      <c r="J25" s="88" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-dtoms01-disk02</v>
       </c>
-      <c r="K25" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="L25" s="89">
-        <v>64</v>
-      </c>
-      <c r="M25" s="89">
-        <v>1</v>
-      </c>
-      <c r="N25" s="89" t="s">
+      <c r="K25" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="L25" s="88">
+        <v>64</v>
+      </c>
+      <c r="M25" s="88">
+        <v>1</v>
+      </c>
+      <c r="N25" s="88" t="s">
         <v>502</v>
       </c>
-      <c r="O25" s="89" t="s">
-        <v>173</v>
-      </c>
-      <c r="P25" s="89" t="s">
+      <c r="O25" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="P25" s="88" t="s">
         <v>499</v>
       </c>
-      <c r="Q25" s="89" t="b">
+      <c r="Q25" s="88" t="b">
         <v>1</v>
       </c>
       <c r="R25" s="56"/>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A26" s="93"/>
-      <c r="B26" s="88" t="s">
+      <c r="A26" s="92"/>
+      <c r="B26" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C26" s="88"/>
-      <c r="D26" s="88" t="s">
+      <c r="C26" s="87" t="str" cm="1">
+        <f t="array" ref="C26">UPPER(INDEX(_xlfn.TEXTSPLIT($D26, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="D26" s="87" t="s">
         <v>351</v>
       </c>
-      <c r="E26" s="94" t="s">
+      <c r="E26" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="F26" s="88" t="s">
+      <c r="F26" s="87" t="s">
         <v>370</v>
       </c>
-      <c r="G26" s="88" t="str">
+      <c r="G26" s="87" t="str">
         <f t="shared" si="0"/>
         <v>d-dtg-tsdb01-disk01</v>
       </c>
-      <c r="H26" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="I26" s="88">
+      <c r="H26" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="I26" s="87">
         <v>256</v>
       </c>
-      <c r="J26" s="88" t="str">
+      <c r="J26" s="87" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-tsdb01-disk02</v>
       </c>
-      <c r="K26" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="L26" s="88">
+      <c r="K26" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="L26" s="87">
         <v>256</v>
       </c>
-      <c r="M26" s="88">
-        <v>1</v>
-      </c>
-      <c r="N26" s="88" t="s">
+      <c r="M26" s="87">
+        <v>1</v>
+      </c>
+      <c r="N26" s="87" t="s">
         <v>502</v>
       </c>
-      <c r="O26" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="P26" s="88" t="s">
+      <c r="O26" s="87" t="s">
+        <v>173</v>
+      </c>
+      <c r="P26" s="87" t="s">
         <v>499</v>
       </c>
-      <c r="Q26" s="88" t="b">
-        <v>1</v>
-      </c>
-      <c r="R26" s="86"/>
+      <c r="Q26" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="R26" s="85"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A27" s="103"/>
-      <c r="B27" s="89" t="s">
+      <c r="A27" s="92"/>
+      <c r="B27" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C27" s="89" t="str" cm="1">
+      <c r="C27" s="88" t="str" cm="1">
         <f t="array" ref="C27">UPPER(INDEX(_xlfn.TEXTSPLIT($D27, "-"), 3))</f>
         <v>DTG</v>
       </c>
-      <c r="D27" s="89" t="s">
+      <c r="D27" s="88" t="s">
         <v>351</v>
       </c>
-      <c r="E27" s="96" t="s">
+      <c r="E27" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="F27" s="89" t="s">
+      <c r="F27" s="88" t="s">
         <v>374</v>
       </c>
-      <c r="G27" s="89" t="str">
+      <c r="G27" s="88" t="str">
         <f t="shared" si="0"/>
         <v>d-dtg-web01-disk01</v>
       </c>
-      <c r="H27" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="I27" s="89">
-        <v>64</v>
-      </c>
-      <c r="J27" s="89" t="str">
+      <c r="H27" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="I27" s="88">
+        <v>64</v>
+      </c>
+      <c r="J27" s="88" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-web01-disk02</v>
       </c>
-      <c r="K27" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="L27" s="89">
-        <v>64</v>
-      </c>
-      <c r="M27" s="89">
-        <v>1</v>
-      </c>
-      <c r="N27" s="89" t="s">
+      <c r="K27" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="L27" s="88">
+        <v>64</v>
+      </c>
+      <c r="M27" s="88">
+        <v>1</v>
+      </c>
+      <c r="N27" s="88" t="s">
         <v>502</v>
       </c>
-      <c r="O27" s="89" t="s">
-        <v>173</v>
-      </c>
-      <c r="P27" s="89" t="s">
+      <c r="O27" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="P27" s="88" t="s">
         <v>499</v>
       </c>
-      <c r="Q27" s="89" t="b">
+      <c r="Q27" s="88" t="b">
         <v>1</v>
       </c>
       <c r="R27" s="56"/>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A28" s="95"/>
-      <c r="B28" s="88" t="s">
+      <c r="A28" s="94"/>
+      <c r="B28" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C28" s="88"/>
-      <c r="D28" s="88" t="s">
+      <c r="C28" s="87" t="str" cm="1">
+        <f t="array" ref="C28">UPPER(INDEX(_xlfn.TEXTSPLIT($D28, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="D28" s="87" t="s">
         <v>351</v>
       </c>
-      <c r="E28" s="94" t="s">
+      <c r="E28" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="F28" s="88" t="s">
+      <c r="F28" s="87" t="s">
         <v>376</v>
       </c>
-      <c r="G28" s="88" t="str">
+      <c r="G28" s="87" t="str">
         <f t="shared" si="0"/>
         <v>d-dtg-zkp01-disk01</v>
       </c>
-      <c r="H28" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="I28" s="88">
-        <v>64</v>
-      </c>
-      <c r="J28" s="88" t="str">
+      <c r="H28" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="I28" s="87">
+        <v>64</v>
+      </c>
+      <c r="J28" s="87" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-zkp01-disk02</v>
       </c>
-      <c r="K28" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="L28" s="88">
-        <v>64</v>
-      </c>
-      <c r="M28" s="88">
-        <v>1</v>
-      </c>
-      <c r="N28" s="88" t="s">
+      <c r="K28" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="L28" s="87">
+        <v>64</v>
+      </c>
+      <c r="M28" s="87">
+        <v>1</v>
+      </c>
+      <c r="N28" s="87" t="s">
         <v>502</v>
       </c>
-      <c r="O28" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="P28" s="88" t="s">
+      <c r="O28" s="87" t="s">
+        <v>173</v>
+      </c>
+      <c r="P28" s="87" t="s">
         <v>499</v>
       </c>
-      <c r="Q28" s="88" t="b">
-        <v>1</v>
-      </c>
-      <c r="R28" s="86"/>
+      <c r="Q28" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="R28" s="85"/>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A29" s="93"/>
-      <c r="B29" s="89" t="s">
+      <c r="A29" s="92"/>
+      <c r="B29" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C29" s="89"/>
-      <c r="D29" s="89" t="s">
+      <c r="C29" s="88" t="str" cm="1">
+        <f t="array" ref="C29">UPPER(INDEX(_xlfn.TEXTSPLIT($D29, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="D29" s="88" t="s">
         <v>351</v>
       </c>
-      <c r="E29" s="96" t="s">
+      <c r="E29" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="F29" s="89" t="s">
+      <c r="F29" s="88" t="s">
         <v>378</v>
       </c>
-      <c r="G29" s="89" t="str">
+      <c r="G29" s="88" t="str">
         <f t="shared" si="0"/>
         <v>d-dtg-zkp02-disk01</v>
       </c>
-      <c r="H29" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="I29" s="89">
-        <v>64</v>
-      </c>
-      <c r="J29" s="89" t="str">
+      <c r="H29" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="I29" s="88">
+        <v>64</v>
+      </c>
+      <c r="J29" s="88" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-zkp02-disk02</v>
       </c>
-      <c r="K29" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="L29" s="89">
-        <v>64</v>
-      </c>
-      <c r="M29" s="89">
-        <v>1</v>
-      </c>
-      <c r="N29" s="89" t="s">
+      <c r="K29" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="L29" s="88">
+        <v>64</v>
+      </c>
+      <c r="M29" s="88">
+        <v>1</v>
+      </c>
+      <c r="N29" s="88" t="s">
         <v>502</v>
       </c>
-      <c r="O29" s="89" t="s">
-        <v>173</v>
-      </c>
-      <c r="P29" s="89" t="s">
+      <c r="O29" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="P29" s="88" t="s">
         <v>499</v>
       </c>
-      <c r="Q29" s="89" t="b">
+      <c r="Q29" s="88" t="b">
         <v>1</v>
       </c>
       <c r="R29" s="56"/>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A30" s="95"/>
-      <c r="B30" s="88" t="s">
+      <c r="A30" s="94"/>
+      <c r="B30" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C30" s="88"/>
-      <c r="D30" s="88" t="s">
+      <c r="C30" s="87" t="str" cm="1">
+        <f t="array" ref="C30">UPPER(INDEX(_xlfn.TEXTSPLIT($D30, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="D30" s="87" t="s">
         <v>351</v>
       </c>
-      <c r="E30" s="94" t="s">
+      <c r="E30" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="F30" s="88" t="s">
+      <c r="F30" s="87" t="s">
         <v>380</v>
       </c>
-      <c r="G30" s="88" t="str">
+      <c r="G30" s="87" t="str">
         <f t="shared" si="0"/>
         <v>d-dtg-zkp03-disk01</v>
       </c>
-      <c r="H30" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="I30" s="88">
-        <v>64</v>
-      </c>
-      <c r="J30" s="88" t="str">
+      <c r="H30" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="I30" s="87">
+        <v>64</v>
+      </c>
+      <c r="J30" s="87" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-zkp03-disk02</v>
       </c>
-      <c r="K30" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="L30" s="88">
-        <v>64</v>
-      </c>
-      <c r="M30" s="88">
-        <v>1</v>
-      </c>
-      <c r="N30" s="88" t="s">
+      <c r="K30" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="L30" s="87">
+        <v>64</v>
+      </c>
+      <c r="M30" s="87">
+        <v>1</v>
+      </c>
+      <c r="N30" s="87" t="s">
         <v>502</v>
       </c>
-      <c r="O30" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="P30" s="88" t="s">
+      <c r="O30" s="87" t="s">
+        <v>173</v>
+      </c>
+      <c r="P30" s="87" t="s">
         <v>499</v>
       </c>
-      <c r="Q30" s="88" t="b">
-        <v>1</v>
-      </c>
-      <c r="R30" s="86"/>
+      <c r="Q30" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="R30" s="85"/>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A31" s="93"/>
-      <c r="B31" s="89" t="s">
+      <c r="A31" s="92"/>
+      <c r="B31" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C31" s="89"/>
-      <c r="D31" s="89" t="s">
+      <c r="C31" s="88" t="str" cm="1">
+        <f t="array" ref="C31">UPPER(INDEX(_xlfn.TEXTSPLIT($D31, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="D31" s="88" t="s">
         <v>351</v>
       </c>
-      <c r="E31" s="96" t="s">
+      <c r="E31" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="F31" s="89" t="s">
+      <c r="F31" s="88" t="s">
         <v>382</v>
       </c>
-      <c r="G31" s="89" t="str">
+      <c r="G31" s="88" t="str">
         <f t="shared" si="0"/>
         <v>d-dtg-kfk01-disk01</v>
       </c>
-      <c r="H31" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="I31" s="89">
-        <v>64</v>
-      </c>
-      <c r="J31" s="89" t="str">
+      <c r="H31" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="I31" s="88">
+        <v>64</v>
+      </c>
+      <c r="J31" s="88" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-kfk01-disk02</v>
       </c>
-      <c r="K31" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="L31" s="89">
-        <v>64</v>
-      </c>
-      <c r="M31" s="89">
-        <v>1</v>
-      </c>
-      <c r="N31" s="89" t="s">
+      <c r="K31" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="L31" s="88">
+        <v>64</v>
+      </c>
+      <c r="M31" s="88">
+        <v>1</v>
+      </c>
+      <c r="N31" s="88" t="s">
         <v>502</v>
       </c>
-      <c r="O31" s="89" t="s">
-        <v>173</v>
-      </c>
-      <c r="P31" s="89" t="s">
+      <c r="O31" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="P31" s="88" t="s">
         <v>499</v>
       </c>
-      <c r="Q31" s="89" t="b">
+      <c r="Q31" s="88" t="b">
         <v>1</v>
       </c>
       <c r="R31" s="56"/>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A32" s="95"/>
-      <c r="B32" s="88" t="s">
+      <c r="A32" s="94"/>
+      <c r="B32" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C32" s="88"/>
-      <c r="D32" s="88" t="s">
+      <c r="C32" s="87" t="str" cm="1">
+        <f t="array" ref="C32">UPPER(INDEX(_xlfn.TEXTSPLIT($D32, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="D32" s="87" t="s">
         <v>351</v>
       </c>
-      <c r="E32" s="94" t="s">
+      <c r="E32" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="F32" s="88" t="s">
+      <c r="F32" s="87" t="s">
         <v>384</v>
       </c>
-      <c r="G32" s="88" t="str">
+      <c r="G32" s="87" t="str">
         <f t="shared" si="0"/>
         <v>d-dtg-kfk02-disk01</v>
       </c>
-      <c r="H32" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="I32" s="88">
-        <v>64</v>
-      </c>
-      <c r="J32" s="88" t="str">
+      <c r="H32" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="I32" s="87">
+        <v>64</v>
+      </c>
+      <c r="J32" s="87" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-kfk02-disk02</v>
       </c>
-      <c r="K32" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="L32" s="88">
-        <v>64</v>
-      </c>
-      <c r="M32" s="88">
-        <v>1</v>
-      </c>
-      <c r="N32" s="88" t="s">
+      <c r="K32" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="L32" s="87">
+        <v>64</v>
+      </c>
+      <c r="M32" s="87">
+        <v>1</v>
+      </c>
+      <c r="N32" s="87" t="s">
         <v>502</v>
       </c>
-      <c r="O32" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="P32" s="88" t="s">
+      <c r="O32" s="87" t="s">
+        <v>173</v>
+      </c>
+      <c r="P32" s="87" t="s">
         <v>499</v>
       </c>
-      <c r="Q32" s="88" t="b">
-        <v>1</v>
-      </c>
-      <c r="R32" s="86"/>
+      <c r="Q32" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="R32" s="85"/>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A33" s="93"/>
-      <c r="B33" s="89" t="s">
+      <c r="A33" s="92"/>
+      <c r="B33" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C33" s="89"/>
-      <c r="D33" s="89" t="s">
+      <c r="C33" s="88" t="str" cm="1">
+        <f t="array" ref="C33">UPPER(INDEX(_xlfn.TEXTSPLIT($D33, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="D33" s="88" t="s">
         <v>351</v>
       </c>
-      <c r="E33" s="96" t="s">
+      <c r="E33" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="F33" s="89" t="s">
+      <c r="F33" s="88" t="s">
         <v>386</v>
       </c>
-      <c r="G33" s="89" t="str">
+      <c r="G33" s="88" t="str">
         <f t="shared" si="0"/>
         <v>d-dtg-kfk03-disk01</v>
       </c>
-      <c r="H33" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="I33" s="89">
-        <v>64</v>
-      </c>
-      <c r="J33" s="89" t="str">
+      <c r="H33" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="I33" s="88">
+        <v>64</v>
+      </c>
+      <c r="J33" s="88" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-kfk03-disk02</v>
       </c>
-      <c r="K33" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="L33" s="89">
-        <v>64</v>
-      </c>
-      <c r="M33" s="89">
-        <v>1</v>
-      </c>
-      <c r="N33" s="89" t="s">
+      <c r="K33" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="L33" s="88">
+        <v>64</v>
+      </c>
+      <c r="M33" s="88">
+        <v>1</v>
+      </c>
+      <c r="N33" s="88" t="s">
         <v>502</v>
       </c>
-      <c r="O33" s="89" t="s">
-        <v>173</v>
-      </c>
-      <c r="P33" s="89" t="s">
+      <c r="O33" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="P33" s="88" t="s">
         <v>499</v>
       </c>
-      <c r="Q33" s="89" t="b">
+      <c r="Q33" s="88" t="b">
         <v>1</v>
       </c>
       <c r="R33" s="56"/>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A34" s="102"/>
-      <c r="B34" s="88" t="s">
+      <c r="A34" s="94"/>
+      <c r="B34" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C34" s="88" t="str" cm="1">
+      <c r="C34" s="87" t="str" cm="1">
         <f t="array" ref="C34">UPPER(INDEX(_xlfn.TEXTSPLIT($D34, "-"), 3))</f>
         <v>DTG</v>
       </c>
-      <c r="D34" s="88" t="s">
+      <c r="D34" s="87" t="s">
         <v>351</v>
       </c>
-      <c r="E34" s="94" t="s">
+      <c r="E34" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="F34" s="88" t="s">
+      <c r="F34" s="87" t="s">
         <v>388</v>
       </c>
-      <c r="G34" s="88" t="str">
+      <c r="G34" s="87" t="str">
         <f t="shared" si="0"/>
         <v>d-dtg-mdoms01-disk01</v>
       </c>
-      <c r="H34" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="I34" s="88">
-        <v>64</v>
-      </c>
-      <c r="J34" s="88" t="str">
+      <c r="H34" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="I34" s="87">
+        <v>64</v>
+      </c>
+      <c r="J34" s="87" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-mdoms01-disk02</v>
       </c>
-      <c r="K34" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="L34" s="88">
-        <v>64</v>
-      </c>
-      <c r="M34" s="88">
-        <v>1</v>
-      </c>
-      <c r="N34" s="88" t="s">
+      <c r="K34" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="L34" s="87">
+        <v>64</v>
+      </c>
+      <c r="M34" s="87">
+        <v>1</v>
+      </c>
+      <c r="N34" s="87" t="s">
         <v>502</v>
       </c>
-      <c r="O34" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="P34" s="88" t="s">
+      <c r="O34" s="87" t="s">
+        <v>173</v>
+      </c>
+      <c r="P34" s="87" t="s">
         <v>499</v>
       </c>
-      <c r="Q34" s="88" t="b">
-        <v>1</v>
-      </c>
-      <c r="R34" s="86"/>
+      <c r="Q34" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="R34" s="85"/>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A35" s="93"/>
-      <c r="B35" s="89" t="s">
+      <c r="A35" s="92"/>
+      <c r="B35" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C35" s="89"/>
-      <c r="D35" s="89" t="s">
+      <c r="C35" s="88" t="str" cm="1">
+        <f t="array" ref="C35">UPPER(INDEX(_xlfn.TEXTSPLIT($D35, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="D35" s="88" t="s">
         <v>351</v>
       </c>
-      <c r="E35" s="96" t="s">
+      <c r="E35" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="F35" s="89" t="s">
+      <c r="F35" s="88" t="s">
         <v>390</v>
       </c>
-      <c r="G35" s="89" t="str">
+      <c r="G35" s="88" t="str">
         <f t="shared" si="0"/>
         <v>d-dtg-cdmlap01-disk01</v>
       </c>
-      <c r="H35" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="I35" s="89">
-        <v>64</v>
-      </c>
-      <c r="J35" s="89" t="str">
+      <c r="H35" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="I35" s="88">
+        <v>64</v>
+      </c>
+      <c r="J35" s="88" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-cdmlap01-disk02</v>
       </c>
-      <c r="K35" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="L35" s="89">
-        <v>64</v>
-      </c>
-      <c r="M35" s="89">
-        <v>1</v>
-      </c>
-      <c r="N35" s="89" t="s">
+      <c r="K35" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="L35" s="88">
+        <v>64</v>
+      </c>
+      <c r="M35" s="88">
+        <v>1</v>
+      </c>
+      <c r="N35" s="88" t="s">
         <v>502</v>
       </c>
-      <c r="O35" s="89" t="s">
-        <v>173</v>
-      </c>
-      <c r="P35" s="89" t="s">
+      <c r="O35" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="P35" s="88" t="s">
         <v>499</v>
       </c>
-      <c r="Q35" s="89" t="b">
+      <c r="Q35" s="88" t="b">
         <v>1</v>
       </c>
       <c r="R35" s="56"/>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A36" s="93"/>
-      <c r="B36" s="88" t="s">
+      <c r="A36" s="92"/>
+      <c r="B36" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C36" s="88"/>
-      <c r="D36" s="88" t="s">
+      <c r="C36" s="87" t="str" cm="1">
+        <f t="array" ref="C36">UPPER(INDEX(_xlfn.TEXTSPLIT($D36, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="D36" s="87" t="s">
         <v>351</v>
       </c>
-      <c r="E36" s="94" t="s">
+      <c r="E36" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="F36" s="88" t="s">
+      <c r="F36" s="87" t="s">
         <v>392</v>
       </c>
-      <c r="G36" s="88" t="str">
+      <c r="G36" s="87" t="str">
         <f t="shared" si="0"/>
         <v>d-dtg-cdstap01-disk01</v>
       </c>
-      <c r="H36" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="I36" s="88">
-        <v>64</v>
-      </c>
-      <c r="J36" s="88" t="str">
+      <c r="H36" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="I36" s="87">
+        <v>64</v>
+      </c>
+      <c r="J36" s="87" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-cdstap01-disk02</v>
       </c>
-      <c r="K36" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="L36" s="88">
-        <v>64</v>
-      </c>
-      <c r="M36" s="88">
-        <v>1</v>
-      </c>
-      <c r="N36" s="88" t="s">
+      <c r="K36" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="L36" s="87">
+        <v>64</v>
+      </c>
+      <c r="M36" s="87">
+        <v>1</v>
+      </c>
+      <c r="N36" s="87" t="s">
         <v>502</v>
       </c>
-      <c r="O36" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="P36" s="88" t="s">
+      <c r="O36" s="87" t="s">
+        <v>173</v>
+      </c>
+      <c r="P36" s="87" t="s">
         <v>499</v>
       </c>
-      <c r="Q36" s="88" t="b">
-        <v>1</v>
-      </c>
-      <c r="R36" s="86"/>
+      <c r="Q36" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="R36" s="85"/>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A37" s="102"/>
-      <c r="B37" s="89" t="s">
+      <c r="A37" s="94"/>
+      <c r="B37" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C37" s="89" t="str" cm="1">
+      <c r="C37" s="88" t="str" cm="1">
         <f t="array" ref="C37">UPPER(INDEX(_xlfn.TEXTSPLIT($D37, "-"), 3))</f>
         <v>DTG</v>
       </c>
-      <c r="D37" s="89" t="s">
+      <c r="D37" s="88" t="s">
         <v>351</v>
       </c>
-      <c r="E37" s="96" t="s">
+      <c r="E37" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="F37" s="89" t="s">
+      <c r="F37" s="88" t="s">
         <v>510</v>
       </c>
-      <c r="G37" s="89" t="str">
+      <c r="G37" s="88" t="str">
         <f t="shared" si="0"/>
         <v>d-dtg-cdsvadm01-disk01</v>
       </c>
-      <c r="H37" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="I37" s="89">
-        <v>64</v>
-      </c>
-      <c r="J37" s="89" t="str">
+      <c r="H37" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="I37" s="88">
+        <v>64</v>
+      </c>
+      <c r="J37" s="88" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-cdsvadm01-disk02</v>
       </c>
-      <c r="K37" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="L37" s="89">
-        <v>64</v>
-      </c>
-      <c r="M37" s="89">
-        <v>1</v>
-      </c>
-      <c r="N37" s="89" t="s">
+      <c r="K37" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="L37" s="88">
+        <v>64</v>
+      </c>
+      <c r="M37" s="88">
+        <v>1</v>
+      </c>
+      <c r="N37" s="88" t="s">
         <v>502</v>
       </c>
-      <c r="O37" s="89" t="s">
-        <v>173</v>
-      </c>
-      <c r="P37" s="89" t="s">
+      <c r="O37" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="P37" s="88" t="s">
         <v>499</v>
       </c>
-      <c r="Q37" s="89" t="b">
+      <c r="Q37" s="88" t="b">
         <v>1</v>
       </c>
       <c r="R37" s="56"/>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A38" s="93"/>
-      <c r="B38" s="88" t="s">
+      <c r="A38" s="92"/>
+      <c r="B38" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C38" s="88"/>
-      <c r="D38" s="88" t="s">
+      <c r="C38" s="87" t="str" cm="1">
+        <f t="array" ref="C38">UPPER(INDEX(_xlfn.TEXTSPLIT($D38, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="D38" s="87" t="s">
         <v>351</v>
       </c>
-      <c r="E38" s="94" t="s">
+      <c r="E38" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="F38" s="88" t="s">
+      <c r="F38" s="87" t="s">
         <v>395</v>
       </c>
-      <c r="G38" s="88" t="str">
+      <c r="G38" s="87" t="str">
         <f t="shared" si="0"/>
         <v>d-dtg-diosap01-disk01</v>
       </c>
-      <c r="H38" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="I38" s="88">
-        <v>64</v>
-      </c>
-      <c r="J38" s="88" t="str">
+      <c r="H38" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="I38" s="87">
+        <v>64</v>
+      </c>
+      <c r="J38" s="87" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-diosap01-disk02</v>
       </c>
-      <c r="K38" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="L38" s="88">
-        <v>64</v>
-      </c>
-      <c r="M38" s="88">
-        <v>1</v>
-      </c>
-      <c r="N38" s="88" t="s">
+      <c r="K38" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="L38" s="87">
+        <v>64</v>
+      </c>
+      <c r="M38" s="87">
+        <v>1</v>
+      </c>
+      <c r="N38" s="87" t="s">
         <v>502</v>
       </c>
-      <c r="O38" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="P38" s="88" t="s">
+      <c r="O38" s="87" t="s">
+        <v>173</v>
+      </c>
+      <c r="P38" s="87" t="s">
         <v>499</v>
       </c>
-      <c r="Q38" s="88" t="b">
-        <v>1</v>
-      </c>
-      <c r="R38" s="86"/>
+      <c r="Q38" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="R38" s="85"/>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A39" s="102"/>
-      <c r="B39" s="89" t="s">
+      <c r="A39" s="94"/>
+      <c r="B39" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C39" s="89" t="str" cm="1">
+      <c r="C39" s="88" t="str" cm="1">
         <f t="array" ref="C39">UPPER(INDEX(_xlfn.TEXTSPLIT($D39, "-"), 3))</f>
         <v>DTG</v>
       </c>
-      <c r="D39" s="89" t="s">
+      <c r="D39" s="88" t="s">
         <v>351</v>
       </c>
-      <c r="E39" s="96" t="s">
+      <c r="E39" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="F39" s="89" t="s">
+      <c r="F39" s="88" t="s">
         <v>397</v>
       </c>
-      <c r="G39" s="89" t="str">
+      <c r="G39" s="88" t="str">
         <f t="shared" si="0"/>
         <v>d-dtg-diosweb01-disk01</v>
       </c>
-      <c r="H39" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="I39" s="89">
-        <v>64</v>
-      </c>
-      <c r="J39" s="89" t="str">
+      <c r="H39" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="I39" s="88">
+        <v>64</v>
+      </c>
+      <c r="J39" s="88" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-diosweb01-disk02</v>
       </c>
-      <c r="K39" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="L39" s="89">
-        <v>64</v>
-      </c>
-      <c r="M39" s="89">
-        <v>1</v>
-      </c>
-      <c r="N39" s="89" t="s">
+      <c r="K39" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="L39" s="88">
+        <v>64</v>
+      </c>
+      <c r="M39" s="88">
+        <v>1</v>
+      </c>
+      <c r="N39" s="88" t="s">
         <v>502</v>
       </c>
-      <c r="O39" s="89" t="s">
-        <v>173</v>
-      </c>
-      <c r="P39" s="89" t="s">
+      <c r="O39" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="P39" s="88" t="s">
         <v>499</v>
       </c>
-      <c r="Q39" s="89" t="b">
+      <c r="Q39" s="88" t="b">
         <v>1</v>
       </c>
       <c r="R39" s="56"/>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A40" s="103"/>
-      <c r="B40" s="88" t="s">
+      <c r="A40" s="92"/>
+      <c r="B40" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C40" s="88" t="str" cm="1">
+      <c r="C40" s="87" t="str" cm="1">
         <f t="array" ref="C40">UPPER(INDEX(_xlfn.TEXTSPLIT($D40, "-"), 3))</f>
         <v>DTG</v>
       </c>
-      <c r="D40" s="88" t="s">
+      <c r="D40" s="87" t="s">
         <v>351</v>
       </c>
-      <c r="E40" s="94" t="s">
+      <c r="E40" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="F40" s="88" t="s">
+      <c r="F40" s="87" t="s">
         <v>399</v>
       </c>
-      <c r="G40" s="88" t="str">
+      <c r="G40" s="87" t="str">
         <f t="shared" si="0"/>
         <v>d-dtg-dprweb01-disk01</v>
       </c>
-      <c r="H40" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="I40" s="88">
-        <v>64</v>
-      </c>
-      <c r="J40" s="88" t="str">
+      <c r="H40" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="I40" s="87">
+        <v>64</v>
+      </c>
+      <c r="J40" s="87" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-dprweb01-disk02</v>
       </c>
-      <c r="K40" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="L40" s="88">
-        <v>64</v>
-      </c>
-      <c r="M40" s="88">
-        <v>1</v>
-      </c>
-      <c r="N40" s="88" t="s">
+      <c r="K40" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="L40" s="87">
+        <v>64</v>
+      </c>
+      <c r="M40" s="87">
+        <v>1</v>
+      </c>
+      <c r="N40" s="87" t="s">
         <v>502</v>
       </c>
-      <c r="O40" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="P40" s="88" t="s">
+      <c r="O40" s="87" t="s">
+        <v>173</v>
+      </c>
+      <c r="P40" s="87" t="s">
         <v>499</v>
       </c>
-      <c r="Q40" s="88" t="b">
-        <v>1</v>
-      </c>
-      <c r="R40" s="86"/>
+      <c r="Q40" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="R40" s="85"/>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A41" s="95"/>
-      <c r="B41" s="89" t="s">
+      <c r="A41" s="94"/>
+      <c r="B41" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C41" s="89"/>
-      <c r="D41" s="89" t="s">
+      <c r="C41" s="88" t="str" cm="1">
+        <f t="array" ref="C41">UPPER(INDEX(_xlfn.TEXTSPLIT($D41, "-"), 3))</f>
+        <v>DTG</v>
+      </c>
+      <c r="D41" s="88" t="s">
         <v>351</v>
       </c>
-      <c r="E41" s="96" t="s">
+      <c r="E41" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="F41" s="89" t="s">
+      <c r="F41" s="88" t="s">
         <v>401</v>
       </c>
-      <c r="G41" s="89" t="str">
+      <c r="G41" s="88" t="str">
         <f t="shared" si="0"/>
         <v>d-dtg-dprap01-disk01</v>
       </c>
-      <c r="H41" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="I41" s="89">
-        <v>64</v>
-      </c>
-      <c r="J41" s="89" t="str">
+      <c r="H41" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="I41" s="88">
+        <v>64</v>
+      </c>
+      <c r="J41" s="88" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-dprap01-disk02</v>
       </c>
-      <c r="K41" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="L41" s="89">
-        <v>64</v>
-      </c>
-      <c r="M41" s="89">
-        <v>1</v>
-      </c>
-      <c r="N41" s="89" t="s">
+      <c r="K41" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="L41" s="88">
+        <v>64</v>
+      </c>
+      <c r="M41" s="88">
+        <v>1</v>
+      </c>
+      <c r="N41" s="88" t="s">
         <v>502</v>
       </c>
-      <c r="O41" s="89" t="s">
-        <v>173</v>
-      </c>
-      <c r="P41" s="89" t="s">
+      <c r="O41" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="P41" s="88" t="s">
         <v>499</v>
       </c>
-      <c r="Q41" s="89" t="b">
+      <c r="Q41" s="88" t="b">
         <v>1</v>
       </c>
       <c r="R41" s="56"/>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A42" s="103"/>
-      <c r="B42" s="88" t="s">
+      <c r="A42" s="92"/>
+      <c r="B42" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C42" s="88" t="str" cm="1">
+      <c r="C42" s="87" t="str" cm="1">
         <f t="array" ref="C42">UPPER(INDEX(_xlfn.TEXTSPLIT($D42, "-"), 3))</f>
         <v>BDP</v>
       </c>
-      <c r="D42" s="88" t="s">
+      <c r="D42" s="87" t="s">
         <v>403</v>
       </c>
-      <c r="E42" s="94" t="s">
+      <c r="E42" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="F42" s="88" t="s">
+      <c r="F42" s="87" t="s">
         <v>404</v>
       </c>
-      <c r="G42" s="88" t="str">
+      <c r="G42" s="87" t="str">
         <f t="shared" si="0"/>
         <v>d-bdp-airfw01-disk01</v>
       </c>
-      <c r="H42" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="I42" s="88">
-        <v>64</v>
-      </c>
-      <c r="J42" s="88" t="str">
+      <c r="H42" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="I42" s="87">
+        <v>64</v>
+      </c>
+      <c r="J42" s="87" t="str">
         <f t="shared" si="1"/>
         <v>d-bdp-airfw01-disk02</v>
       </c>
-      <c r="K42" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="L42" s="88">
-        <v>64</v>
-      </c>
-      <c r="M42" s="88">
-        <v>1</v>
-      </c>
-      <c r="N42" s="88" t="s">
+      <c r="K42" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="L42" s="87">
+        <v>64</v>
+      </c>
+      <c r="M42" s="87">
+        <v>1</v>
+      </c>
+      <c r="N42" s="87" t="s">
         <v>502</v>
       </c>
-      <c r="O42" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="P42" s="88" t="s">
+      <c r="O42" s="87" t="s">
+        <v>173</v>
+      </c>
+      <c r="P42" s="87" t="s">
         <v>499</v>
       </c>
-      <c r="Q42" s="88" t="b">
-        <v>1</v>
-      </c>
-      <c r="R42" s="86"/>
+      <c r="Q42" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="R42" s="85"/>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A43" s="102"/>
-      <c r="B43" s="89" t="s">
+      <c r="A43" s="94"/>
+      <c r="B43" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C43" s="89" t="str" cm="1">
+      <c r="C43" s="88" t="str" cm="1">
         <f t="array" ref="C43">UPPER(INDEX(_xlfn.TEXTSPLIT($D43, "-"), 3))</f>
         <v>BDP</v>
       </c>
-      <c r="D43" s="89" t="s">
+      <c r="D43" s="88" t="s">
         <v>403</v>
       </c>
-      <c r="E43" s="96" t="s">
+      <c r="E43" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="F43" s="89" t="s">
+      <c r="F43" s="88" t="s">
         <v>407</v>
       </c>
-      <c r="G43" s="89" t="str">
+      <c r="G43" s="88" t="str">
         <f t="shared" si="0"/>
         <v>d-bdp-kepler01-disk01</v>
       </c>
-      <c r="H43" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="I43" s="89">
-        <v>64</v>
-      </c>
-      <c r="J43" s="89" t="str">
+      <c r="H43" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="I43" s="88">
+        <v>64</v>
+      </c>
+      <c r="J43" s="88" t="str">
         <f t="shared" si="1"/>
         <v>d-bdp-kepler01-disk02</v>
       </c>
-      <c r="K43" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="L43" s="89">
-        <v>64</v>
-      </c>
-      <c r="M43" s="89">
-        <v>1</v>
-      </c>
-      <c r="N43" s="89" t="s">
+      <c r="K43" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="L43" s="88">
+        <v>64</v>
+      </c>
+      <c r="M43" s="88">
+        <v>1</v>
+      </c>
+      <c r="N43" s="88" t="s">
         <v>502</v>
       </c>
-      <c r="O43" s="89" t="s">
-        <v>173</v>
-      </c>
-      <c r="P43" s="89" t="s">
+      <c r="O43" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="P43" s="88" t="s">
         <v>499</v>
       </c>
-      <c r="Q43" s="89" t="b">
+      <c r="Q43" s="88" t="b">
         <v>1</v>
       </c>
       <c r="R43" s="56"/>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A44" s="103"/>
-      <c r="B44" s="88" t="s">
+      <c r="A44" s="92"/>
+      <c r="B44" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C44" s="88" t="str" cm="1">
+      <c r="C44" s="87" t="str" cm="1">
         <f t="array" ref="C44">UPPER(INDEX(_xlfn.TEXTSPLIT($D44, "-"), 3))</f>
         <v>BDP</v>
       </c>
-      <c r="D44" s="88" t="s">
+      <c r="D44" s="87" t="s">
         <v>403</v>
       </c>
-      <c r="E44" s="94" t="s">
+      <c r="E44" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="F44" s="88" t="s">
+      <c r="F44" s="87" t="s">
         <v>511</v>
       </c>
-      <c r="G44" s="88" t="str">
+      <c r="G44" s="87" t="str">
         <f t="shared" si="0"/>
         <v>d-bdp-cxmadm01-disk01</v>
       </c>
-      <c r="H44" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="I44" s="88">
-        <v>64</v>
-      </c>
-      <c r="J44" s="88" t="str">
+      <c r="H44" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="I44" s="87">
+        <v>64</v>
+      </c>
+      <c r="J44" s="87" t="str">
         <f t="shared" si="1"/>
         <v>d-bdp-cxmadm01-disk02</v>
       </c>
-      <c r="K44" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="L44" s="88">
-        <v>64</v>
-      </c>
-      <c r="M44" s="88">
-        <v>1</v>
-      </c>
-      <c r="N44" s="88" t="s">
+      <c r="K44" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="L44" s="87">
+        <v>64</v>
+      </c>
+      <c r="M44" s="87">
+        <v>1</v>
+      </c>
+      <c r="N44" s="87" t="s">
         <v>502</v>
       </c>
-      <c r="O44" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="P44" s="88" t="s">
+      <c r="O44" s="87" t="s">
+        <v>173</v>
+      </c>
+      <c r="P44" s="87" t="s">
         <v>499</v>
       </c>
-      <c r="Q44" s="88" t="b">
-        <v>1</v>
-      </c>
-      <c r="R44" s="86"/>
+      <c r="Q44" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="R44" s="85"/>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A45" s="103"/>
-      <c r="B45" s="89" t="s">
+      <c r="A45" s="92"/>
+      <c r="B45" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C45" s="89" t="str" cm="1">
+      <c r="C45" s="88" t="str" cm="1">
         <f t="array" ref="C45">UPPER(INDEX(_xlfn.TEXTSPLIT($D45, "-"), 3))</f>
         <v>BDP</v>
       </c>
-      <c r="D45" s="89" t="s">
+      <c r="D45" s="88" t="s">
         <v>403</v>
       </c>
-      <c r="E45" s="96" t="s">
+      <c r="E45" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="F45" s="89" t="s">
+      <c r="F45" s="88" t="s">
         <v>410</v>
       </c>
-      <c r="G45" s="89" t="str">
+      <c r="G45" s="88" t="str">
         <f t="shared" si="0"/>
         <v>d-bdp-slap01-disk01</v>
       </c>
-      <c r="H45" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="I45" s="89">
-        <v>64</v>
-      </c>
-      <c r="J45" s="89" t="str">
+      <c r="H45" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="I45" s="88">
+        <v>64</v>
+      </c>
+      <c r="J45" s="88" t="str">
         <f t="shared" si="1"/>
         <v>d-bdp-slap01-disk02</v>
       </c>
-      <c r="K45" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="L45" s="89">
-        <v>64</v>
-      </c>
-      <c r="M45" s="89">
-        <v>1</v>
-      </c>
-      <c r="N45" s="89" t="s">
+      <c r="K45" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="L45" s="88">
+        <v>64</v>
+      </c>
+      <c r="M45" s="88">
+        <v>1</v>
+      </c>
+      <c r="N45" s="88" t="s">
         <v>502</v>
       </c>
-      <c r="O45" s="89" t="s">
-        <v>173</v>
-      </c>
-      <c r="P45" s="89" t="s">
+      <c r="O45" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="P45" s="88" t="s">
         <v>499</v>
       </c>
-      <c r="Q45" s="89" t="b">
+      <c r="Q45" s="88" t="b">
         <v>1</v>
       </c>
       <c r="R45" s="56"/>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A46" s="102"/>
-      <c r="B46" s="88" t="s">
+      <c r="A46" s="94"/>
+      <c r="B46" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C46" s="88" t="str" cm="1">
+      <c r="C46" s="87" t="str" cm="1">
         <f t="array" ref="C46">UPPER(INDEX(_xlfn.TEXTSPLIT($D46, "-"), 3))</f>
         <v>DIP</v>
       </c>
-      <c r="D46" s="88" t="s">
+      <c r="D46" s="87" t="s">
         <v>473</v>
       </c>
-      <c r="E46" s="94" t="s">
+      <c r="E46" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="F46" s="88" t="s">
+      <c r="F46" s="87" t="s">
         <v>412</v>
       </c>
-      <c r="G46" s="88" t="str">
+      <c r="G46" s="87" t="str">
         <f t="shared" si="0"/>
         <v>d-dip-adm01-disk01</v>
       </c>
-      <c r="H46" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="I46" s="88">
-        <v>64</v>
-      </c>
-      <c r="J46" s="88" t="str">
+      <c r="H46" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="I46" s="87">
+        <v>64</v>
+      </c>
+      <c r="J46" s="87" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-adm01-disk02</v>
       </c>
-      <c r="K46" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="L46" s="88">
-        <v>64</v>
-      </c>
-      <c r="M46" s="88">
-        <v>1</v>
-      </c>
-      <c r="N46" s="88" t="s">
+      <c r="K46" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="L46" s="87">
+        <v>64</v>
+      </c>
+      <c r="M46" s="87">
+        <v>1</v>
+      </c>
+      <c r="N46" s="87" t="s">
         <v>502</v>
       </c>
-      <c r="O46" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="P46" s="88" t="s">
+      <c r="O46" s="87" t="s">
+        <v>173</v>
+      </c>
+      <c r="P46" s="87" t="s">
         <v>499</v>
       </c>
-      <c r="Q46" s="88" t="b">
-        <v>1</v>
-      </c>
-      <c r="R46" s="86"/>
+      <c r="Q46" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="R46" s="85"/>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A47" s="103"/>
-      <c r="B47" s="89" t="s">
+      <c r="A47" s="92"/>
+      <c r="B47" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C47" s="89" t="str" cm="1">
+      <c r="C47" s="88" t="str" cm="1">
         <f t="array" ref="C47">UPPER(INDEX(_xlfn.TEXTSPLIT($D47, "-"), 3))</f>
         <v>DIP</v>
       </c>
-      <c r="D47" s="89" t="s">
+      <c r="D47" s="88" t="s">
         <v>473</v>
       </c>
-      <c r="E47" s="96" t="s">
+      <c r="E47" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="F47" s="89" t="s">
+      <c r="F47" s="88" t="s">
         <v>415</v>
       </c>
-      <c r="G47" s="89" t="str">
+      <c r="G47" s="88" t="str">
         <f t="shared" si="0"/>
         <v>d-dip-ap01-disk01</v>
       </c>
-      <c r="H47" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="I47" s="89">
-        <v>64</v>
-      </c>
-      <c r="J47" s="89" t="str">
+      <c r="H47" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="I47" s="88">
+        <v>64</v>
+      </c>
+      <c r="J47" s="88" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-ap01-disk02</v>
       </c>
-      <c r="K47" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="L47" s="89">
-        <v>64</v>
-      </c>
-      <c r="M47" s="89">
-        <v>1</v>
-      </c>
-      <c r="N47" s="89" t="s">
+      <c r="K47" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="L47" s="88">
+        <v>64</v>
+      </c>
+      <c r="M47" s="88">
+        <v>1</v>
+      </c>
+      <c r="N47" s="88" t="s">
         <v>502</v>
       </c>
-      <c r="O47" s="89" t="s">
-        <v>173</v>
-      </c>
-      <c r="P47" s="89" t="s">
+      <c r="O47" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="P47" s="88" t="s">
         <v>499</v>
       </c>
-      <c r="Q47" s="89" t="b">
+      <c r="Q47" s="88" t="b">
         <v>1</v>
       </c>
       <c r="R47" s="56"/>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A48" s="95"/>
-      <c r="B48" s="88" t="s">
+      <c r="A48" s="94"/>
+      <c r="B48" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C48" s="88"/>
-      <c r="D48" s="88" t="s">
+      <c r="C48" s="87" t="str" cm="1">
+        <f t="array" ref="C48">UPPER(INDEX(_xlfn.TEXTSPLIT($D48, "-"), 3))</f>
+        <v>DIP</v>
+      </c>
+      <c r="D48" s="87" t="s">
         <v>473</v>
       </c>
-      <c r="E48" s="94" t="s">
+      <c r="E48" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="F48" s="88" t="s">
+      <c r="F48" s="87" t="s">
         <v>417</v>
       </c>
-      <c r="G48" s="88" t="str">
+      <c r="G48" s="87" t="str">
         <f t="shared" si="0"/>
         <v>d-dip-flk01-disk01</v>
       </c>
-      <c r="H48" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="I48" s="88">
-        <v>64</v>
-      </c>
-      <c r="J48" s="88" t="str">
+      <c r="H48" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="I48" s="87">
+        <v>64</v>
+      </c>
+      <c r="J48" s="87" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-flk01-disk02</v>
       </c>
-      <c r="K48" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="L48" s="88">
-        <v>64</v>
-      </c>
-      <c r="M48" s="88">
-        <v>1</v>
-      </c>
-      <c r="N48" s="88" t="s">
+      <c r="K48" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="L48" s="87">
+        <v>64</v>
+      </c>
+      <c r="M48" s="87">
+        <v>1</v>
+      </c>
+      <c r="N48" s="87" t="s">
         <v>502</v>
       </c>
-      <c r="O48" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="P48" s="88" t="s">
+      <c r="O48" s="87" t="s">
+        <v>173</v>
+      </c>
+      <c r="P48" s="87" t="s">
         <v>499</v>
       </c>
-      <c r="Q48" s="88" t="b">
-        <v>1</v>
-      </c>
-      <c r="R48" s="86"/>
+      <c r="Q48" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="R48" s="85"/>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A49" s="93"/>
-      <c r="B49" s="89" t="s">
+      <c r="A49" s="92"/>
+      <c r="B49" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C49" s="89"/>
-      <c r="D49" s="89" t="s">
+      <c r="C49" s="88" t="str" cm="1">
+        <f t="array" ref="C49">UPPER(INDEX(_xlfn.TEXTSPLIT($D49, "-"), 3))</f>
+        <v>DIP</v>
+      </c>
+      <c r="D49" s="88" t="s">
         <v>473</v>
       </c>
-      <c r="E49" s="96" t="s">
+      <c r="E49" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="F49" s="89" t="s">
+      <c r="F49" s="88" t="s">
         <v>419</v>
       </c>
-      <c r="G49" s="89" t="str">
+      <c r="G49" s="88" t="str">
         <f t="shared" si="0"/>
         <v>d-dip-flk02-disk01</v>
       </c>
-      <c r="H49" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="I49" s="89">
-        <v>64</v>
-      </c>
-      <c r="J49" s="89" t="str">
+      <c r="H49" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="I49" s="88">
+        <v>64</v>
+      </c>
+      <c r="J49" s="88" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-flk02-disk02</v>
       </c>
-      <c r="K49" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="L49" s="89">
-        <v>64</v>
-      </c>
-      <c r="M49" s="89">
-        <v>1</v>
-      </c>
-      <c r="N49" s="89" t="s">
+      <c r="K49" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="L49" s="88">
+        <v>64</v>
+      </c>
+      <c r="M49" s="88">
+        <v>1</v>
+      </c>
+      <c r="N49" s="88" t="s">
         <v>502</v>
       </c>
-      <c r="O49" s="89" t="s">
-        <v>173</v>
-      </c>
-      <c r="P49" s="89" t="s">
+      <c r="O49" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="P49" s="88" t="s">
         <v>499</v>
       </c>
-      <c r="Q49" s="89" t="b">
+      <c r="Q49" s="88" t="b">
         <v>1</v>
       </c>
       <c r="R49" s="56"/>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A50" s="95"/>
-      <c r="B50" s="88" t="s">
+      <c r="A50" s="94"/>
+      <c r="B50" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C50" s="88"/>
-      <c r="D50" s="88" t="s">
+      <c r="C50" s="87" t="str" cm="1">
+        <f t="array" ref="C50">UPPER(INDEX(_xlfn.TEXTSPLIT($D50, "-"), 3))</f>
+        <v>DIP</v>
+      </c>
+      <c r="D50" s="87" t="s">
         <v>473</v>
       </c>
-      <c r="E50" s="94" t="s">
+      <c r="E50" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="F50" s="88" t="s">
+      <c r="F50" s="87" t="s">
         <v>421</v>
       </c>
-      <c r="G50" s="88" t="str">
+      <c r="G50" s="87" t="str">
         <f t="shared" si="0"/>
         <v>d-dip-flk03-disk01</v>
       </c>
-      <c r="H50" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="I50" s="88">
-        <v>64</v>
-      </c>
-      <c r="J50" s="88" t="str">
+      <c r="H50" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="I50" s="87">
+        <v>64</v>
+      </c>
+      <c r="J50" s="87" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-flk03-disk02</v>
       </c>
-      <c r="K50" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="L50" s="88">
-        <v>64</v>
-      </c>
-      <c r="M50" s="88">
-        <v>1</v>
-      </c>
-      <c r="N50" s="88" t="s">
+      <c r="K50" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="L50" s="87">
+        <v>64</v>
+      </c>
+      <c r="M50" s="87">
+        <v>1</v>
+      </c>
+      <c r="N50" s="87" t="s">
         <v>502</v>
       </c>
-      <c r="O50" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="P50" s="88" t="s">
+      <c r="O50" s="87" t="s">
+        <v>173</v>
+      </c>
+      <c r="P50" s="87" t="s">
         <v>499</v>
       </c>
-      <c r="Q50" s="88" t="b">
-        <v>1</v>
-      </c>
-      <c r="R50" s="86"/>
+      <c r="Q50" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="R50" s="85"/>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A51" s="93"/>
-      <c r="B51" s="89" t="s">
+      <c r="A51" s="92"/>
+      <c r="B51" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C51" s="89"/>
-      <c r="D51" s="89" t="s">
+      <c r="C51" s="88" t="str" cm="1">
+        <f t="array" ref="C51">UPPER(INDEX(_xlfn.TEXTSPLIT($D51, "-"), 3))</f>
+        <v>DIP</v>
+      </c>
+      <c r="D51" s="88" t="s">
         <v>473</v>
       </c>
-      <c r="E51" s="96" t="s">
+      <c r="E51" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="F51" s="89" t="s">
+      <c r="F51" s="88" t="s">
         <v>423</v>
       </c>
-      <c r="G51" s="89" t="str">
+      <c r="G51" s="88" t="str">
         <f t="shared" si="0"/>
         <v>d-dip-geoap01-disk01</v>
       </c>
-      <c r="H51" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="I51" s="89">
-        <v>64</v>
-      </c>
-      <c r="J51" s="89" t="str">
+      <c r="H51" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="I51" s="88">
+        <v>64</v>
+      </c>
+      <c r="J51" s="88" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-geoap01-disk02</v>
       </c>
-      <c r="K51" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="L51" s="89">
-        <v>64</v>
-      </c>
-      <c r="M51" s="89">
-        <v>1</v>
-      </c>
-      <c r="N51" s="89" t="s">
+      <c r="K51" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="L51" s="88">
+        <v>64</v>
+      </c>
+      <c r="M51" s="88">
+        <v>1</v>
+      </c>
+      <c r="N51" s="88" t="s">
         <v>502</v>
       </c>
-      <c r="O51" s="89" t="s">
-        <v>173</v>
-      </c>
-      <c r="P51" s="89" t="s">
+      <c r="O51" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="P51" s="88" t="s">
         <v>499</v>
       </c>
-      <c r="Q51" s="89" t="b">
+      <c r="Q51" s="88" t="b">
         <v>1</v>
       </c>
       <c r="R51" s="56"/>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A52" s="95"/>
-      <c r="B52" s="88" t="s">
+      <c r="A52" s="94"/>
+      <c r="B52" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C52" s="88"/>
-      <c r="D52" s="88" t="s">
+      <c r="C52" s="87" t="str" cm="1">
+        <f t="array" ref="C52">UPPER(INDEX(_xlfn.TEXTSPLIT($D52, "-"), 3))</f>
+        <v>DIP</v>
+      </c>
+      <c r="D52" s="87" t="s">
         <v>473</v>
       </c>
-      <c r="E52" s="94" t="s">
+      <c r="E52" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="F52" s="88" t="s">
+      <c r="F52" s="87" t="s">
         <v>425</v>
       </c>
-      <c r="G52" s="88" t="str">
+      <c r="G52" s="87" t="str">
         <f t="shared" si="0"/>
         <v>d-dip-kfk01-disk01</v>
       </c>
-      <c r="H52" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="I52" s="88">
-        <v>64</v>
-      </c>
-      <c r="J52" s="88" t="str">
+      <c r="H52" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="I52" s="87">
+        <v>64</v>
+      </c>
+      <c r="J52" s="87" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-kfk01-disk02</v>
       </c>
-      <c r="K52" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="L52" s="88">
-        <v>64</v>
-      </c>
-      <c r="M52" s="88">
-        <v>1</v>
-      </c>
-      <c r="N52" s="88" t="s">
+      <c r="K52" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="L52" s="87">
+        <v>64</v>
+      </c>
+      <c r="M52" s="87">
+        <v>1</v>
+      </c>
+      <c r="N52" s="87" t="s">
         <v>502</v>
       </c>
-      <c r="O52" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="P52" s="88" t="s">
+      <c r="O52" s="87" t="s">
+        <v>173</v>
+      </c>
+      <c r="P52" s="87" t="s">
         <v>499</v>
       </c>
-      <c r="Q52" s="88" t="b">
-        <v>1</v>
-      </c>
-      <c r="R52" s="86"/>
+      <c r="Q52" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="R52" s="85"/>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A53" s="93"/>
-      <c r="B53" s="89" t="s">
+      <c r="A53" s="92"/>
+      <c r="B53" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C53" s="89"/>
-      <c r="D53" s="89" t="s">
+      <c r="C53" s="88" t="str" cm="1">
+        <f t="array" ref="C53">UPPER(INDEX(_xlfn.TEXTSPLIT($D53, "-"), 3))</f>
+        <v>DIP</v>
+      </c>
+      <c r="D53" s="88" t="s">
         <v>473</v>
       </c>
-      <c r="E53" s="96" t="s">
+      <c r="E53" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="F53" s="89" t="s">
+      <c r="F53" s="88" t="s">
         <v>474</v>
       </c>
-      <c r="G53" s="89" t="str">
+      <c r="G53" s="88" t="str">
         <f t="shared" si="0"/>
         <v>d-dip-kfk02-disk01</v>
       </c>
-      <c r="H53" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="I53" s="89">
-        <v>64</v>
-      </c>
-      <c r="J53" s="89" t="str">
+      <c r="H53" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="I53" s="88">
+        <v>64</v>
+      </c>
+      <c r="J53" s="88" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-kfk02-disk02</v>
       </c>
-      <c r="K53" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="L53" s="89">
-        <v>64</v>
-      </c>
-      <c r="M53" s="89">
-        <v>1</v>
-      </c>
-      <c r="N53" s="89" t="s">
+      <c r="K53" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="L53" s="88">
+        <v>64</v>
+      </c>
+      <c r="M53" s="88">
+        <v>1</v>
+      </c>
+      <c r="N53" s="88" t="s">
         <v>502</v>
       </c>
-      <c r="O53" s="89" t="s">
-        <v>173</v>
-      </c>
-      <c r="P53" s="89" t="s">
+      <c r="O53" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="P53" s="88" t="s">
         <v>499</v>
       </c>
-      <c r="Q53" s="89" t="b">
+      <c r="Q53" s="88" t="b">
         <v>1</v>
       </c>
       <c r="R53" s="56"/>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A54" s="93"/>
-      <c r="B54" s="88" t="s">
+      <c r="A54" s="92"/>
+      <c r="B54" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C54" s="88"/>
-      <c r="D54" s="88" t="s">
+      <c r="C54" s="87" t="str" cm="1">
+        <f t="array" ref="C54">UPPER(INDEX(_xlfn.TEXTSPLIT($D54, "-"), 3))</f>
+        <v>DIP</v>
+      </c>
+      <c r="D54" s="87" t="s">
         <v>473</v>
       </c>
-      <c r="E54" s="94" t="s">
+      <c r="E54" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="F54" s="88" t="s">
+      <c r="F54" s="87" t="s">
         <v>475</v>
       </c>
-      <c r="G54" s="88" t="str">
+      <c r="G54" s="87" t="str">
         <f t="shared" si="0"/>
         <v>d-dip-kfk03-disk01</v>
       </c>
-      <c r="H54" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="I54" s="88">
-        <v>64</v>
-      </c>
-      <c r="J54" s="88" t="str">
+      <c r="H54" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="I54" s="87">
+        <v>64</v>
+      </c>
+      <c r="J54" s="87" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-kfk03-disk02</v>
       </c>
-      <c r="K54" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="L54" s="88">
-        <v>64</v>
-      </c>
-      <c r="M54" s="88">
-        <v>1</v>
-      </c>
-      <c r="N54" s="88" t="s">
+      <c r="K54" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="L54" s="87">
+        <v>64</v>
+      </c>
+      <c r="M54" s="87">
+        <v>1</v>
+      </c>
+      <c r="N54" s="87" t="s">
         <v>502</v>
       </c>
-      <c r="O54" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="P54" s="88" t="s">
+      <c r="O54" s="87" t="s">
+        <v>173</v>
+      </c>
+      <c r="P54" s="87" t="s">
         <v>499</v>
       </c>
-      <c r="Q54" s="88" t="b">
-        <v>1</v>
-      </c>
-      <c r="R54" s="86"/>
+      <c r="Q54" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="R54" s="85"/>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A55" s="95"/>
-      <c r="B55" s="89" t="s">
+      <c r="A55" s="94"/>
+      <c r="B55" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C55" s="89"/>
-      <c r="D55" s="89" t="s">
+      <c r="C55" s="88" t="str" cm="1">
+        <f t="array" ref="C55">UPPER(INDEX(_xlfn.TEXTSPLIT($D55, "-"), 3))</f>
+        <v>DIP</v>
+      </c>
+      <c r="D55" s="88" t="s">
         <v>473</v>
       </c>
-      <c r="E55" s="96" t="s">
+      <c r="E55" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="F55" s="89" t="s">
+      <c r="F55" s="88" t="s">
         <v>429</v>
       </c>
-      <c r="G55" s="89" t="str">
+      <c r="G55" s="88" t="str">
         <f t="shared" si="0"/>
         <v>d-dip-mqap01-disk01</v>
       </c>
-      <c r="H55" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="I55" s="89">
-        <v>64</v>
-      </c>
-      <c r="J55" s="89" t="str">
+      <c r="H55" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="I55" s="88">
+        <v>64</v>
+      </c>
+      <c r="J55" s="88" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-mqap01-disk02</v>
       </c>
-      <c r="K55" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="L55" s="89">
-        <v>64</v>
-      </c>
-      <c r="M55" s="89">
-        <v>1</v>
-      </c>
-      <c r="N55" s="89" t="s">
+      <c r="K55" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="L55" s="88">
+        <v>64</v>
+      </c>
+      <c r="M55" s="88">
+        <v>1</v>
+      </c>
+      <c r="N55" s="88" t="s">
         <v>502</v>
       </c>
-      <c r="O55" s="89" t="s">
-        <v>173</v>
-      </c>
-      <c r="P55" s="89" t="s">
+      <c r="O55" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="P55" s="88" t="s">
         <v>499</v>
       </c>
-      <c r="Q55" s="89" t="b">
+      <c r="Q55" s="88" t="b">
         <v>1</v>
       </c>
       <c r="R55" s="56"/>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A56" s="103"/>
-      <c r="B56" s="88" t="s">
+      <c r="A56" s="92"/>
+      <c r="B56" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C56" s="88" t="str" cm="1">
+      <c r="C56" s="87" t="str" cm="1">
         <f t="array" ref="C56">UPPER(INDEX(_xlfn.TEXTSPLIT($D56, "-"), 3))</f>
         <v>DIP</v>
       </c>
-      <c r="D56" s="88" t="s">
+      <c r="D56" s="87" t="s">
         <v>473</v>
       </c>
-      <c r="E56" s="94" t="s">
+      <c r="E56" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="F56" s="88" t="s">
+      <c r="F56" s="87" t="s">
         <v>431</v>
       </c>
-      <c r="G56" s="88" t="str">
+      <c r="G56" s="87" t="str">
         <f t="shared" si="0"/>
         <v>d-dip-mqweb01-disk01</v>
       </c>
-      <c r="H56" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="I56" s="88">
-        <v>64</v>
-      </c>
-      <c r="J56" s="88" t="str">
+      <c r="H56" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="I56" s="87">
+        <v>64</v>
+      </c>
+      <c r="J56" s="87" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-mqweb01-disk02</v>
       </c>
-      <c r="K56" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="L56" s="88">
-        <v>64</v>
-      </c>
-      <c r="M56" s="88">
-        <v>1</v>
-      </c>
-      <c r="N56" s="88" t="s">
+      <c r="K56" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="L56" s="87">
+        <v>64</v>
+      </c>
+      <c r="M56" s="87">
+        <v>1</v>
+      </c>
+      <c r="N56" s="87" t="s">
         <v>502</v>
       </c>
-      <c r="O56" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="P56" s="88" t="s">
+      <c r="O56" s="87" t="s">
+        <v>173</v>
+      </c>
+      <c r="P56" s="87" t="s">
         <v>499</v>
       </c>
-      <c r="Q56" s="88" t="b">
-        <v>1</v>
-      </c>
-      <c r="R56" s="86"/>
+      <c r="Q56" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="R56" s="85"/>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A57" s="102"/>
-      <c r="B57" s="89" t="s">
+      <c r="A57" s="94"/>
+      <c r="B57" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C57" s="89" t="str" cm="1">
+      <c r="C57" s="88" t="str" cm="1">
         <f t="array" ref="C57">UPPER(INDEX(_xlfn.TEXTSPLIT($D57, "-"), 3))</f>
         <v>DIP</v>
       </c>
-      <c r="D57" s="89" t="s">
+      <c r="D57" s="88" t="s">
         <v>473</v>
       </c>
-      <c r="E57" s="96" t="s">
+      <c r="E57" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="F57" s="89" t="s">
+      <c r="F57" s="88" t="s">
         <v>433</v>
       </c>
-      <c r="G57" s="89" t="str">
+      <c r="G57" s="88" t="str">
         <f t="shared" si="0"/>
         <v>d-dip-oms01-disk01</v>
       </c>
-      <c r="H57" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="I57" s="89">
-        <v>64</v>
-      </c>
-      <c r="J57" s="89" t="str">
+      <c r="H57" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="I57" s="88">
+        <v>64</v>
+      </c>
+      <c r="J57" s="88" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-oms01-disk02</v>
       </c>
-      <c r="K57" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="L57" s="89">
-        <v>64</v>
-      </c>
-      <c r="M57" s="89">
-        <v>1</v>
-      </c>
-      <c r="N57" s="89" t="s">
+      <c r="K57" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="L57" s="88">
+        <v>64</v>
+      </c>
+      <c r="M57" s="88">
+        <v>1</v>
+      </c>
+      <c r="N57" s="88" t="s">
         <v>502</v>
       </c>
-      <c r="O57" s="89" t="s">
-        <v>173</v>
-      </c>
-      <c r="P57" s="89" t="s">
+      <c r="O57" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="P57" s="88" t="s">
         <v>499</v>
       </c>
-      <c r="Q57" s="89" t="b">
+      <c r="Q57" s="88" t="b">
         <v>1</v>
       </c>
       <c r="R57" s="56"/>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A58" s="103"/>
-      <c r="B58" s="88" t="s">
+      <c r="A58" s="92"/>
+      <c r="B58" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C58" s="88" t="str" cm="1">
+      <c r="C58" s="87" t="str" cm="1">
         <f t="array" ref="C58">UPPER(INDEX(_xlfn.TEXTSPLIT($D58, "-"), 3))</f>
         <v>DIP</v>
       </c>
-      <c r="D58" s="88" t="s">
+      <c r="D58" s="87" t="s">
         <v>473</v>
       </c>
-      <c r="E58" s="94" t="s">
+      <c r="E58" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="F58" s="88" t="s">
+      <c r="F58" s="87" t="s">
         <v>435</v>
       </c>
-      <c r="G58" s="88" t="str">
+      <c r="G58" s="87" t="str">
         <f t="shared" si="0"/>
         <v>d-dip-web01-disk01</v>
       </c>
-      <c r="H58" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="I58" s="88">
-        <v>64</v>
-      </c>
-      <c r="J58" s="88" t="str">
+      <c r="H58" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="I58" s="87">
+        <v>64</v>
+      </c>
+      <c r="J58" s="87" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-web01-disk02</v>
       </c>
-      <c r="K58" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="L58" s="88">
-        <v>64</v>
-      </c>
-      <c r="M58" s="88">
-        <v>1</v>
-      </c>
-      <c r="N58" s="88" t="s">
+      <c r="K58" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="L58" s="87">
+        <v>64</v>
+      </c>
+      <c r="M58" s="87">
+        <v>1</v>
+      </c>
+      <c r="N58" s="87" t="s">
         <v>502</v>
       </c>
-      <c r="O58" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="P58" s="88" t="s">
+      <c r="O58" s="87" t="s">
+        <v>173</v>
+      </c>
+      <c r="P58" s="87" t="s">
         <v>499</v>
       </c>
-      <c r="Q58" s="88" t="b">
-        <v>1</v>
-      </c>
-      <c r="R58" s="86"/>
+      <c r="Q58" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="R58" s="85"/>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A59" s="102"/>
-      <c r="B59" s="89" t="s">
+      <c r="A59" s="94"/>
+      <c r="B59" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C59" s="89" t="str" cm="1">
+      <c r="C59" s="88" t="str" cm="1">
         <f t="array" ref="C59">UPPER(INDEX(_xlfn.TEXTSPLIT($D59, "-"), 3))</f>
         <v>COM</v>
       </c>
-      <c r="D59" s="89" t="s">
+      <c r="D59" s="88" t="s">
         <v>437</v>
       </c>
-      <c r="E59" s="96" t="s">
+      <c r="E59" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="F59" s="89" t="s">
+      <c r="F59" s="88" t="s">
         <v>438</v>
       </c>
-      <c r="G59" s="89" t="str">
+      <c r="G59" s="88" t="str">
         <f t="shared" si="0"/>
         <v>d-com-auth01-disk01</v>
       </c>
-      <c r="H59" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="I59" s="89">
-        <v>64</v>
-      </c>
-      <c r="J59" s="89" t="str">
+      <c r="H59" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="I59" s="88">
+        <v>64</v>
+      </c>
+      <c r="J59" s="88" t="str">
         <f t="shared" si="1"/>
         <v>d-com-auth01-disk02</v>
       </c>
-      <c r="K59" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="L59" s="89">
-        <v>64</v>
-      </c>
-      <c r="M59" s="89">
-        <v>1</v>
-      </c>
-      <c r="N59" s="89" t="s">
+      <c r="K59" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="L59" s="88">
+        <v>64</v>
+      </c>
+      <c r="M59" s="88">
+        <v>1</v>
+      </c>
+      <c r="N59" s="88" t="s">
         <v>502</v>
       </c>
-      <c r="O59" s="89" t="s">
-        <v>173</v>
-      </c>
-      <c r="P59" s="89" t="s">
+      <c r="O59" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="P59" s="88" t="s">
         <v>499</v>
       </c>
-      <c r="Q59" s="89" t="b">
+      <c r="Q59" s="88" t="b">
         <v>1</v>
       </c>
       <c r="R59" s="56"/>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A60" s="103"/>
-      <c r="B60" s="88" t="s">
+      <c r="A60" s="92"/>
+      <c r="B60" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C60" s="88" t="str" cm="1">
+      <c r="C60" s="87" t="str" cm="1">
         <f t="array" ref="C60">UPPER(INDEX(_xlfn.TEXTSPLIT($D60, "-"), 3))</f>
         <v>COM</v>
       </c>
-      <c r="D60" s="88" t="s">
+      <c r="D60" s="87" t="s">
         <v>437</v>
       </c>
-      <c r="E60" s="94" t="s">
+      <c r="E60" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="F60" s="88" t="s">
+      <c r="F60" s="87" t="s">
         <v>441</v>
       </c>
-      <c r="G60" s="88" t="str">
+      <c r="G60" s="87" t="str">
         <f t="shared" si="0"/>
         <v>d-com-proxy01-disk01</v>
       </c>
-      <c r="H60" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="I60" s="88">
-        <v>64</v>
-      </c>
-      <c r="J60" s="88" t="str">
+      <c r="H60" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="I60" s="87">
+        <v>64</v>
+      </c>
+      <c r="J60" s="87" t="str">
         <f t="shared" si="1"/>
         <v>d-com-proxy01-disk02</v>
       </c>
-      <c r="K60" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="L60" s="88">
-        <v>64</v>
-      </c>
-      <c r="M60" s="88">
-        <v>1</v>
-      </c>
-      <c r="N60" s="88" t="s">
+      <c r="K60" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="L60" s="87">
+        <v>64</v>
+      </c>
+      <c r="M60" s="87">
+        <v>1</v>
+      </c>
+      <c r="N60" s="87" t="s">
         <v>502</v>
       </c>
-      <c r="O60" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="P60" s="88" t="s">
+      <c r="O60" s="87" t="s">
+        <v>173</v>
+      </c>
+      <c r="P60" s="87" t="s">
         <v>499</v>
       </c>
-      <c r="Q60" s="88" t="b">
-        <v>1</v>
-      </c>
-      <c r="R60" s="86"/>
+      <c r="Q60" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="R60" s="85"/>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A61" s="95"/>
-      <c r="B61" s="89" t="s">
+      <c r="A61" s="94"/>
+      <c r="B61" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C61" s="89"/>
-      <c r="D61" s="89" t="s">
+      <c r="C61" s="88" t="str" cm="1">
+        <f t="array" ref="C61">UPPER(INDEX(_xlfn.TEXTSPLIT($D61, "-"), 3))</f>
+        <v>IF</v>
+      </c>
+      <c r="D61" s="88" t="s">
         <v>444</v>
       </c>
-      <c r="E61" s="96" t="s">
+      <c r="E61" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="F61" s="89" t="s">
+      <c r="F61" s="88" t="s">
         <v>445</v>
       </c>
-      <c r="G61" s="89" t="str">
+      <c r="G61" s="88" t="str">
         <f t="shared" si="0"/>
         <v>d-if-gramon01-disk01</v>
       </c>
-      <c r="H61" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="I61" s="89">
-        <v>64</v>
-      </c>
-      <c r="J61" s="89" t="str">
+      <c r="H61" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="I61" s="88">
+        <v>64</v>
+      </c>
+      <c r="J61" s="88" t="str">
         <f t="shared" si="1"/>
         <v>d-if-gramon01-disk02</v>
       </c>
-      <c r="K61" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="L61" s="89">
-        <v>64</v>
-      </c>
-      <c r="M61" s="89">
-        <v>1</v>
-      </c>
-      <c r="N61" s="89" t="s">
+      <c r="K61" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="L61" s="88">
+        <v>64</v>
+      </c>
+      <c r="M61" s="88">
+        <v>1</v>
+      </c>
+      <c r="N61" s="88" t="s">
         <v>502</v>
       </c>
-      <c r="O61" s="89" t="s">
-        <v>173</v>
-      </c>
-      <c r="P61" s="89" t="s">
+      <c r="O61" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="P61" s="88" t="s">
         <v>499</v>
       </c>
-      <c r="Q61" s="89" t="b">
+      <c r="Q61" s="88" t="b">
         <v>1</v>
       </c>
       <c r="R61" s="56"/>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A62" s="98"/>
-      <c r="B62" s="88" t="s">
+      <c r="A62" s="96"/>
+      <c r="B62" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C62" s="88"/>
-      <c r="D62" s="88" t="s">
+      <c r="C62" s="87" t="str" cm="1">
+        <f t="array" ref="C62">UPPER(INDEX(_xlfn.TEXTSPLIT($D62, "-"), 3))</f>
+        <v>CS</v>
+      </c>
+      <c r="D62" s="87" t="s">
         <v>175</v>
       </c>
-      <c r="E62" s="94" t="s">
+      <c r="E62" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="F62" s="88" t="s">
+      <c r="F62" s="87" t="s">
         <v>448</v>
       </c>
-      <c r="G62" s="88" t="str">
+      <c r="G62" s="87" t="str">
         <f t="shared" si="0"/>
         <v>d-cs-chtap01-disk01</v>
       </c>
-      <c r="H62" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="I62" s="88">
-        <v>64</v>
-      </c>
-      <c r="J62" s="88" t="str">
+      <c r="H62" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="I62" s="87">
+        <v>64</v>
+      </c>
+      <c r="J62" s="87" t="str">
         <f t="shared" si="1"/>
         <v>d-cs-chtap01-disk02</v>
       </c>
-      <c r="K62" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="L62" s="88">
-        <v>64</v>
-      </c>
-      <c r="M62" s="88">
-        <v>1</v>
-      </c>
-      <c r="N62" s="88" t="s">
+      <c r="K62" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="L62" s="87">
+        <v>64</v>
+      </c>
+      <c r="M62" s="87">
+        <v>1</v>
+      </c>
+      <c r="N62" s="87" t="s">
         <v>502</v>
       </c>
-      <c r="O62" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="P62" s="88" t="s">
+      <c r="O62" s="87" t="s">
+        <v>173</v>
+      </c>
+      <c r="P62" s="87" t="s">
         <v>499</v>
       </c>
-      <c r="Q62" s="88" t="b">
-        <v>1</v>
-      </c>
-      <c r="R62" s="86"/>
+      <c r="Q62" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="R62" s="85"/>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A63" s="98"/>
-      <c r="B63" s="89" t="s">
+      <c r="A63" s="96"/>
+      <c r="B63" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C63" s="89"/>
-      <c r="D63" s="89" t="s">
+      <c r="C63" s="88" t="str" cm="1">
+        <f t="array" ref="C63">UPPER(INDEX(_xlfn.TEXTSPLIT($D63, "-"), 3))</f>
+        <v>CS</v>
+      </c>
+      <c r="D63" s="88" t="s">
         <v>451</v>
       </c>
-      <c r="E63" s="96" t="s">
+      <c r="E63" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="F63" s="89" t="s">
+      <c r="F63" s="88" t="s">
         <v>452</v>
       </c>
-      <c r="G63" s="89" t="str">
+      <c r="G63" s="88" t="str">
         <f t="shared" si="0"/>
         <v>d-cs-chtweb01-disk01</v>
       </c>
-      <c r="H63" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="I63" s="89">
-        <v>64</v>
-      </c>
-      <c r="J63" s="89" t="str">
+      <c r="H63" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="I63" s="88">
+        <v>64</v>
+      </c>
+      <c r="J63" s="88" t="str">
         <f t="shared" si="1"/>
         <v>d-cs-chtweb01-disk02</v>
       </c>
-      <c r="K63" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="L63" s="89">
-        <v>64</v>
-      </c>
-      <c r="M63" s="89">
-        <v>1</v>
-      </c>
-      <c r="N63" s="89" t="s">
+      <c r="K63" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="L63" s="88">
+        <v>64</v>
+      </c>
+      <c r="M63" s="88">
+        <v>1</v>
+      </c>
+      <c r="N63" s="88" t="s">
         <v>502</v>
       </c>
-      <c r="O63" s="89" t="s">
-        <v>173</v>
-      </c>
-      <c r="P63" s="89" t="s">
+      <c r="O63" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="P63" s="88" t="s">
         <v>499</v>
       </c>
-      <c r="Q63" s="89" t="b">
+      <c r="Q63" s="88" t="b">
         <v>1</v>
       </c>
       <c r="R63" s="56"/>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A64" s="99"/>
-      <c r="B64" s="88" t="s">
+      <c r="A64" s="97"/>
+      <c r="B64" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C64" s="88"/>
-      <c r="D64" s="88" t="s">
+      <c r="C64" s="87" t="str" cm="1">
+        <f t="array" ref="C64">UPPER(INDEX(_xlfn.TEXTSPLIT($D64, "-"), 3))</f>
+        <v>CS</v>
+      </c>
+      <c r="D64" s="87" t="s">
         <v>451</v>
       </c>
-      <c r="E64" s="94" t="s">
+      <c r="E64" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="F64" s="88" t="s">
+      <c r="F64" s="87" t="s">
         <v>455</v>
       </c>
-      <c r="G64" s="88" t="str">
+      <c r="G64" s="87" t="str">
         <f t="shared" si="0"/>
         <v>d-cs-chtintweb01-disk01</v>
       </c>
-      <c r="H64" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="I64" s="88">
-        <v>64</v>
-      </c>
-      <c r="J64" s="88" t="str">
+      <c r="H64" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="I64" s="87">
+        <v>64</v>
+      </c>
+      <c r="J64" s="87" t="str">
         <f t="shared" si="1"/>
         <v>d-cs-chtintweb01-disk02</v>
       </c>
-      <c r="K64" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="L64" s="88">
-        <v>64</v>
-      </c>
-      <c r="M64" s="88">
-        <v>1</v>
-      </c>
-      <c r="N64" s="88" t="s">
+      <c r="K64" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="L64" s="87">
+        <v>64</v>
+      </c>
+      <c r="M64" s="87">
+        <v>1</v>
+      </c>
+      <c r="N64" s="87" t="s">
         <v>502</v>
       </c>
-      <c r="O64" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="P64" s="88" t="s">
+      <c r="O64" s="87" t="s">
+        <v>173</v>
+      </c>
+      <c r="P64" s="87" t="s">
         <v>499</v>
       </c>
-      <c r="Q64" s="88" t="b">
-        <v>1</v>
-      </c>
-      <c r="R64" s="86"/>
+      <c r="Q64" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="R64" s="85"/>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A65" s="93"/>
-      <c r="B65" s="89" t="s">
+      <c r="A65" s="92"/>
+      <c r="B65" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C65" s="89"/>
-      <c r="D65" s="89" t="s">
+      <c r="C65" s="88" t="str" cm="1">
+        <f t="array" ref="C65">UPPER(INDEX(_xlfn.TEXTSPLIT($D65, "-"), 3))</f>
+        <v>DOIP</v>
+      </c>
+      <c r="D65" s="88" t="s">
         <v>457</v>
       </c>
-      <c r="E65" s="96" t="s">
+      <c r="E65" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="F65" s="89" t="s">
+      <c r="F65" s="88" t="s">
         <v>458</v>
       </c>
-      <c r="G65" s="89" t="str">
+      <c r="G65" s="88" t="str">
         <f t="shared" si="0"/>
         <v>d-doip-web01-disk01</v>
       </c>
-      <c r="H65" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="I65" s="89">
-        <v>64</v>
-      </c>
-      <c r="J65" s="89" t="str">
+      <c r="H65" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="I65" s="88">
+        <v>64</v>
+      </c>
+      <c r="J65" s="88" t="str">
         <f t="shared" si="1"/>
         <v>d-doip-web01-disk02</v>
       </c>
-      <c r="K65" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="L65" s="89">
-        <v>64</v>
-      </c>
-      <c r="M65" s="89">
-        <v>1</v>
-      </c>
-      <c r="N65" s="89" t="s">
+      <c r="K65" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="L65" s="88">
+        <v>64</v>
+      </c>
+      <c r="M65" s="88">
+        <v>1</v>
+      </c>
+      <c r="N65" s="88" t="s">
         <v>502</v>
       </c>
-      <c r="O65" s="89" t="s">
-        <v>173</v>
-      </c>
-      <c r="P65" s="89" t="s">
+      <c r="O65" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="P65" s="88" t="s">
         <v>499</v>
       </c>
-      <c r="Q65" s="89" t="b">
+      <c r="Q65" s="88" t="b">
         <v>1</v>
       </c>
       <c r="R65" s="56"/>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A66" s="95"/>
-      <c r="B66" s="88" t="s">
+      <c r="A66" s="94"/>
+      <c r="B66" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C66" s="88"/>
-      <c r="D66" s="88" t="s">
+      <c r="C66" s="87" t="str" cm="1">
+        <f t="array" ref="C66">UPPER(INDEX(_xlfn.TEXTSPLIT($D66, "-"), 3))</f>
+        <v>DOIP</v>
+      </c>
+      <c r="D66" s="87" t="s">
         <v>457</v>
       </c>
-      <c r="E66" s="94" t="s">
+      <c r="E66" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="F66" s="88" t="s">
+      <c r="F66" s="87" t="s">
         <v>461</v>
       </c>
-      <c r="G66" s="88" t="str">
+      <c r="G66" s="87" t="str">
         <f t="shared" si="0"/>
         <v>d-doip-ap01-disk01</v>
       </c>
-      <c r="H66" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="I66" s="88">
-        <v>64</v>
-      </c>
-      <c r="J66" s="88" t="str">
+      <c r="H66" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="I66" s="87">
+        <v>64</v>
+      </c>
+      <c r="J66" s="87" t="str">
         <f t="shared" si="1"/>
         <v>d-doip-ap01-disk02</v>
       </c>
-      <c r="K66" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="L66" s="88">
-        <v>64</v>
-      </c>
-      <c r="M66" s="88">
-        <v>1</v>
-      </c>
-      <c r="N66" s="88" t="s">
+      <c r="K66" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="L66" s="87">
+        <v>64</v>
+      </c>
+      <c r="M66" s="87">
+        <v>1</v>
+      </c>
+      <c r="N66" s="87" t="s">
         <v>502</v>
       </c>
-      <c r="O66" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="P66" s="88" t="s">
+      <c r="O66" s="87" t="s">
+        <v>173</v>
+      </c>
+      <c r="P66" s="87" t="s">
         <v>499</v>
       </c>
-      <c r="Q66" s="88" t="b">
-        <v>1</v>
-      </c>
-      <c r="R66" s="86"/>
+      <c r="Q66" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="R66" s="85"/>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A67" s="93"/>
-      <c r="B67" s="89" t="s">
+      <c r="A67" s="92"/>
+      <c r="B67" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C67" s="89"/>
-      <c r="D67" s="89" t="s">
+      <c r="C67" s="88" t="str" cm="1">
+        <f t="array" ref="C67">UPPER(INDEX(_xlfn.TEXTSPLIT($D67, "-"), 3))</f>
+        <v>DOIP</v>
+      </c>
+      <c r="D67" s="88" t="s">
         <v>457</v>
       </c>
-      <c r="E67" s="96" t="s">
+      <c r="E67" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="F67" s="89" t="s">
+      <c r="F67" s="88" t="s">
         <v>463</v>
       </c>
-      <c r="G67" s="89" t="str">
+      <c r="G67" s="88" t="str">
         <f>SUBSTITUTE($F67,"hazr-","")&amp;"-disk01"</f>
         <v>d-doip-adm01-disk01</v>
       </c>
-      <c r="H67" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="I67" s="89">
-        <v>64</v>
-      </c>
-      <c r="J67" s="89" t="str">
+      <c r="H67" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="I67" s="88">
+        <v>64</v>
+      </c>
+      <c r="J67" s="88" t="str">
         <f>SUBSTITUTE($F67,"hazr-","")&amp;"-disk02"</f>
         <v>d-doip-adm01-disk02</v>
       </c>
-      <c r="K67" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="L67" s="89">
-        <v>64</v>
-      </c>
-      <c r="M67" s="89">
-        <v>1</v>
-      </c>
-      <c r="N67" s="89" t="s">
+      <c r="K67" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="L67" s="88">
+        <v>64</v>
+      </c>
+      <c r="M67" s="88">
+        <v>1</v>
+      </c>
+      <c r="N67" s="88" t="s">
         <v>502</v>
       </c>
-      <c r="O67" s="89" t="s">
-        <v>173</v>
-      </c>
-      <c r="P67" s="89" t="s">
+      <c r="O67" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="P67" s="88" t="s">
         <v>499</v>
       </c>
-      <c r="Q67" s="89" t="b">
+      <c r="Q67" s="88" t="b">
         <v>1</v>
       </c>
       <c r="R67" s="56"/>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A68" s="102"/>
-      <c r="B68" s="88" t="s">
+      <c r="A68" s="94"/>
+      <c r="B68" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C68" s="88" t="str" cm="1">
+      <c r="C68" s="87" t="str" cm="1">
         <f t="array" ref="C68">UPPER(INDEX(_xlfn.TEXTSPLIT($D68, "-"), 3))</f>
         <v>BDP</v>
       </c>
-      <c r="D68" s="88" t="s">
+      <c r="D68" s="87" t="s">
         <v>403</v>
       </c>
-      <c r="E68" s="94" t="s">
+      <c r="E68" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="F68" s="88" t="s">
+      <c r="F68" s="87" t="s">
         <v>465</v>
       </c>
-      <c r="G68" s="88" t="str">
+      <c r="G68" s="87" t="str">
         <f>SUBSTITUTE($F68,"hazr-","")&amp;"-disk01"</f>
         <v>d-bdp-crkweb01-disk01</v>
       </c>
-      <c r="H68" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="I68" s="88">
-        <v>64</v>
-      </c>
-      <c r="J68" s="88" t="str">
+      <c r="H68" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="I68" s="87">
+        <v>64</v>
+      </c>
+      <c r="J68" s="87" t="str">
         <f>SUBSTITUTE($F68,"hazr-","")&amp;"-disk02"</f>
         <v>d-bdp-crkweb01-disk02</v>
       </c>
-      <c r="K68" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="L68" s="88">
-        <v>64</v>
-      </c>
-      <c r="M68" s="88">
-        <v>1</v>
-      </c>
-      <c r="N68" s="88" t="s">
+      <c r="K68" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="L68" s="87">
+        <v>64</v>
+      </c>
+      <c r="M68" s="87">
+        <v>1</v>
+      </c>
+      <c r="N68" s="87" t="s">
         <v>502</v>
       </c>
-      <c r="O68" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="P68" s="88" t="s">
+      <c r="O68" s="87" t="s">
+        <v>173</v>
+      </c>
+      <c r="P68" s="87" t="s">
         <v>499</v>
       </c>
-      <c r="Q68" s="88" t="b">
-        <v>1</v>
-      </c>
-      <c r="R68" s="86"/>
+      <c r="Q68" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="R68" s="85"/>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A69" s="93"/>
-      <c r="B69" s="89" t="s">
+      <c r="A69" s="92"/>
+      <c r="B69" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C69" s="89"/>
-      <c r="D69" s="89" t="s">
+      <c r="C69" s="88" t="str" cm="1">
+        <f t="array" ref="C69">UPPER(INDEX(_xlfn.TEXTSPLIT($D69, "-"), 3))</f>
+        <v>BDP</v>
+      </c>
+      <c r="D69" s="88" t="s">
         <v>403</v>
       </c>
-      <c r="E69" s="96" t="s">
+      <c r="E69" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="F69" s="89" t="s">
+      <c r="F69" s="88" t="s">
         <v>507</v>
       </c>
-      <c r="G69" s="89" t="str">
+      <c r="G69" s="88" t="str">
         <f>SUBSTITUTE($F69,"hazr-","")&amp;"-disk01"</f>
         <v>d-bdp-crkap01-disk01</v>
       </c>
-      <c r="H69" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="I69" s="89">
-        <v>64</v>
-      </c>
-      <c r="J69" s="89" t="str">
+      <c r="H69" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="I69" s="88">
+        <v>64</v>
+      </c>
+      <c r="J69" s="88" t="str">
         <f>SUBSTITUTE($F69,"hazr-","")&amp;"-disk02"</f>
         <v>d-bdp-crkap01-disk02</v>
       </c>
-      <c r="K69" s="89" t="s">
-        <v>472</v>
-      </c>
-      <c r="L69" s="89">
-        <v>64</v>
-      </c>
-      <c r="M69" s="89">
-        <v>1</v>
-      </c>
-      <c r="N69" s="89" t="s">
+      <c r="K69" s="88" t="s">
+        <v>472</v>
+      </c>
+      <c r="L69" s="88">
+        <v>64</v>
+      </c>
+      <c r="M69" s="88">
+        <v>1</v>
+      </c>
+      <c r="N69" s="88" t="s">
         <v>502</v>
       </c>
-      <c r="O69" s="89" t="s">
-        <v>173</v>
-      </c>
-      <c r="P69" s="89" t="s">
+      <c r="O69" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="P69" s="88" t="s">
         <v>499</v>
       </c>
-      <c r="Q69" s="89" t="b">
+      <c r="Q69" s="88" t="b">
         <v>1</v>
       </c>
       <c r="R69" s="56"/>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A70" s="95"/>
-      <c r="B70" s="88" t="s">
+      <c r="A70" s="94"/>
+      <c r="B70" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C70" s="88"/>
-      <c r="D70" s="88" t="s">
+      <c r="C70" s="87" t="str" cm="1">
+        <f t="array" ref="C70">UPPER(INDEX(_xlfn.TEXTSPLIT($D70, "-"), 3))</f>
+        <v>BDP</v>
+      </c>
+      <c r="D70" s="87" t="s">
         <v>403</v>
       </c>
-      <c r="E70" s="94" t="s">
+      <c r="E70" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="F70" s="88" t="s">
+      <c r="F70" s="87" t="s">
         <v>470</v>
       </c>
-      <c r="G70" s="88" t="str">
+      <c r="G70" s="87" t="str">
         <f>SUBSTITUTE($F70,"hazr-","")&amp;"-disk01"</f>
         <v>d-bdp-crkml01-disk01</v>
       </c>
-      <c r="H70" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="I70" s="88">
-        <v>64</v>
-      </c>
-      <c r="J70" s="88" t="str">
+      <c r="H70" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="I70" s="87">
+        <v>64</v>
+      </c>
+      <c r="J70" s="87" t="str">
         <f>SUBSTITUTE($F70,"hazr-","")&amp;"-disk02"</f>
         <v>d-bdp-crkml01-disk02</v>
       </c>
-      <c r="K70" s="88" t="s">
-        <v>472</v>
-      </c>
-      <c r="L70" s="88">
-        <v>64</v>
-      </c>
-      <c r="M70" s="88">
-        <v>1</v>
-      </c>
-      <c r="N70" s="88" t="s">
+      <c r="K70" s="87" t="s">
+        <v>472</v>
+      </c>
+      <c r="L70" s="87">
+        <v>64</v>
+      </c>
+      <c r="M70" s="87">
+        <v>1</v>
+      </c>
+      <c r="N70" s="87" t="s">
         <v>502</v>
       </c>
-      <c r="O70" s="88" t="s">
-        <v>173</v>
-      </c>
-      <c r="P70" s="88" t="s">
+      <c r="O70" s="87" t="s">
+        <v>173</v>
+      </c>
+      <c r="P70" s="87" t="s">
         <v>499</v>
       </c>
-      <c r="Q70" s="88" t="b">
-        <v>1</v>
-      </c>
-      <c r="R70" s="86"/>
+      <c r="Q70" s="87" t="b">
+        <v>1</v>
+      </c>
+      <c r="R70" s="85"/>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A71" s="93"/>
-      <c r="B71" s="89" t="s">
+      <c r="A71" s="92"/>
+      <c r="B71" s="88" t="s">
         <v>81</v>
       </c>
-      <c r="C71" s="89"/>
-      <c r="D71" s="89" t="s">
+      <c r="C71" s="88" t="str" cm="1">
+        <f t="array" ref="C71">UPPER(INDEX(_xlfn.TEXTSPLIT($D71, "-"), 3))</f>
+        <v>DIS</v>
+      </c>
+      <c r="D71" s="88" t="s">
         <v>310</v>
       </c>
-      <c r="E71" s="96" t="s">
+      <c r="E71" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="F71" s="89" t="s">
+      <c r="F71" s="88" t="s">
         <v>477</v>
       </c>
-      <c r="G71" s="89" t="s">
+      <c r="G71" s="88" t="s">
         <v>506</v>
       </c>
-      <c r="H71" s="89" t="s">
+      <c r="H71" s="88" t="s">
         <v>506</v>
       </c>
-      <c r="I71" s="89" t="s">
+      <c r="I71" s="88" t="s">
         <v>506</v>
       </c>
-      <c r="J71" s="89" t="s">
+      <c r="J71" s="88" t="s">
         <v>506</v>
       </c>
-      <c r="K71" s="89" t="s">
+      <c r="K71" s="88" t="s">
         <v>506</v>
       </c>
-      <c r="L71" s="89" t="s">
+      <c r="L71" s="88" t="s">
         <v>506</v>
       </c>
-      <c r="M71" s="89" t="s">
+      <c r="M71" s="88" t="s">
         <v>506</v>
       </c>
-      <c r="N71" s="89" t="s">
+      <c r="N71" s="88" t="s">
         <v>506</v>
       </c>
-      <c r="O71" s="89" t="s">
-        <v>173</v>
-      </c>
-      <c r="P71" s="89" t="s">
+      <c r="O71" s="88" t="s">
+        <v>173</v>
+      </c>
+      <c r="P71" s="88" t="s">
         <v>506</v>
       </c>
-      <c r="Q71" s="89" t="s">
+      <c r="Q71" s="88" t="s">
         <v>506</v>
       </c>
       <c r="R71" s="56"/>
@@ -18477,12 +18740,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18630,15 +18890,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -18662,17 +18933,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260422_리소스배포_개발.xlsx
+++ b/서버정보/20260422_리소스배포_개발.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{659E04C8-5D41-4F8D-8292-62014530DD05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0976570E-DE66-440E-850A-39E02A576255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18740,9 +18740,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18890,26 +18893,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -18933,9 +18925,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260422_리소스배포_개발.xlsx
+++ b/서버정보/20260422_리소스배포_개발.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{544FE2C4-4581-4F39-857A-A17D47D62F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{972AD4F9-4A2F-40C8-9D3C-A67CD6E63158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -45,7 +45,7 @@
     <author>zenithn</author>
   </authors>
   <commentList>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{4E95A42A-EE05-46FF-9ADE-8C06C9CCADD3}">
+    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{4E95A42A-EE05-46FF-9ADE-8C06C9CCADD3}">
       <text>
         <r>
           <rPr>
@@ -573,7 +573,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2435" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2504" uniqueCount="431">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2079,6 +2079,10 @@
   </si>
   <si>
     <t>d-dis-cs-sbn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NicRG</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -14214,7 +14218,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAB1F184-7BFC-47CB-AC71-63C76B7E3D12}">
-  <dimension ref="A1:K69"/>
+  <dimension ref="A1:L69"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.75" customWidth="1"/>
@@ -14223,11 +14227,11 @@
     <col min="6" max="6" width="12.25" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.5" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="9" max="10" width="18.5" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B1" s="29" t="s">
         <v>0</v>
       </c>
@@ -14253,13 +14257,16 @@
         <v>356</v>
       </c>
       <c r="J1" s="31" t="s">
+        <v>430</v>
+      </c>
+      <c r="K1" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="K1" s="31" t="s">
+      <c r="L1" s="31" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B2" s="33" t="s">
         <v>31</v>
       </c>
@@ -14286,15 +14293,18 @@
       <c r="I2" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="J2" s="33" t="str">
+      <c r="J2" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="K2" s="33" t="str">
         <f>SUBSTITUTE($I2,"hazr-","")&amp;"-nic"</f>
         <v>d-dis-ap01-nic</v>
       </c>
-      <c r="K2" s="34" t="s">
+      <c r="L2" s="34" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="35" t="s">
         <v>31</v>
       </c>
@@ -14321,15 +14331,18 @@
       <c r="I3" s="24" t="s">
         <v>377</v>
       </c>
-      <c r="J3" s="35" t="str">
+      <c r="J3" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K3" s="35" t="str">
         <f>SUBSTITUTE($I3,"hazr-","")&amp;"-nic"</f>
         <v>d-dis-adm01-nic</v>
       </c>
-      <c r="K3" s="37" t="s">
+      <c r="L3" s="37" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" s="33" t="s">
         <v>31</v>
       </c>
@@ -14356,15 +14369,18 @@
       <c r="I4" s="22" t="s">
         <v>378</v>
       </c>
-      <c r="J4" s="33" t="str">
-        <f t="shared" ref="J4:J68" si="1">SUBSTITUTE($I4,"hazr-","")&amp;"-nic"</f>
+      <c r="J4" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="K4" s="33" t="str">
+        <f t="shared" ref="K4:K68" si="1">SUBSTITUTE($I4,"hazr-","")&amp;"-nic"</f>
         <v>d-dis-bbiweb01-nic</v>
       </c>
-      <c r="K4" s="34" t="s">
+      <c r="L4" s="34" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="35" t="s">
         <v>31</v>
       </c>
@@ -14391,15 +14407,18 @@
       <c r="I5" s="24" t="s">
         <v>407</v>
       </c>
-      <c r="J5" s="35" t="str">
+      <c r="J5" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K5" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-dis-bbicltap01-nic</v>
       </c>
-      <c r="K5" s="37" t="s">
+      <c r="L5" s="37" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="36" t="s">
         <v>31</v>
       </c>
@@ -14426,15 +14445,18 @@
       <c r="I6" s="22" t="s">
         <v>203</v>
       </c>
-      <c r="J6" s="33" t="str">
+      <c r="J6" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="K6" s="33" t="str">
         <f t="shared" si="1"/>
         <v>d-dis-bbimsgap01-nic</v>
       </c>
-      <c r="K6" s="34" t="s">
+      <c r="L6" s="34" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="35" t="s">
         <v>31</v>
       </c>
@@ -14461,15 +14483,18 @@
       <c r="I7" s="24" t="s">
         <v>408</v>
       </c>
-      <c r="J7" s="35" t="str">
+      <c r="J7" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K7" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-dis-walkap01-nic</v>
       </c>
-      <c r="K7" s="37" t="s">
+      <c r="L7" s="37" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="36" t="s">
         <v>31</v>
       </c>
@@ -14496,15 +14521,18 @@
       <c r="I8" s="22" t="s">
         <v>207</v>
       </c>
-      <c r="J8" s="33" t="str">
+      <c r="J8" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="K8" s="33" t="str">
         <f t="shared" si="1"/>
         <v>d-dis-bat01-nic</v>
       </c>
-      <c r="K8" s="34" t="s">
+      <c r="L8" s="34" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="35" t="s">
         <v>31</v>
       </c>
@@ -14531,15 +14559,18 @@
       <c r="I9" s="24" t="s">
         <v>381</v>
       </c>
-      <c r="J9" s="35" t="str">
+      <c r="J9" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K9" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-dis-drvcltap01-nic</v>
       </c>
-      <c r="K9" s="37" t="s">
+      <c r="L9" s="37" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="36" t="s">
         <v>31</v>
       </c>
@@ -14566,15 +14597,18 @@
       <c r="I10" s="22" t="s">
         <v>211</v>
       </c>
-      <c r="J10" s="33" t="str">
+      <c r="J10" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="K10" s="33" t="str">
         <f t="shared" si="1"/>
         <v>d-dis-walkweb01-nic</v>
       </c>
-      <c r="K10" s="34" t="s">
+      <c r="L10" s="34" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="35" t="s">
         <v>31</v>
       </c>
@@ -14601,15 +14635,18 @@
       <c r="I11" s="24" t="s">
         <v>409</v>
       </c>
-      <c r="J11" s="35" t="str">
+      <c r="J11" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K11" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-dis-drvmsgap01-nic</v>
       </c>
-      <c r="K11" s="37" t="s">
+      <c r="L11" s="37" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="36" t="s">
         <v>31</v>
       </c>
@@ -14636,15 +14673,18 @@
       <c r="I12" s="22" t="s">
         <v>382</v>
       </c>
-      <c r="J12" s="33" t="str">
+      <c r="J12" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="K12" s="33" t="str">
         <f t="shared" si="1"/>
         <v>d-dis-web01-nic</v>
       </c>
-      <c r="K12" s="34" t="s">
+      <c r="L12" s="34" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="35" t="s">
         <v>31</v>
       </c>
@@ -14671,15 +14711,18 @@
       <c r="I13" s="24" t="s">
         <v>383</v>
       </c>
-      <c r="J13" s="35" t="str">
+      <c r="J13" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K13" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-dis-cmsadm01-nic</v>
       </c>
-      <c r="K13" s="37" t="s">
+      <c r="L13" s="37" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="36" t="s">
         <v>31</v>
       </c>
@@ -14706,15 +14749,18 @@
       <c r="I14" s="22" t="s">
         <v>219</v>
       </c>
-      <c r="J14" s="33" t="str">
+      <c r="J14" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="K14" s="33" t="str">
         <f t="shared" si="1"/>
         <v>d-dis-cmsap01-nic</v>
       </c>
-      <c r="K14" s="34" t="s">
+      <c r="L14" s="34" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="35" t="s">
         <v>31</v>
       </c>
@@ -14741,15 +14787,18 @@
       <c r="I15" s="24" t="s">
         <v>380</v>
       </c>
-      <c r="J15" s="35" t="str">
+      <c r="J15" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K15" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-dis-cmsweb01-nic</v>
       </c>
-      <c r="K15" s="37" t="s">
+      <c r="L15" s="37" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" s="36" t="s">
         <v>31</v>
       </c>
@@ -14776,15 +14825,18 @@
       <c r="I16" s="22" t="s">
         <v>402</v>
       </c>
-      <c r="J16" s="33" t="str">
+      <c r="J16" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="K16" s="33" t="str">
         <f t="shared" si="1"/>
         <v>d-dis-cmbsap01-nic</v>
       </c>
-      <c r="K16" s="34" t="s">
+      <c r="L16" s="34" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="35" t="s">
         <v>31</v>
       </c>
@@ -14811,15 +14863,18 @@
       <c r="I17" s="24" t="s">
         <v>410</v>
       </c>
-      <c r="J17" s="35" t="str">
+      <c r="J17" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="K17" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-ingap01-nic</v>
       </c>
-      <c r="K17" s="37" t="s">
+      <c r="L17" s="37" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="36" t="s">
         <v>31</v>
       </c>
@@ -14846,15 +14901,18 @@
       <c r="I18" s="22" t="s">
         <v>229</v>
       </c>
-      <c r="J18" s="33" t="str">
+      <c r="J18" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="K18" s="33" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-ap01-nic</v>
       </c>
-      <c r="K18" s="34" t="s">
+      <c r="L18" s="34" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="35" t="s">
         <v>31</v>
       </c>
@@ -14881,15 +14939,18 @@
       <c r="I19" s="24" t="s">
         <v>411</v>
       </c>
-      <c r="J19" s="35" t="str">
+      <c r="J19" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="K19" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-extgeoap01-nic</v>
       </c>
-      <c r="K19" s="37" t="s">
+      <c r="L19" s="37" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="36" t="s">
         <v>31</v>
       </c>
@@ -14916,15 +14977,18 @@
       <c r="I20" s="22" t="s">
         <v>233</v>
       </c>
-      <c r="J20" s="33" t="str">
+      <c r="J20" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="K20" s="33" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-geoap01-nic</v>
       </c>
-      <c r="K20" s="34" t="s">
+      <c r="L20" s="34" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="35" t="s">
         <v>31</v>
       </c>
@@ -14951,15 +15015,18 @@
       <c r="I21" s="24" t="s">
         <v>412</v>
       </c>
-      <c r="J21" s="35" t="str">
+      <c r="J21" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="K21" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-mq01-nic</v>
       </c>
-      <c r="K21" s="37" t="s">
+      <c r="L21" s="37" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="36" t="s">
         <v>31</v>
       </c>
@@ -14986,15 +15053,18 @@
       <c r="I22" s="22" t="s">
         <v>384</v>
       </c>
-      <c r="J22" s="33" t="str">
+      <c r="J22" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="K22" s="33" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-admweb01-nic</v>
       </c>
-      <c r="K22" s="34" t="s">
+      <c r="L22" s="34" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="35" t="s">
         <v>31</v>
       </c>
@@ -15021,15 +15091,18 @@
       <c r="I23" s="24" t="s">
         <v>385</v>
       </c>
-      <c r="J23" s="35" t="str">
+      <c r="J23" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="K23" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-admap01-nic</v>
       </c>
-      <c r="K23" s="37" t="s">
+      <c r="L23" s="37" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="36" t="s">
         <v>31</v>
       </c>
@@ -15056,15 +15129,18 @@
       <c r="I24" s="22" t="s">
         <v>242</v>
       </c>
-      <c r="J24" s="33" t="str">
+      <c r="J24" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="K24" s="33" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-dtoms01-nic</v>
       </c>
-      <c r="K24" s="34" t="s">
+      <c r="L24" s="34" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="35" t="s">
         <v>31</v>
       </c>
@@ -15091,15 +15167,18 @@
       <c r="I25" s="24" t="s">
         <v>386</v>
       </c>
-      <c r="J25" s="35" t="str">
+      <c r="J25" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="K25" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-tsdb01-nic</v>
       </c>
-      <c r="K25" s="37" t="s">
+      <c r="L25" s="37" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" s="36" t="s">
         <v>31</v>
       </c>
@@ -15126,15 +15205,18 @@
       <c r="I26" s="22" t="s">
         <v>387</v>
       </c>
-      <c r="J26" s="33" t="str">
+      <c r="J26" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="K26" s="33" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-web01-nic</v>
       </c>
-      <c r="K26" s="34" t="s">
+      <c r="L26" s="34" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B27" s="35" t="s">
         <v>31</v>
       </c>
@@ -15161,15 +15243,18 @@
       <c r="I27" s="24" t="s">
         <v>413</v>
       </c>
-      <c r="J27" s="35" t="str">
+      <c r="J27" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="K27" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-zkp01-nic</v>
       </c>
-      <c r="K27" s="37" t="s">
+      <c r="L27" s="37" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B28" s="36" t="s">
         <v>31</v>
       </c>
@@ -15196,15 +15281,18 @@
       <c r="I28" s="22" t="s">
         <v>252</v>
       </c>
-      <c r="J28" s="33" t="str">
+      <c r="J28" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="K28" s="33" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-zkp02-nic</v>
       </c>
-      <c r="K28" s="34" t="s">
+      <c r="L28" s="34" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B29" s="35" t="s">
         <v>31</v>
       </c>
@@ -15231,15 +15319,18 @@
       <c r="I29" s="24" t="s">
         <v>414</v>
       </c>
-      <c r="J29" s="35" t="str">
+      <c r="J29" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="K29" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-zkp03-nic</v>
       </c>
-      <c r="K29" s="37" t="s">
+      <c r="L29" s="37" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B30" s="36" t="s">
         <v>31</v>
       </c>
@@ -15266,15 +15357,18 @@
       <c r="I30" s="22" t="s">
         <v>256</v>
       </c>
-      <c r="J30" s="33" t="str">
+      <c r="J30" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="K30" s="33" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-kfk01-nic</v>
       </c>
-      <c r="K30" s="34" t="s">
+      <c r="L30" s="34" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B31" s="35" t="s">
         <v>31</v>
       </c>
@@ -15301,15 +15395,18 @@
       <c r="I31" s="24" t="s">
         <v>415</v>
       </c>
-      <c r="J31" s="35" t="str">
+      <c r="J31" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="K31" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-kfk02-nic</v>
       </c>
-      <c r="K31" s="37" t="s">
+      <c r="L31" s="37" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B32" s="36" t="s">
         <v>31</v>
       </c>
@@ -15336,15 +15433,18 @@
       <c r="I32" s="22" t="s">
         <v>260</v>
       </c>
-      <c r="J32" s="33" t="str">
+      <c r="J32" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="K32" s="33" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-kfk03-nic</v>
       </c>
-      <c r="K32" s="34" t="s">
+      <c r="L32" s="34" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B33" s="35" t="s">
         <v>31</v>
       </c>
@@ -15371,15 +15471,18 @@
       <c r="I33" s="24" t="s">
         <v>388</v>
       </c>
-      <c r="J33" s="35" t="str">
+      <c r="J33" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="K33" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-mdoms01-nic</v>
       </c>
-      <c r="K33" s="37" t="s">
+      <c r="L33" s="37" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B34" s="36" t="s">
         <v>31</v>
       </c>
@@ -15406,15 +15509,18 @@
       <c r="I34" s="22" t="s">
         <v>264</v>
       </c>
-      <c r="J34" s="33" t="str">
+      <c r="J34" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="K34" s="33" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-cdmlap01-nic</v>
       </c>
-      <c r="K34" s="34" t="s">
+      <c r="L34" s="34" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B35" s="35" t="s">
         <v>31</v>
       </c>
@@ -15441,15 +15547,18 @@
       <c r="I35" s="24" t="s">
         <v>416</v>
       </c>
-      <c r="J35" s="35" t="str">
+      <c r="J35" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="K35" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-cdstap01-nic</v>
       </c>
-      <c r="K35" s="37" t="s">
+      <c r="L35" s="37" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B36" s="36" t="s">
         <v>31</v>
       </c>
@@ -15476,15 +15585,18 @@
       <c r="I36" s="22" t="s">
         <v>373</v>
       </c>
-      <c r="J36" s="33" t="str">
+      <c r="J36" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="K36" s="33" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-cdsvadm01-nic</v>
       </c>
-      <c r="K36" s="34" t="s">
+      <c r="L36" s="34" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B37" s="35" t="s">
         <v>31</v>
       </c>
@@ -15511,15 +15623,18 @@
       <c r="I37" s="24" t="s">
         <v>417</v>
       </c>
-      <c r="J37" s="35" t="str">
+      <c r="J37" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="K37" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-diosap01-nic</v>
       </c>
-      <c r="K37" s="37" t="s">
+      <c r="L37" s="37" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B38" s="36" t="s">
         <v>31</v>
       </c>
@@ -15546,15 +15661,18 @@
       <c r="I38" s="22" t="s">
         <v>389</v>
       </c>
-      <c r="J38" s="33" t="str">
+      <c r="J38" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="K38" s="33" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-diosweb01-nic</v>
       </c>
-      <c r="K38" s="34" t="s">
+      <c r="L38" s="34" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B39" s="35" t="s">
         <v>31</v>
       </c>
@@ -15581,15 +15699,18 @@
       <c r="I39" s="24" t="s">
         <v>390</v>
       </c>
-      <c r="J39" s="35" t="str">
+      <c r="J39" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="K39" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-dprweb01-nic</v>
       </c>
-      <c r="K39" s="37" t="s">
+      <c r="L39" s="37" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B40" s="36" t="s">
         <v>31</v>
       </c>
@@ -15616,15 +15737,18 @@
       <c r="I40" s="22" t="s">
         <v>275</v>
       </c>
-      <c r="J40" s="33" t="str">
+      <c r="J40" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="K40" s="33" t="str">
         <f t="shared" si="1"/>
         <v>d-dtg-dprap01-nic</v>
       </c>
-      <c r="K40" s="34" t="s">
+      <c r="L40" s="34" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B41" s="35" t="s">
         <v>31</v>
       </c>
@@ -15651,15 +15775,18 @@
       <c r="I41" s="24" t="s">
         <v>391</v>
       </c>
-      <c r="J41" s="35" t="str">
+      <c r="J41" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="K41" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-bdp-airfw01-nic</v>
       </c>
-      <c r="K41" s="37" t="s">
+      <c r="L41" s="37" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B42" s="36" t="s">
         <v>31</v>
       </c>
@@ -15686,15 +15813,18 @@
       <c r="I42" s="22" t="s">
         <v>392</v>
       </c>
-      <c r="J42" s="33" t="str">
+      <c r="J42" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="K42" s="33" t="str">
         <f t="shared" si="1"/>
         <v>d-bdp-kepler01-nic</v>
       </c>
-      <c r="K42" s="34" t="s">
+      <c r="L42" s="34" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B43" s="35" t="s">
         <v>31</v>
       </c>
@@ -15721,15 +15851,18 @@
       <c r="I43" s="24" t="s">
         <v>374</v>
       </c>
-      <c r="J43" s="35" t="str">
+      <c r="J43" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="K43" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-bdp-cxmadm01-nic</v>
       </c>
-      <c r="K43" s="37" t="s">
+      <c r="L43" s="37" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B44" s="36" t="s">
         <v>31</v>
       </c>
@@ -15756,15 +15889,18 @@
       <c r="I44" s="22" t="s">
         <v>393</v>
       </c>
-      <c r="J44" s="33" t="str">
+      <c r="J44" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="K44" s="33" t="str">
         <f t="shared" si="1"/>
         <v>d-bdp-slap01-nic</v>
       </c>
-      <c r="K44" s="34" t="s">
+      <c r="L44" s="34" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B45" s="35" t="s">
         <v>31</v>
       </c>
@@ -15791,15 +15927,18 @@
       <c r="I45" s="24" t="s">
         <v>394</v>
       </c>
-      <c r="J45" s="35" t="str">
+      <c r="J45" s="17" t="s">
+        <v>338</v>
+      </c>
+      <c r="K45" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-adm01-nic</v>
       </c>
-      <c r="K45" s="37" t="s">
+      <c r="L45" s="37" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B46" s="36" t="s">
         <v>31</v>
       </c>
@@ -15826,15 +15965,18 @@
       <c r="I46" s="22" t="s">
         <v>395</v>
       </c>
-      <c r="J46" s="33" t="str">
+      <c r="J46" s="16" t="s">
+        <v>338</v>
+      </c>
+      <c r="K46" s="33" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-ap01-nic</v>
       </c>
-      <c r="K46" s="34" t="s">
+      <c r="L46" s="34" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B47" s="35" t="s">
         <v>31</v>
       </c>
@@ -15861,15 +16003,18 @@
       <c r="I47" s="24" t="s">
         <v>418</v>
       </c>
-      <c r="J47" s="35" t="str">
+      <c r="J47" s="17" t="s">
+        <v>338</v>
+      </c>
+      <c r="K47" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-flk01-nic</v>
       </c>
-      <c r="K47" s="37" t="s">
+      <c r="L47" s="37" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B48" s="36" t="s">
         <v>31</v>
       </c>
@@ -15896,15 +16041,18 @@
       <c r="I48" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="J48" s="33" t="str">
+      <c r="J48" s="16" t="s">
+        <v>338</v>
+      </c>
+      <c r="K48" s="33" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-flk02-nic</v>
       </c>
-      <c r="K48" s="34" t="s">
+      <c r="L48" s="34" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B49" s="35" t="s">
         <v>31</v>
       </c>
@@ -15931,15 +16079,18 @@
       <c r="I49" s="24" t="s">
         <v>419</v>
       </c>
-      <c r="J49" s="35" t="str">
+      <c r="J49" s="17" t="s">
+        <v>338</v>
+      </c>
+      <c r="K49" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-flk03-nic</v>
       </c>
-      <c r="K49" s="37" t="s">
+      <c r="L49" s="37" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B50" s="36" t="s">
         <v>31</v>
       </c>
@@ -15966,15 +16117,18 @@
       <c r="I50" s="22" t="s">
         <v>297</v>
       </c>
-      <c r="J50" s="33" t="str">
+      <c r="J50" s="16" t="s">
+        <v>338</v>
+      </c>
+      <c r="K50" s="33" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-geoap01-nic</v>
       </c>
-      <c r="K50" s="34" t="s">
+      <c r="L50" s="34" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B51" s="35" t="s">
         <v>31</v>
       </c>
@@ -16001,15 +16155,18 @@
       <c r="I51" s="24" t="s">
         <v>420</v>
       </c>
-      <c r="J51" s="35" t="str">
+      <c r="J51" s="17" t="s">
+        <v>338</v>
+      </c>
+      <c r="K51" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-kfk01-nic</v>
       </c>
-      <c r="K51" s="37" t="s">
+      <c r="L51" s="37" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B52" s="36" t="s">
         <v>31</v>
       </c>
@@ -16036,15 +16193,18 @@
       <c r="I52" s="22" t="s">
         <v>339</v>
       </c>
-      <c r="J52" s="33" t="str">
+      <c r="J52" s="16" t="s">
+        <v>338</v>
+      </c>
+      <c r="K52" s="33" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-kfk02-nic</v>
       </c>
-      <c r="K52" s="34" t="s">
+      <c r="L52" s="34" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B53" s="35" t="s">
         <v>31</v>
       </c>
@@ -16071,15 +16231,18 @@
       <c r="I53" s="24" t="s">
         <v>340</v>
       </c>
-      <c r="J53" s="35" t="str">
+      <c r="J53" s="17" t="s">
+        <v>338</v>
+      </c>
+      <c r="K53" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-kfk03-nic</v>
       </c>
-      <c r="K53" s="37" t="s">
+      <c r="L53" s="37" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B54" s="36" t="s">
         <v>31</v>
       </c>
@@ -16106,15 +16269,18 @@
       <c r="I54" s="22" t="s">
         <v>303</v>
       </c>
-      <c r="J54" s="33" t="str">
+      <c r="J54" s="16" t="s">
+        <v>338</v>
+      </c>
+      <c r="K54" s="33" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-mqap01-nic</v>
       </c>
-      <c r="K54" s="34" t="s">
+      <c r="L54" s="34" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="55" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B55" s="35" t="s">
         <v>31</v>
       </c>
@@ -16141,15 +16307,18 @@
       <c r="I55" s="24" t="s">
         <v>396</v>
       </c>
-      <c r="J55" s="35" t="str">
+      <c r="J55" s="17" t="s">
+        <v>338</v>
+      </c>
+      <c r="K55" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-mqweb01-nic</v>
       </c>
-      <c r="K55" s="37" t="s">
+      <c r="L55" s="37" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="56" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B56" s="36" t="s">
         <v>31</v>
       </c>
@@ -16176,15 +16345,18 @@
       <c r="I56" s="22" t="s">
         <v>397</v>
       </c>
-      <c r="J56" s="33" t="str">
+      <c r="J56" s="16" t="s">
+        <v>338</v>
+      </c>
+      <c r="K56" s="33" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-oms01-nic</v>
       </c>
-      <c r="K56" s="34" t="s">
+      <c r="L56" s="34" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="57" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B57" s="35" t="s">
         <v>31</v>
       </c>
@@ -16211,15 +16383,18 @@
       <c r="I57" s="24" t="s">
         <v>398</v>
       </c>
-      <c r="J57" s="35" t="str">
+      <c r="J57" s="17" t="s">
+        <v>338</v>
+      </c>
+      <c r="K57" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-web01-nic</v>
       </c>
-      <c r="K57" s="37" t="s">
+      <c r="L57" s="37" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="58" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B58" s="36" t="s">
         <v>31</v>
       </c>
@@ -16246,15 +16421,18 @@
       <c r="I58" s="22" t="s">
         <v>399</v>
       </c>
-      <c r="J58" s="33" t="str">
+      <c r="J58" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="K58" s="33" t="str">
         <f t="shared" si="1"/>
         <v>d-com-auth01-nic</v>
       </c>
-      <c r="K58" s="34" t="s">
+      <c r="L58" s="34" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="59" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B59" s="35" t="s">
         <v>31</v>
       </c>
@@ -16281,15 +16459,18 @@
       <c r="I59" s="24" t="s">
         <v>400</v>
       </c>
-      <c r="J59" s="35" t="str">
+      <c r="J59" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="K59" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-com-proxy01-nic</v>
       </c>
-      <c r="K59" s="37" t="s">
+      <c r="L59" s="37" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="60" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B60" s="36" t="s">
         <v>31</v>
       </c>
@@ -16316,15 +16497,18 @@
       <c r="I60" s="22" t="s">
         <v>319</v>
       </c>
-      <c r="J60" s="33" t="str">
+      <c r="J60" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="K60" s="33" t="str">
         <f t="shared" si="1"/>
         <v>d-if-gramon01-nic</v>
       </c>
-      <c r="K60" s="34" t="s">
+      <c r="L60" s="34" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="61" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B61" s="35" t="s">
         <v>31</v>
       </c>
@@ -16351,15 +16535,18 @@
       <c r="I61" s="24" t="s">
         <v>404</v>
       </c>
-      <c r="J61" s="35" t="str">
+      <c r="J61" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="K61" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-doip-web01-nic</v>
       </c>
-      <c r="K61" s="37" t="s">
+      <c r="L61" s="37" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="62" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B62" s="36" t="s">
         <v>31</v>
       </c>
@@ -16386,15 +16573,18 @@
       <c r="I62" s="22" t="s">
         <v>326</v>
       </c>
-      <c r="J62" s="33" t="str">
+      <c r="J62" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="K62" s="33" t="str">
         <f t="shared" si="1"/>
         <v>d-doip-ap01-nic</v>
       </c>
-      <c r="K62" s="34" t="s">
+      <c r="L62" s="34" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="63" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B63" s="35" t="s">
         <v>31</v>
       </c>
@@ -16421,15 +16611,18 @@
       <c r="I63" s="24" t="s">
         <v>405</v>
       </c>
-      <c r="J63" s="35" t="str">
+      <c r="J63" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="K63" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-doip-adm01-nic</v>
       </c>
-      <c r="K63" s="37" t="s">
+      <c r="L63" s="37" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="64" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B64" s="36" t="s">
         <v>31</v>
       </c>
@@ -16456,15 +16649,18 @@
       <c r="I64" s="22" t="s">
         <v>401</v>
       </c>
-      <c r="J64" s="33" t="str">
+      <c r="J64" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="K64" s="33" t="str">
         <f t="shared" si="1"/>
         <v>d-bdp-crkweb01-nic</v>
       </c>
-      <c r="K64" s="34" t="s">
+      <c r="L64" s="34" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B65" s="35" t="s">
         <v>31</v>
       </c>
@@ -16491,15 +16687,18 @@
       <c r="I65" s="24" t="s">
         <v>372</v>
       </c>
-      <c r="J65" s="35" t="str">
+      <c r="J65" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="K65" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-bdp-crkap01-nic</v>
       </c>
-      <c r="K65" s="37" t="s">
+      <c r="L65" s="37" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B66" s="36" t="s">
         <v>31</v>
       </c>
@@ -16526,15 +16725,18 @@
       <c r="I66" s="22" t="s">
         <v>335</v>
       </c>
-      <c r="J66" s="33" t="str">
+      <c r="J66" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="K66" s="33" t="str">
         <f t="shared" si="1"/>
         <v>d-bdp-crkml01-nic</v>
       </c>
-      <c r="K66" s="34" t="s">
+      <c r="L66" s="34" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B67" s="35" t="s">
         <v>31</v>
       </c>
@@ -16561,15 +16763,18 @@
       <c r="I67" s="24" t="s">
         <v>406</v>
       </c>
-      <c r="J67" s="49" t="str">
+      <c r="J67" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="K67" s="49" t="str">
         <f t="shared" si="1"/>
         <v>d-dis-dfir01-nic</v>
       </c>
-      <c r="K67" s="37" t="s">
+      <c r="L67" s="37" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="41"/>
       <c r="B68" s="42" t="s">
         <v>31</v>
@@ -16596,15 +16801,18 @@
       <c r="I68" s="47" t="s">
         <v>423</v>
       </c>
-      <c r="J68" s="33" t="str">
+      <c r="J68" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="K68" s="33" t="str">
         <f t="shared" si="1"/>
         <v>temp-zen-01-nic</v>
       </c>
-      <c r="K68" s="45" t="s">
+      <c r="L68" s="45" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="41"/>
       <c r="B69" s="43" t="s">
         <v>31</v>
@@ -16631,11 +16839,14 @@
       <c r="I69" s="48" t="s">
         <v>424</v>
       </c>
-      <c r="J69" s="49" t="str">
-        <f t="shared" ref="J69" si="3">SUBSTITUTE($I69,"hazr-","")&amp;"-nic"</f>
+      <c r="J69" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="K69" s="49" t="str">
+        <f t="shared" ref="K69" si="3">SUBSTITUTE($I69,"hazr-","")&amp;"-nic"</f>
         <v>temp-zen-02-nic</v>
       </c>
-      <c r="K69" s="46" t="s">
+      <c r="L69" s="46" t="s">
         <v>403</v>
       </c>
     </row>

--- a/서버정보/20260422_리소스배포_개발.xlsx
+++ b/서버정보/20260422_리소스배포_개발.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{972AD4F9-4A2F-40C8-9D3C-A67CD6E63158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7473E02-0CB1-40B2-A65C-B0630CC521C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2361,7 +2361,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2476,9 +2476,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2491,7 +2488,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2500,7 +2497,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -2508,9 +2505,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -9822,7 +9816,7 @@
       <c r="S63" s="1"/>
       <c r="T63" s="1"/>
       <c r="U63" s="1" t="str">
-        <f>SUBSTITUTE(F63,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" ref="U63:U69" si="5">SUBSTITUTE(F63,"hazr-","")&amp;"-nic"</f>
         <v>d-doip-adm01-nic</v>
       </c>
       <c r="V63" s="1" t="b">
@@ -9911,7 +9905,7 @@
       <c r="S64" s="1"/>
       <c r="T64" s="1"/>
       <c r="U64" s="1" t="str">
-        <f>SUBSTITUTE(F64,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="5"/>
         <v>d-bdp-crkweb01-nic</v>
       </c>
       <c r="V64" s="1" t="b">
@@ -10000,7 +9994,7 @@
       <c r="S65" s="1"/>
       <c r="T65" s="1"/>
       <c r="U65" s="1" t="str">
-        <f>SUBSTITUTE(F65,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="5"/>
         <v>d-bdp-crkap01-nic</v>
       </c>
       <c r="V65" s="1" t="b">
@@ -10089,7 +10083,7 @@
       <c r="S66" s="1"/>
       <c r="T66" s="1"/>
       <c r="U66" s="1" t="str">
-        <f>SUBSTITUTE(F66,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="5"/>
         <v>d-bdp-crkml01-nic</v>
       </c>
       <c r="V66" s="1" t="b">
@@ -10178,7 +10172,7 @@
       <c r="S67" s="1"/>
       <c r="T67" s="1"/>
       <c r="U67" s="1" t="str">
-        <f>SUBSTITUTE(F67,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" si="5"/>
         <v>d-dis-dfir01-nic</v>
       </c>
       <c r="V67" s="1" t="b">
@@ -10212,14 +10206,14 @@
       <c r="AF67" s="1"/>
     </row>
     <row r="68" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A68" s="39"/>
+      <c r="A68" s="38"/>
       <c r="B68" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="D68" s="38" t="s">
+      <c r="D68" s="1" t="s">
         <v>51</v>
       </c>
       <c r="E68" s="1" t="s">
@@ -10243,7 +10237,7 @@
       <c r="K68" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="L68" s="40" t="s">
+      <c r="L68" s="39" t="s">
         <v>428</v>
       </c>
       <c r="M68" s="9" t="s">
@@ -10252,7 +10246,7 @@
       <c r="N68" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="O68" s="38" t="str">
+      <c r="O68" s="1" t="str">
         <f>SUBSTITUTE(F68,"hazr-","")&amp;"-osdisk"</f>
         <v>temp-zen-01-osdisk</v>
       </c>
@@ -10262,11 +10256,11 @@
       <c r="Q68" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="R68" s="38"/>
+      <c r="R68" s="1"/>
       <c r="S68" s="1"/>
-      <c r="T68" s="38"/>
-      <c r="U68" s="38" t="str">
-        <f>SUBSTITUTE(F68,"hazr-","")&amp;"-nic"</f>
+      <c r="T68" s="1"/>
+      <c r="U68" s="1" t="str">
+        <f t="shared" si="5"/>
         <v>temp-zen-01-nic</v>
       </c>
       <c r="V68" s="1" t="b">
@@ -10300,14 +10294,14 @@
       <c r="AF68" s="1"/>
     </row>
     <row r="69" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A69" s="39"/>
+      <c r="A69" s="38"/>
       <c r="B69" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="D69" s="38" t="s">
+      <c r="D69" s="1" t="s">
         <v>51</v>
       </c>
       <c r="E69" s="1" t="s">
@@ -10331,7 +10325,7 @@
       <c r="K69" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="L69" s="40" t="s">
+      <c r="L69" s="39" t="s">
         <v>428</v>
       </c>
       <c r="M69" s="9" t="s">
@@ -10340,7 +10334,7 @@
       <c r="N69" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="O69" s="38" t="str">
+      <c r="O69" s="1" t="str">
         <f>SUBSTITUTE(F69,"hazr-","")&amp;"-osdisk"</f>
         <v>temp-zen-02-osdisk</v>
       </c>
@@ -10350,11 +10344,11 @@
       <c r="Q69" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="R69" s="38"/>
+      <c r="R69" s="1"/>
       <c r="S69" s="1"/>
-      <c r="T69" s="38"/>
-      <c r="U69" s="38" t="str">
-        <f>SUBSTITUTE(F69,"hazr-","")&amp;"-nic"</f>
+      <c r="T69" s="1"/>
+      <c r="U69" s="1" t="str">
+        <f t="shared" si="5"/>
         <v>temp-zen-02-nic</v>
       </c>
       <c r="V69" s="1" t="b">
@@ -14103,7 +14097,7 @@
       <c r="R67" s="8"/>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A68" s="50"/>
+      <c r="A68" s="48"/>
       <c r="B68" s="16" t="s">
         <v>31</v>
       </c>
@@ -14120,7 +14114,7 @@
         <v>423</v>
       </c>
       <c r="G68" s="16" t="str">
-        <f t="shared" ref="G67:G69" si="2">SUBSTITUTE($F68,"hazr-","")&amp;"-disk01"</f>
+        <f t="shared" ref="G68:G69" si="2">SUBSTITUTE($F68,"hazr-","")&amp;"-disk01"</f>
         <v>temp-zen-01-disk01</v>
       </c>
       <c r="H68" s="16" t="s">
@@ -14157,7 +14151,7 @@
       <c r="R68" s="14"/>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A69" s="50"/>
+      <c r="A69" s="48"/>
       <c r="B69" s="17" t="s">
         <v>31</v>
       </c>
@@ -16766,7 +16760,7 @@
       <c r="J67" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="K67" s="49" t="str">
+      <c r="K67" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-dis-dfir01-nic</v>
       </c>
@@ -16775,30 +16769,30 @@
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A68" s="41"/>
-      <c r="B68" s="42" t="s">
+      <c r="A68" s="40"/>
+      <c r="B68" s="41" t="s">
         <v>31</v>
       </c>
       <c r="C68" s="33" t="s">
         <v>341</v>
       </c>
-      <c r="D68" s="44" t="s">
+      <c r="D68" s="43" t="s">
         <v>51</v>
       </c>
       <c r="E68" s="33" t="str">
         <f t="shared" si="2"/>
         <v>temp-zen-01-nsg</v>
       </c>
-      <c r="F68" s="44" t="s">
-        <v>49</v>
-      </c>
-      <c r="G68" s="44" t="s">
+      <c r="F68" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="G68" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="H68" s="44" t="s">
+      <c r="H68" s="43" t="s">
         <v>429</v>
       </c>
-      <c r="I68" s="47" t="s">
+      <c r="I68" s="46" t="s">
         <v>423</v>
       </c>
       <c r="J68" s="16" t="s">
@@ -16808,45 +16802,45 @@
         <f t="shared" si="1"/>
         <v>temp-zen-01-nic</v>
       </c>
-      <c r="L68" s="45" t="s">
+      <c r="L68" s="44" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A69" s="41"/>
-      <c r="B69" s="43" t="s">
+      <c r="A69" s="40"/>
+      <c r="B69" s="42" t="s">
         <v>31</v>
       </c>
       <c r="C69" s="35" t="s">
         <v>341</v>
       </c>
-      <c r="D69" s="43" t="s">
+      <c r="D69" s="42" t="s">
         <v>51</v>
       </c>
       <c r="E69" s="35" t="str">
         <f t="shared" si="2"/>
         <v>temp-zen-02-nsg</v>
       </c>
-      <c r="F69" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="G69" s="43" t="s">
+      <c r="F69" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="G69" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="H69" s="43" t="s">
+      <c r="H69" s="42" t="s">
         <v>429</v>
       </c>
-      <c r="I69" s="48" t="s">
+      <c r="I69" s="47" t="s">
         <v>424</v>
       </c>
       <c r="J69" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="K69" s="49" t="str">
+      <c r="K69" s="35" t="str">
         <f t="shared" ref="K69" si="3">SUBSTITUTE($I69,"hazr-","")&amp;"-nic"</f>
         <v>temp-zen-02-nic</v>
       </c>
-      <c r="L69" s="46" t="s">
+      <c r="L69" s="45" t="s">
         <v>403</v>
       </c>
     </row>

--- a/서버정보/20260422_리소스배포_개발.xlsx
+++ b/서버정보/20260422_리소스배포_개발.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7473E02-0CB1-40B2-A65C-B0630CC521C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25752B76-B730-41EC-A209-B50C404040C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -436,7 +436,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>, NIC</t>
+          <t>, VM</t>
         </r>
         <r>
           <rPr>
@@ -573,7 +573,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2504" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2540" uniqueCount="441">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2050,39 +2050,62 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Linux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>temp-zen-01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>temp-zen-02</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.156.168.11</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.156.168.12</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>azureadmin</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>rkskekfk1234!@</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>d-dis-cs-sbn</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>NicRG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>d-dis-db-sbn</t>
+  </si>
+  <si>
+    <t>d-dis-pe-sbn</t>
+  </si>
+  <si>
+    <t>d-puls-db-sbn</t>
+  </si>
+  <si>
+    <t>d-puls-pe-sbn</t>
+  </si>
+  <si>
+    <t>d-doip-db-sbn</t>
+  </si>
+  <si>
+    <t>d-doip-pe-sbn</t>
+  </si>
+  <si>
+    <t>d-ddg-db-sbn</t>
+  </si>
+  <si>
+    <t>d-ddg-pe-sbn</t>
+  </si>
+  <si>
+    <t>d-bdp-db-sbn</t>
+  </si>
+  <si>
+    <t>d-bdp-pe-sbn</t>
+  </si>
+  <si>
+    <t>d-dip-db-sbn</t>
+  </si>
+  <si>
+    <t>d-com-pe-sbn</t>
+  </si>
+  <si>
+    <t>d-com-db-sbn</t>
+  </si>
+  <si>
+    <t>d-if-db-sbn</t>
+  </si>
+  <si>
+    <t>d-if-pe-sbn</t>
+  </si>
+  <si>
+    <t>d-cs-db-sbn</t>
+  </si>
+  <si>
+    <t>d-cs-pe-sbn</t>
+  </si>
+  <si>
+    <t>X</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2090,7 +2113,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2196,17 +2219,8 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2237,20 +2251,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -2341,27 +2343,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2476,43 +2464,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="33">
     <dxf>
@@ -3067,8 +3021,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="B1:AF69" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31">
-  <autoFilter ref="B1:AF69" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="B1:AF67" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31">
+  <autoFilter ref="B1:AF67" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="31">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Stage" dataDxfId="30"/>
     <tableColumn id="2" xr3:uid="{DD2076C4-D866-4329-BEA8-1D816DAF3627}" name="Role" dataDxfId="29">
@@ -4195,7 +4149,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF69"/>
+  <dimension ref="A1:AF67"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.375" style="18" customWidth="1"/>
@@ -9816,7 +9770,7 @@
       <c r="S63" s="1"/>
       <c r="T63" s="1"/>
       <c r="U63" s="1" t="str">
-        <f t="shared" ref="U63:U69" si="5">SUBSTITUTE(F63,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" ref="U63:U67" si="5">SUBSTITUTE(F63,"hazr-","")&amp;"-nic"</f>
         <v>d-doip-adm01-nic</v>
       </c>
       <c r="V63" s="1" t="b">
@@ -10205,199 +10159,19 @@
       <c r="AE67" s="1"/>
       <c r="AF67" s="1"/>
     </row>
-    <row r="68" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A68" s="38"/>
-      <c r="B68" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="H68" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="I68" s="1">
-        <v>2</v>
-      </c>
-      <c r="J68" s="1">
-        <v>8</v>
-      </c>
-      <c r="K68" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="L68" s="39" t="s">
-        <v>428</v>
-      </c>
-      <c r="M68" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="N68" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="O68" s="1" t="str">
-        <f>SUBSTITUTE(F68,"hazr-","")&amp;"-osdisk"</f>
-        <v>temp-zen-01-osdisk</v>
-      </c>
-      <c r="P68" s="1">
-        <v>64</v>
-      </c>
-      <c r="Q68" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="R68" s="1"/>
-      <c r="S68" s="1"/>
-      <c r="T68" s="1"/>
-      <c r="U68" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>temp-zen-01-nic</v>
-      </c>
-      <c r="V68" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="W68" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="X68" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y68" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z68" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="AA68" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB68" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AC68" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="AD68" s="1">
-        <v>1</v>
-      </c>
-      <c r="AE68" s="1"/>
-      <c r="AF68" s="1"/>
-    </row>
-    <row r="69" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A69" s="38"/>
-      <c r="B69" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="G69" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="I69" s="1">
-        <v>2</v>
-      </c>
-      <c r="J69" s="1">
-        <v>8</v>
-      </c>
-      <c r="K69" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="L69" s="39" t="s">
-        <v>428</v>
-      </c>
-      <c r="M69" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="N69" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="O69" s="1" t="str">
-        <f>SUBSTITUTE(F69,"hazr-","")&amp;"-osdisk"</f>
-        <v>temp-zen-02-osdisk</v>
-      </c>
-      <c r="P69" s="1">
-        <v>64</v>
-      </c>
-      <c r="Q69" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="R69" s="1"/>
-      <c r="S69" s="1"/>
-      <c r="T69" s="1"/>
-      <c r="U69" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v>temp-zen-02-nic</v>
-      </c>
-      <c r="V69" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="W69" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="X69" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y69" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z69" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="AA69" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="AB69" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AC69" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="AD69" s="1">
-        <v>1</v>
-      </c>
-      <c r="AE69" s="1"/>
-      <c r="AF69" s="1"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="L68" r:id="rId1" xr:uid="{50979B1F-2006-4524-800D-AF07B36BDE50}"/>
-    <hyperlink ref="L69" r:id="rId2" xr:uid="{56A4CD57-5AA9-47CD-BC41-343B87217867}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="63" orientation="landscape" r:id="rId3"/>
+  <pageSetup paperSize="9" scale="63" orientation="landscape" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52F281E7-0665-4BB7-80DB-4208A01A998B}">
-  <dimension ref="A1:R69"/>
+  <dimension ref="A1:R67"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.625" style="18" customWidth="1"/>
@@ -14096,114 +13870,6 @@
       </c>
       <c r="R67" s="8"/>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A68" s="48"/>
-      <c r="B68" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="16" t="s">
-        <v>341</v>
-      </c>
-      <c r="D68" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="E68" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="F68" s="16" t="s">
-        <v>423</v>
-      </c>
-      <c r="G68" s="16" t="str">
-        <f t="shared" ref="G68:G69" si="2">SUBSTITUTE($F68,"hazr-","")&amp;"-disk01"</f>
-        <v>temp-zen-01-disk01</v>
-      </c>
-      <c r="H68" s="16" t="s">
-        <v>337</v>
-      </c>
-      <c r="I68" s="16">
-        <v>64</v>
-      </c>
-      <c r="J68" s="16" t="str">
-        <f>SUBSTITUTE($F68,"hazr-","")&amp;"-disk02"</f>
-        <v>temp-zen-01-disk02</v>
-      </c>
-      <c r="K68" s="16" t="s">
-        <v>337</v>
-      </c>
-      <c r="L68" s="16">
-        <v>64</v>
-      </c>
-      <c r="M68" s="16">
-        <v>1</v>
-      </c>
-      <c r="N68" s="16" t="s">
-        <v>367</v>
-      </c>
-      <c r="O68" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="P68" s="16" t="s">
-        <v>364</v>
-      </c>
-      <c r="Q68" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="R68" s="14"/>
-    </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A69" s="48"/>
-      <c r="B69" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="17" t="s">
-        <v>341</v>
-      </c>
-      <c r="D69" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="E69" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="F69" s="17" t="s">
-        <v>424</v>
-      </c>
-      <c r="G69" s="17" t="str">
-        <f t="shared" si="2"/>
-        <v>temp-zen-02-disk01</v>
-      </c>
-      <c r="H69" s="17" t="s">
-        <v>337</v>
-      </c>
-      <c r="I69" s="17">
-        <v>64</v>
-      </c>
-      <c r="J69" s="17" t="str">
-        <f>SUBSTITUTE($F69,"hazr-","")&amp;"-disk02"</f>
-        <v>temp-zen-02-disk02</v>
-      </c>
-      <c r="K69" s="17" t="s">
-        <v>337</v>
-      </c>
-      <c r="L69" s="17">
-        <v>64</v>
-      </c>
-      <c r="M69" s="17">
-        <v>1</v>
-      </c>
-      <c r="N69" s="17" t="s">
-        <v>367</v>
-      </c>
-      <c r="O69" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="P69" s="17" t="s">
-        <v>364</v>
-      </c>
-      <c r="Q69" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="R69" s="8"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14212,7 +13878,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAB1F184-7BFC-47CB-AC71-63C76B7E3D12}">
-  <dimension ref="A1:L69"/>
+  <sheetPr>
+    <tabColor theme="5"/>
+  </sheetPr>
+  <dimension ref="B1:L85"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.75" customWidth="1"/>
@@ -14251,7 +13920,7 @@
         <v>356</v>
       </c>
       <c r="J1" s="31" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="K1" s="31" t="s">
         <v>26</v>
@@ -14367,7 +14036,7 @@
         <v>52</v>
       </c>
       <c r="K4" s="33" t="str">
-        <f t="shared" ref="K4:K68" si="1">SUBSTITUTE($I4,"hazr-","")&amp;"-nic"</f>
+        <f t="shared" ref="K4:K67" si="1">SUBSTITUTE($I4,"hazr-","")&amp;"-nic"</f>
         <v>d-dis-bbiweb01-nic</v>
       </c>
       <c r="L4" s="34" t="s">
@@ -15716,7 +15385,7 @@
         <v>49</v>
       </c>
       <c r="E40" s="33" t="str">
-        <f t="shared" ref="E40:E69" si="2">SUBSTITUTE($I40,"hazr-","")&amp;"-nsg"</f>
+        <f t="shared" ref="E40:E67" si="2">SUBSTITUTE($I40,"hazr-","")&amp;"-nsg"</f>
         <v>d-dtg-dprap01-nsg</v>
       </c>
       <c r="F40" s="33" t="s">
@@ -16654,7 +16323,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B65" s="35" t="s">
         <v>31</v>
       </c>
@@ -16692,7 +16361,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B66" s="36" t="s">
         <v>31</v>
       </c>
@@ -16730,7 +16399,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B67" s="35" t="s">
         <v>31</v>
       </c>
@@ -16768,80 +16437,562 @@
         <v>403</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A68" s="40"/>
-      <c r="B68" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="33" t="s">
-        <v>341</v>
-      </c>
-      <c r="D68" s="43" t="s">
-        <v>51</v>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B68" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="33" t="str" cm="1">
+        <f t="array" ref="C68">UPPER(INDEX(_xlfn.TEXTSPLIT($E68, "-"), 2))</f>
+        <v>DIS</v>
+      </c>
+      <c r="D68" s="33" t="s">
+        <v>49</v>
       </c>
       <c r="E68" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v>temp-zen-01-nsg</v>
-      </c>
-      <c r="F68" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="G68" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="H68" s="43" t="s">
+        <f>SUBSTITUTE(H68,"-sbn","")&amp;"-nsg"</f>
+        <v>d-dis-db-nsg</v>
+      </c>
+      <c r="F68" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="G68" s="33" t="s">
+        <v>188</v>
+      </c>
+      <c r="H68" s="33" t="s">
+        <v>423</v>
+      </c>
+      <c r="I68" s="33"/>
+      <c r="J68" s="33"/>
+      <c r="K68" s="33"/>
+      <c r="L68" s="33" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B69" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="35" t="str" cm="1">
+        <f t="array" ref="C69">UPPER(INDEX(_xlfn.TEXTSPLIT($E69, "-"), 2))</f>
+        <v>DIS</v>
+      </c>
+      <c r="D69" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="E69" s="35" t="str">
+        <f t="shared" ref="E69:E85" si="3">SUBSTITUTE(H69,"-sbn","")&amp;"-nsg"</f>
+        <v>d-dis-pe-nsg</v>
+      </c>
+      <c r="F69" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="G69" s="35" t="s">
+        <v>188</v>
+      </c>
+      <c r="H69" s="35" t="s">
+        <v>424</v>
+      </c>
+      <c r="I69" s="35"/>
+      <c r="J69" s="35"/>
+      <c r="K69" s="35"/>
+      <c r="L69" s="35" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B70" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="36" t="str" cm="1">
+        <f t="array" ref="C70">UPPER(INDEX(_xlfn.TEXTSPLIT($E70, "-"), 2))</f>
+        <v>PULS</v>
+      </c>
+      <c r="D70" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="E70" s="33" t="str">
+        <f t="shared" si="3"/>
+        <v>d-puls-db-nsg</v>
+      </c>
+      <c r="F70" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="G70" s="33" t="s">
+        <v>188</v>
+      </c>
+      <c r="H70" s="33" t="s">
+        <v>425</v>
+      </c>
+      <c r="I70" s="33"/>
+      <c r="J70" s="33"/>
+      <c r="K70" s="33"/>
+      <c r="L70" s="33" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B71" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="35" t="str" cm="1">
+        <f t="array" ref="C71">UPPER(INDEX(_xlfn.TEXTSPLIT($E71, "-"), 2))</f>
+        <v>PULS</v>
+      </c>
+      <c r="D71" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="E71" s="35" t="str">
+        <f t="shared" si="3"/>
+        <v>d-puls-pe-nsg</v>
+      </c>
+      <c r="F71" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="G71" s="35" t="s">
+        <v>188</v>
+      </c>
+      <c r="H71" s="35" t="s">
+        <v>426</v>
+      </c>
+      <c r="I71" s="35"/>
+      <c r="J71" s="35"/>
+      <c r="K71" s="35"/>
+      <c r="L71" s="35" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B72" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="36" t="str" cm="1">
+        <f t="array" ref="C72">UPPER(INDEX(_xlfn.TEXTSPLIT($E72, "-"), 2))</f>
+        <v>DOIP</v>
+      </c>
+      <c r="D72" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="E72" s="33" t="str">
+        <f t="shared" si="3"/>
+        <v>d-doip-db-nsg</v>
+      </c>
+      <c r="F72" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="G72" s="33" t="s">
+        <v>188</v>
+      </c>
+      <c r="H72" s="33" t="s">
+        <v>427</v>
+      </c>
+      <c r="I72" s="33"/>
+      <c r="J72" s="33"/>
+      <c r="K72" s="33"/>
+      <c r="L72" s="33" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B73" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="35" t="str" cm="1">
+        <f t="array" ref="C73">UPPER(INDEX(_xlfn.TEXTSPLIT($E73, "-"), 2))</f>
+        <v>DOIP</v>
+      </c>
+      <c r="D73" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="E73" s="35" t="str">
+        <f t="shared" si="3"/>
+        <v>d-doip-pe-nsg</v>
+      </c>
+      <c r="F73" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="G73" s="35" t="s">
+        <v>188</v>
+      </c>
+      <c r="H73" s="35" t="s">
+        <v>428</v>
+      </c>
+      <c r="I73" s="35"/>
+      <c r="J73" s="35"/>
+      <c r="K73" s="35"/>
+      <c r="L73" s="35" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B74" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="36" t="str" cm="1">
+        <f t="array" ref="C74">UPPER(INDEX(_xlfn.TEXTSPLIT($E74, "-"), 2))</f>
+        <v>DDG</v>
+      </c>
+      <c r="D74" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="E74" s="33" t="str">
+        <f t="shared" si="3"/>
+        <v>d-ddg-db-nsg</v>
+      </c>
+      <c r="F74" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="G74" s="33" t="s">
+        <v>188</v>
+      </c>
+      <c r="H74" s="33" t="s">
         <v>429</v>
       </c>
-      <c r="I68" s="46" t="s">
-        <v>423</v>
-      </c>
-      <c r="J68" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="K68" s="33" t="str">
-        <f t="shared" si="1"/>
-        <v>temp-zen-01-nic</v>
-      </c>
-      <c r="L68" s="44" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A69" s="40"/>
-      <c r="B69" s="42" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="35" t="s">
-        <v>341</v>
-      </c>
-      <c r="D69" s="42" t="s">
-        <v>51</v>
-      </c>
-      <c r="E69" s="35" t="str">
-        <f t="shared" si="2"/>
-        <v>temp-zen-02-nsg</v>
-      </c>
-      <c r="F69" s="42" t="s">
-        <v>49</v>
-      </c>
-      <c r="G69" s="42" t="s">
-        <v>57</v>
-      </c>
-      <c r="H69" s="42" t="s">
-        <v>429</v>
-      </c>
-      <c r="I69" s="47" t="s">
-        <v>424</v>
-      </c>
-      <c r="J69" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="K69" s="35" t="str">
-        <f t="shared" ref="K69" si="3">SUBSTITUTE($I69,"hazr-","")&amp;"-nic"</f>
-        <v>temp-zen-02-nic</v>
-      </c>
-      <c r="L69" s="45" t="s">
-        <v>403</v>
+      <c r="I74" s="33"/>
+      <c r="J74" s="33"/>
+      <c r="K74" s="33"/>
+      <c r="L74" s="33" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B75" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="35" t="str" cm="1">
+        <f t="array" ref="C75">UPPER(INDEX(_xlfn.TEXTSPLIT($E75, "-"), 2))</f>
+        <v>DDG</v>
+      </c>
+      <c r="D75" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="E75" s="35" t="str">
+        <f t="shared" si="3"/>
+        <v>d-ddg-pe-nsg</v>
+      </c>
+      <c r="F75" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="G75" s="35" t="s">
+        <v>188</v>
+      </c>
+      <c r="H75" s="35" t="s">
+        <v>430</v>
+      </c>
+      <c r="I75" s="35"/>
+      <c r="J75" s="35"/>
+      <c r="K75" s="35"/>
+      <c r="L75" s="35" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B76" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="36" t="str" cm="1">
+        <f t="array" ref="C76">UPPER(INDEX(_xlfn.TEXTSPLIT($E76, "-"), 2))</f>
+        <v>BDP</v>
+      </c>
+      <c r="D76" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="E76" s="33" t="str">
+        <f t="shared" si="3"/>
+        <v>d-bdp-db-nsg</v>
+      </c>
+      <c r="F76" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="G76" s="33" t="s">
+        <v>188</v>
+      </c>
+      <c r="H76" s="33" t="s">
+        <v>431</v>
+      </c>
+      <c r="I76" s="33"/>
+      <c r="J76" s="33"/>
+      <c r="K76" s="33"/>
+      <c r="L76" s="33" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B77" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="35" t="str" cm="1">
+        <f t="array" ref="C77">UPPER(INDEX(_xlfn.TEXTSPLIT($E77, "-"), 2))</f>
+        <v>BDP</v>
+      </c>
+      <c r="D77" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="E77" s="35" t="str">
+        <f t="shared" si="3"/>
+        <v>d-bdp-pe-nsg</v>
+      </c>
+      <c r="F77" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="G77" s="35" t="s">
+        <v>188</v>
+      </c>
+      <c r="H77" s="35" t="s">
+        <v>432</v>
+      </c>
+      <c r="I77" s="35"/>
+      <c r="J77" s="35"/>
+      <c r="K77" s="35"/>
+      <c r="L77" s="35" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="78" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B78" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="36" t="str" cm="1">
+        <f t="array" ref="C78">UPPER(INDEX(_xlfn.TEXTSPLIT($E78, "-"), 2))</f>
+        <v>DIP</v>
+      </c>
+      <c r="D78" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="E78" s="33" t="str">
+        <f t="shared" si="3"/>
+        <v>d-dip-db-nsg</v>
+      </c>
+      <c r="F78" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="G78" s="33" t="s">
+        <v>188</v>
+      </c>
+      <c r="H78" s="33" t="s">
+        <v>433</v>
+      </c>
+      <c r="I78" s="33"/>
+      <c r="J78" s="33"/>
+      <c r="K78" s="33"/>
+      <c r="L78" s="33" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B79" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="35" t="str" cm="1">
+        <f t="array" ref="C79">UPPER(INDEX(_xlfn.TEXTSPLIT($E79, "-"), 2))</f>
+        <v>COM</v>
+      </c>
+      <c r="D79" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="E79" s="35" t="str">
+        <f t="shared" si="3"/>
+        <v>d-com-pe-nsg</v>
+      </c>
+      <c r="F79" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="G79" s="35" t="s">
+        <v>188</v>
+      </c>
+      <c r="H79" s="35" t="s">
+        <v>434</v>
+      </c>
+      <c r="I79" s="35"/>
+      <c r="J79" s="35"/>
+      <c r="K79" s="35"/>
+      <c r="L79" s="35" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="80" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B80" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="36" t="str" cm="1">
+        <f t="array" ref="C80">UPPER(INDEX(_xlfn.TEXTSPLIT($E80, "-"), 2))</f>
+        <v>COM</v>
+      </c>
+      <c r="D80" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="E80" s="33" t="str">
+        <f t="shared" si="3"/>
+        <v>d-com-db-nsg</v>
+      </c>
+      <c r="F80" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="G80" s="33" t="s">
+        <v>188</v>
+      </c>
+      <c r="H80" s="33" t="s">
+        <v>435</v>
+      </c>
+      <c r="I80" s="33"/>
+      <c r="J80" s="33"/>
+      <c r="K80" s="33"/>
+      <c r="L80" s="33" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="81" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B81" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="35" t="str" cm="1">
+        <f t="array" ref="C81">UPPER(INDEX(_xlfn.TEXTSPLIT($E81, "-"), 2))</f>
+        <v>COM</v>
+      </c>
+      <c r="D81" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="E81" s="35" t="str">
+        <f t="shared" si="3"/>
+        <v>d-com-pe-nsg</v>
+      </c>
+      <c r="F81" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="G81" s="35" t="s">
+        <v>188</v>
+      </c>
+      <c r="H81" s="35" t="s">
+        <v>434</v>
+      </c>
+      <c r="I81" s="35"/>
+      <c r="J81" s="35"/>
+      <c r="K81" s="35"/>
+      <c r="L81" s="35" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="82" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B82" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="36" t="str" cm="1">
+        <f t="array" ref="C82">UPPER(INDEX(_xlfn.TEXTSPLIT($E82, "-"), 2))</f>
+        <v>IF</v>
+      </c>
+      <c r="D82" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="E82" s="33" t="str">
+        <f t="shared" si="3"/>
+        <v>d-if-db-nsg</v>
+      </c>
+      <c r="F82" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="G82" s="33" t="s">
+        <v>188</v>
+      </c>
+      <c r="H82" s="33" t="s">
+        <v>436</v>
+      </c>
+      <c r="I82" s="33"/>
+      <c r="J82" s="33"/>
+      <c r="K82" s="33"/>
+      <c r="L82" s="33" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="83" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B83" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" s="35" t="str" cm="1">
+        <f t="array" ref="C83">UPPER(INDEX(_xlfn.TEXTSPLIT($E83, "-"), 2))</f>
+        <v>IF</v>
+      </c>
+      <c r="D83" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="E83" s="35" t="str">
+        <f t="shared" si="3"/>
+        <v>d-if-pe-nsg</v>
+      </c>
+      <c r="F83" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="G83" s="35" t="s">
+        <v>188</v>
+      </c>
+      <c r="H83" s="35" t="s">
+        <v>437</v>
+      </c>
+      <c r="I83" s="35"/>
+      <c r="J83" s="35"/>
+      <c r="K83" s="35"/>
+      <c r="L83" s="35" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="84" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B84" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="C84" s="36" t="str" cm="1">
+        <f t="array" ref="C84">UPPER(INDEX(_xlfn.TEXTSPLIT($E84, "-"), 2))</f>
+        <v>CS</v>
+      </c>
+      <c r="D84" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="E84" s="33" t="str">
+        <f t="shared" si="3"/>
+        <v>d-cs-db-nsg</v>
+      </c>
+      <c r="F84" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="G84" s="33" t="s">
+        <v>188</v>
+      </c>
+      <c r="H84" s="33" t="s">
+        <v>438</v>
+      </c>
+      <c r="I84" s="33"/>
+      <c r="J84" s="33"/>
+      <c r="K84" s="33"/>
+      <c r="L84" s="33" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="85" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B85" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="C85" s="35" t="str" cm="1">
+        <f t="array" ref="C85">UPPER(INDEX(_xlfn.TEXTSPLIT($E85, "-"), 2))</f>
+        <v>CS</v>
+      </c>
+      <c r="D85" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="E85" s="35" t="str">
+        <f t="shared" si="3"/>
+        <v>d-cs-pe-nsg</v>
+      </c>
+      <c r="F85" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="G85" s="35" t="s">
+        <v>188</v>
+      </c>
+      <c r="H85" s="35" t="s">
+        <v>439</v>
+      </c>
+      <c r="I85" s="35"/>
+      <c r="J85" s="35"/>
+      <c r="K85" s="35"/>
+      <c r="L85" s="35" t="s">
+        <v>440</v>
       </c>
     </row>
   </sheetData>

--- a/서버정보/20260422_리소스배포_개발.xlsx
+++ b/서버정보/20260422_리소스배포_개발.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25752B76-B730-41EC-A209-B50C404040C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7044FC39-1BF1-4097-9AAB-F8DEB8B483C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -573,7 +573,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2540" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2534" uniqueCount="441">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3363,6 +3363,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{721B19D1-383B-4C42-B4E9-A7935F09393B}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
   <dimension ref="A1:BK71"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3966,6 +3969,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4551C21F-24D7-4C3A-A8CD-5A629D1AA37B}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
   <dimension ref="A1:F71"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4149,6 +4155,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
   <dimension ref="A1:AF67"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -10171,6 +10180,9 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52F281E7-0665-4BB7-80DB-4208A01A998B}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
   <dimension ref="A1:R67"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -13881,7 +13893,7 @@
   <sheetPr>
     <tabColor theme="5"/>
   </sheetPr>
-  <dimension ref="B1:L85"/>
+  <dimension ref="B1:L84"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.75" customWidth="1"/>
@@ -16480,7 +16492,7 @@
         <v>49</v>
       </c>
       <c r="E69" s="35" t="str">
-        <f t="shared" ref="E69:E85" si="3">SUBSTITUTE(H69,"-sbn","")&amp;"-nsg"</f>
+        <f t="shared" ref="E69:E84" si="3">SUBSTITUTE(H69,"-sbn","")&amp;"-nsg"</f>
         <v>d-dis-pe-nsg</v>
       </c>
       <c r="F69" s="35" t="s">
@@ -16846,14 +16858,14 @@
       </c>
       <c r="C81" s="35" t="str" cm="1">
         <f t="array" ref="C81">UPPER(INDEX(_xlfn.TEXTSPLIT($E81, "-"), 2))</f>
-        <v>COM</v>
+        <v>IF</v>
       </c>
       <c r="D81" s="35" t="s">
         <v>49</v>
       </c>
       <c r="E81" s="35" t="str">
         <f t="shared" si="3"/>
-        <v>d-com-pe-nsg</v>
+        <v>d-if-db-nsg</v>
       </c>
       <c r="F81" s="35" t="s">
         <v>49</v>
@@ -16862,7 +16874,7 @@
         <v>188</v>
       </c>
       <c r="H81" s="35" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="I81" s="35"/>
       <c r="J81" s="35"/>
@@ -16884,7 +16896,7 @@
       </c>
       <c r="E82" s="33" t="str">
         <f t="shared" si="3"/>
-        <v>d-if-db-nsg</v>
+        <v>d-if-pe-nsg</v>
       </c>
       <c r="F82" s="33" t="s">
         <v>49</v>
@@ -16893,7 +16905,7 @@
         <v>188</v>
       </c>
       <c r="H82" s="33" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="I82" s="33"/>
       <c r="J82" s="33"/>
@@ -16908,14 +16920,14 @@
       </c>
       <c r="C83" s="35" t="str" cm="1">
         <f t="array" ref="C83">UPPER(INDEX(_xlfn.TEXTSPLIT($E83, "-"), 2))</f>
-        <v>IF</v>
+        <v>CS</v>
       </c>
       <c r="D83" s="35" t="s">
         <v>49</v>
       </c>
       <c r="E83" s="35" t="str">
         <f t="shared" si="3"/>
-        <v>d-if-pe-nsg</v>
+        <v>d-cs-db-nsg</v>
       </c>
       <c r="F83" s="35" t="s">
         <v>49</v>
@@ -16924,7 +16936,7 @@
         <v>188</v>
       </c>
       <c r="H83" s="35" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="I83" s="35"/>
       <c r="J83" s="35"/>
@@ -16946,7 +16958,7 @@
       </c>
       <c r="E84" s="33" t="str">
         <f t="shared" si="3"/>
-        <v>d-cs-db-nsg</v>
+        <v>d-cs-pe-nsg</v>
       </c>
       <c r="F84" s="33" t="s">
         <v>49</v>
@@ -16955,43 +16967,12 @@
         <v>188</v>
       </c>
       <c r="H84" s="33" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="I84" s="33"/>
       <c r="J84" s="33"/>
       <c r="K84" s="33"/>
       <c r="L84" s="33" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="85" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B85" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="C85" s="35" t="str" cm="1">
-        <f t="array" ref="C85">UPPER(INDEX(_xlfn.TEXTSPLIT($E85, "-"), 2))</f>
-        <v>CS</v>
-      </c>
-      <c r="D85" s="35" t="s">
-        <v>49</v>
-      </c>
-      <c r="E85" s="35" t="str">
-        <f t="shared" si="3"/>
-        <v>d-cs-pe-nsg</v>
-      </c>
-      <c r="F85" s="35" t="s">
-        <v>49</v>
-      </c>
-      <c r="G85" s="35" t="s">
-        <v>188</v>
-      </c>
-      <c r="H85" s="35" t="s">
-        <v>439</v>
-      </c>
-      <c r="I85" s="35"/>
-      <c r="J85" s="35"/>
-      <c r="K85" s="35"/>
-      <c r="L85" s="35" t="s">
         <v>440</v>
       </c>
     </row>

--- a/서버정보/20260422_리소스배포_개발.xlsx
+++ b/서버정보/20260422_리소스배포_개발.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7044FC39-1BF1-4097-9AAB-F8DEB8B483C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD983E1A-522C-4B4B-BFCE-473DE8282E25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -573,7 +573,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2534" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2530" uniqueCount="441">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2099,13 +2099,15 @@
     <t>d-if-pe-sbn</t>
   </si>
   <si>
-    <t>d-cs-db-sbn</t>
-  </si>
-  <si>
-    <t>d-cs-pe-sbn</t>
-  </si>
-  <si>
     <t>X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DIP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>d-dip-pe-nsg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2349,7 +2351,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2464,11 +2466,24 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="33">
+  <dxfs count="34">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -3021,46 +3036,46 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="B1:AF67" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="B1:AF67" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
   <autoFilter ref="B1:AF67" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="31">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Stage" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{DD2076C4-D866-4329-BEA8-1D816DAF3627}" name="Role" dataDxfId="29">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Stage" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{DD2076C4-D866-4329-BEA8-1D816DAF3627}" name="Role" dataDxfId="30">
       <calculatedColumnFormula array="1">UPPER(INDEX(_xlfn.TEXTSPLIT($D2, "-"), 3))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="RGname" dataDxfId="28"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Location" dataDxfId="27"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="26"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="PrivateIP" dataDxfId="25"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="VmSize" dataDxfId="24"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="CPU" dataDxfId="23"/>
-    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="RAM" dataDxfId="22"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="AdminUsername" dataDxfId="21"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="AdminPassword" dataDxfId="20"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="OsType" dataDxfId="19"/>
-    <tableColumn id="10" xr3:uid="{5C5FDBAD-A0A4-4C75-968A-8587646674EE}" name="ImageResourceId" dataDxfId="18"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="OsDiskName" dataDxfId="17">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="RGname" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Location" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="PrivateIP" dataDxfId="26"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="VmSize" dataDxfId="25"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="CPU" dataDxfId="24"/>
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0000-000022000000}" name="RAM" dataDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="AdminUsername" dataDxfId="22"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="AdminPassword" dataDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="OsType" dataDxfId="20"/>
+    <tableColumn id="10" xr3:uid="{5C5FDBAD-A0A4-4C75-968A-8587646674EE}" name="ImageResourceId" dataDxfId="19"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="OsDiskName" dataDxfId="18">
       <calculatedColumnFormula>SUBSTITUTE(F2,"hazr-","")&amp;"-osdisk"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="OsDiskSize" dataDxfId="16"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="OsDiskStorageType" dataDxfId="15"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="DataDiskName" dataDxfId="14"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="DataDiskSize" dataDxfId="13"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="DataDiskStorageType" dataDxfId="12"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="NicName" dataDxfId="11">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="OsDiskSize" dataDxfId="17"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="OsDiskStorageType" dataDxfId="16"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="DataDiskName" dataDxfId="15"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="DataDiskSize" dataDxfId="14"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="DataDiskStorageType" dataDxfId="13"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="NicName" dataDxfId="12">
       <calculatedColumnFormula>SUBSTITUTE(F2,"hazr-","")&amp;"-nic"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{6FD9A0A6-7008-49AB-B2C9-4BEDF1811434}" name="EnableAcceleratedNetworking" dataDxfId="10"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="IsStatic" dataDxfId="9"/>
-    <tableColumn id="11" xr3:uid="{65903CF2-1AF4-4B86-A9E4-474DE495E3CB}" name="VnetRG" dataDxfId="8"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="VnetName" dataDxfId="7"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="SubnetName" dataDxfId="6"/>
-    <tableColumn id="28" xr3:uid="{73185387-6B41-497F-9EB6-5675CC43B3E3}" name="UseOsDiskDoubleEncryption " dataDxfId="5"/>
-    <tableColumn id="21" xr3:uid="{804782E7-599A-496A-B10D-EFCB52F3E7DB}" name="DESRG" dataDxfId="4"/>
-    <tableColumn id="16" xr3:uid="{1ED2A695-2028-4644-8B0B-7B32A8F548C4}" name="DESName" dataDxfId="3"/>
-    <tableColumn id="36" xr3:uid="{9EB3DACA-84E4-4D05-8E76-433A4A9E33E7}" name="Zones" dataDxfId="2"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="SubscriptionName" dataDxfId="1"/>
-    <tableColumn id="35" xr3:uid="{A2E4758D-942B-4C99-96CE-9F1494B6961B}" name="Description" dataDxfId="0"/>
+    <tableColumn id="27" xr3:uid="{6FD9A0A6-7008-49AB-B2C9-4BEDF1811434}" name="EnableAcceleratedNetworking" dataDxfId="11"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="IsStatic" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{65903CF2-1AF4-4B86-A9E4-474DE495E3CB}" name="VnetRG" dataDxfId="9"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="VnetName" dataDxfId="8"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="SubnetName" dataDxfId="7"/>
+    <tableColumn id="28" xr3:uid="{73185387-6B41-497F-9EB6-5675CC43B3E3}" name="UseOsDiskDoubleEncryption " dataDxfId="6"/>
+    <tableColumn id="21" xr3:uid="{804782E7-599A-496A-B10D-EFCB52F3E7DB}" name="DESRG" dataDxfId="5"/>
+    <tableColumn id="16" xr3:uid="{1ED2A695-2028-4644-8B0B-7B32A8F548C4}" name="DESName" dataDxfId="4"/>
+    <tableColumn id="36" xr3:uid="{9EB3DACA-84E4-4D05-8E76-433A4A9E33E7}" name="Zones" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="SubscriptionName" dataDxfId="2"/>
+    <tableColumn id="35" xr3:uid="{A2E4758D-942B-4C99-96CE-9F1494B6961B}" name="Description" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -13891,9 +13906,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAB1F184-7BFC-47CB-AC71-63C76B7E3D12}">
   <sheetPr>
-    <tabColor theme="5"/>
+    <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="B1:L84"/>
+  <dimension ref="A1:L83"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.75" customWidth="1"/>
@@ -13906,7 +13921,7 @@
     <col min="11" max="11" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B1" s="29" t="s">
         <v>0</v>
       </c>
@@ -13941,7 +13956,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="38"/>
       <c r="B2" s="33" t="s">
         <v>31</v>
       </c>
@@ -13979,7 +13995,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="38"/>
       <c r="B3" s="35" t="s">
         <v>31</v>
       </c>
@@ -14017,7 +14034,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="38"/>
       <c r="B4" s="33" t="s">
         <v>31</v>
       </c>
@@ -14055,7 +14073,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="38"/>
       <c r="B5" s="35" t="s">
         <v>31</v>
       </c>
@@ -14093,7 +14112,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="38"/>
       <c r="B6" s="36" t="s">
         <v>31</v>
       </c>
@@ -14131,7 +14151,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="38"/>
       <c r="B7" s="35" t="s">
         <v>31</v>
       </c>
@@ -14169,7 +14190,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="38"/>
       <c r="B8" s="36" t="s">
         <v>31</v>
       </c>
@@ -14207,7 +14229,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="38"/>
       <c r="B9" s="35" t="s">
         <v>31</v>
       </c>
@@ -14245,7 +14268,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="38"/>
       <c r="B10" s="36" t="s">
         <v>31</v>
       </c>
@@ -14283,7 +14307,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="38"/>
       <c r="B11" s="35" t="s">
         <v>31</v>
       </c>
@@ -14321,7 +14346,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="38"/>
       <c r="B12" s="36" t="s">
         <v>31</v>
       </c>
@@ -14359,7 +14385,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="38"/>
       <c r="B13" s="35" t="s">
         <v>31</v>
       </c>
@@ -14397,7 +14424,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="38"/>
       <c r="B14" s="36" t="s">
         <v>31</v>
       </c>
@@ -14435,7 +14463,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="38"/>
       <c r="B15" s="35" t="s">
         <v>31</v>
       </c>
@@ -14473,7 +14502,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="38"/>
       <c r="B16" s="36" t="s">
         <v>31</v>
       </c>
@@ -14511,7 +14541,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="38"/>
       <c r="B17" s="35" t="s">
         <v>31</v>
       </c>
@@ -14549,7 +14580,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="38"/>
       <c r="B18" s="36" t="s">
         <v>31</v>
       </c>
@@ -14587,7 +14619,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="38"/>
       <c r="B19" s="35" t="s">
         <v>31</v>
       </c>
@@ -14625,7 +14658,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="38"/>
       <c r="B20" s="36" t="s">
         <v>31</v>
       </c>
@@ -14663,7 +14697,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="38"/>
       <c r="B21" s="35" t="s">
         <v>31</v>
       </c>
@@ -14701,7 +14736,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="38"/>
       <c r="B22" s="36" t="s">
         <v>31</v>
       </c>
@@ -14739,7 +14775,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="38"/>
       <c r="B23" s="35" t="s">
         <v>31</v>
       </c>
@@ -14777,7 +14814,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="38"/>
       <c r="B24" s="36" t="s">
         <v>31</v>
       </c>
@@ -14815,7 +14853,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" s="38"/>
       <c r="B25" s="35" t="s">
         <v>31</v>
       </c>
@@ -14853,7 +14892,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="38"/>
       <c r="B26" s="36" t="s">
         <v>31</v>
       </c>
@@ -14891,7 +14931,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="38"/>
       <c r="B27" s="35" t="s">
         <v>31</v>
       </c>
@@ -14929,7 +14970,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="38"/>
       <c r="B28" s="36" t="s">
         <v>31</v>
       </c>
@@ -14967,7 +15009,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="38"/>
       <c r="B29" s="35" t="s">
         <v>31</v>
       </c>
@@ -15005,7 +15048,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="38"/>
       <c r="B30" s="36" t="s">
         <v>31</v>
       </c>
@@ -15043,7 +15087,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="38"/>
       <c r="B31" s="35" t="s">
         <v>31</v>
       </c>
@@ -15081,7 +15126,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" s="38"/>
       <c r="B32" s="36" t="s">
         <v>31</v>
       </c>
@@ -15119,7 +15165,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" s="38"/>
       <c r="B33" s="35" t="s">
         <v>31</v>
       </c>
@@ -15157,7 +15204,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="38"/>
       <c r="B34" s="36" t="s">
         <v>31</v>
       </c>
@@ -15195,7 +15243,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="38"/>
       <c r="B35" s="35" t="s">
         <v>31</v>
       </c>
@@ -15233,7 +15282,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="38"/>
       <c r="B36" s="36" t="s">
         <v>31</v>
       </c>
@@ -15271,7 +15321,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" s="38"/>
       <c r="B37" s="35" t="s">
         <v>31</v>
       </c>
@@ -15309,7 +15360,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" s="38"/>
       <c r="B38" s="36" t="s">
         <v>31</v>
       </c>
@@ -15347,7 +15399,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" s="38"/>
       <c r="B39" s="35" t="s">
         <v>31</v>
       </c>
@@ -15385,7 +15438,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" s="38"/>
       <c r="B40" s="36" t="s">
         <v>31</v>
       </c>
@@ -15423,7 +15477,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" s="38"/>
       <c r="B41" s="35" t="s">
         <v>31</v>
       </c>
@@ -15461,7 +15516,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42" s="38"/>
       <c r="B42" s="36" t="s">
         <v>31</v>
       </c>
@@ -15499,7 +15555,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43" s="38"/>
       <c r="B43" s="35" t="s">
         <v>31</v>
       </c>
@@ -15537,7 +15594,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44" s="38"/>
       <c r="B44" s="36" t="s">
         <v>31</v>
       </c>
@@ -15575,7 +15633,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A45" s="38"/>
       <c r="B45" s="35" t="s">
         <v>31</v>
       </c>
@@ -15613,7 +15672,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A46" s="38"/>
       <c r="B46" s="36" t="s">
         <v>31</v>
       </c>
@@ -15651,7 +15711,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A47" s="38"/>
       <c r="B47" s="35" t="s">
         <v>31</v>
       </c>
@@ -15689,7 +15750,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A48" s="38"/>
       <c r="B48" s="36" t="s">
         <v>31</v>
       </c>
@@ -15727,7 +15789,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A49" s="38"/>
       <c r="B49" s="35" t="s">
         <v>31</v>
       </c>
@@ -15765,7 +15828,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A50" s="38"/>
       <c r="B50" s="36" t="s">
         <v>31</v>
       </c>
@@ -15803,7 +15867,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A51" s="38"/>
       <c r="B51" s="35" t="s">
         <v>31</v>
       </c>
@@ -15841,7 +15906,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A52" s="38"/>
       <c r="B52" s="36" t="s">
         <v>31</v>
       </c>
@@ -15879,7 +15945,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A53" s="38"/>
       <c r="B53" s="35" t="s">
         <v>31</v>
       </c>
@@ -15917,7 +15984,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A54" s="38"/>
       <c r="B54" s="36" t="s">
         <v>31</v>
       </c>
@@ -15955,7 +16023,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="55" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A55" s="38"/>
       <c r="B55" s="35" t="s">
         <v>31</v>
       </c>
@@ -15993,7 +16062,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="56" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A56" s="38"/>
       <c r="B56" s="36" t="s">
         <v>31</v>
       </c>
@@ -16031,7 +16101,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="57" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A57" s="38"/>
       <c r="B57" s="35" t="s">
         <v>31</v>
       </c>
@@ -16069,7 +16140,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="58" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A58" s="38"/>
       <c r="B58" s="36" t="s">
         <v>31</v>
       </c>
@@ -16107,7 +16179,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="59" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A59" s="38"/>
       <c r="B59" s="35" t="s">
         <v>31</v>
       </c>
@@ -16145,7 +16218,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="60" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A60" s="38"/>
       <c r="B60" s="36" t="s">
         <v>31</v>
       </c>
@@ -16183,7 +16257,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="61" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A61" s="38"/>
       <c r="B61" s="35" t="s">
         <v>31</v>
       </c>
@@ -16221,7 +16296,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="62" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A62" s="38"/>
       <c r="B62" s="36" t="s">
         <v>31</v>
       </c>
@@ -16259,7 +16335,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="63" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A63" s="38"/>
       <c r="B63" s="35" t="s">
         <v>31</v>
       </c>
@@ -16297,7 +16374,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="64" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A64" s="38"/>
       <c r="B64" s="36" t="s">
         <v>31</v>
       </c>
@@ -16335,7 +16413,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A65" s="38"/>
       <c r="B65" s="35" t="s">
         <v>31</v>
       </c>
@@ -16373,7 +16452,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A66" s="38"/>
       <c r="B66" s="36" t="s">
         <v>31</v>
       </c>
@@ -16411,7 +16491,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A67" s="38"/>
       <c r="B67" s="35" t="s">
         <v>31</v>
       </c>
@@ -16449,7 +16530,8 @@
         <v>403</v>
       </c>
     </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A68" s="38"/>
       <c r="B68" s="36" t="s">
         <v>31</v>
       </c>
@@ -16477,10 +16559,11 @@
       <c r="J68" s="33"/>
       <c r="K68" s="33"/>
       <c r="L68" s="33" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.3">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A69" s="38"/>
       <c r="B69" s="35" t="s">
         <v>31</v>
       </c>
@@ -16492,7 +16575,7 @@
         <v>49</v>
       </c>
       <c r="E69" s="35" t="str">
-        <f t="shared" ref="E69:E84" si="3">SUBSTITUTE(H69,"-sbn","")&amp;"-nsg"</f>
+        <f t="shared" ref="E69:E83" si="3">SUBSTITUTE(H69,"-sbn","")&amp;"-nsg"</f>
         <v>d-dis-pe-nsg</v>
       </c>
       <c r="F69" s="35" t="s">
@@ -16508,10 +16591,11 @@
       <c r="J69" s="35"/>
       <c r="K69" s="35"/>
       <c r="L69" s="35" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.3">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A70" s="38"/>
       <c r="B70" s="36" t="s">
         <v>31</v>
       </c>
@@ -16539,10 +16623,11 @@
       <c r="J70" s="33"/>
       <c r="K70" s="33"/>
       <c r="L70" s="33" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.3">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A71" s="38"/>
       <c r="B71" s="35" t="s">
         <v>31</v>
       </c>
@@ -16570,10 +16655,11 @@
       <c r="J71" s="35"/>
       <c r="K71" s="35"/>
       <c r="L71" s="35" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.3">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A72" s="38"/>
       <c r="B72" s="36" t="s">
         <v>31</v>
       </c>
@@ -16601,10 +16687,11 @@
       <c r="J72" s="33"/>
       <c r="K72" s="33"/>
       <c r="L72" s="33" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.3">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A73" s="38"/>
       <c r="B73" s="35" t="s">
         <v>31</v>
       </c>
@@ -16632,10 +16719,11 @@
       <c r="J73" s="35"/>
       <c r="K73" s="35"/>
       <c r="L73" s="35" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.3">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A74" s="38"/>
       <c r="B74" s="36" t="s">
         <v>31</v>
       </c>
@@ -16663,10 +16751,11 @@
       <c r="J74" s="33"/>
       <c r="K74" s="33"/>
       <c r="L74" s="33" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.3">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A75" s="38"/>
       <c r="B75" s="35" t="s">
         <v>31</v>
       </c>
@@ -16694,10 +16783,11 @@
       <c r="J75" s="35"/>
       <c r="K75" s="35"/>
       <c r="L75" s="35" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.3">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A76" s="38"/>
       <c r="B76" s="36" t="s">
         <v>31</v>
       </c>
@@ -16725,10 +16815,11 @@
       <c r="J76" s="33"/>
       <c r="K76" s="33"/>
       <c r="L76" s="33" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.3">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A77" s="38"/>
       <c r="B77" s="35" t="s">
         <v>31</v>
       </c>
@@ -16756,10 +16847,11 @@
       <c r="J77" s="35"/>
       <c r="K77" s="35"/>
       <c r="L77" s="35" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="78" spans="2:12" x14ac:dyDescent="0.3">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A78" s="38"/>
       <c r="B78" s="36" t="s">
         <v>31</v>
       </c>
@@ -16787,41 +16879,41 @@
       <c r="J78" s="33"/>
       <c r="K78" s="33"/>
       <c r="L78" s="33" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A79" s="38"/>
+      <c r="B79" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="35" t="s">
+        <v>439</v>
+      </c>
+      <c r="D79" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="E79" s="35" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B79" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="35" t="str" cm="1">
-        <f t="array" ref="C79">UPPER(INDEX(_xlfn.TEXTSPLIT($E79, "-"), 2))</f>
-        <v>COM</v>
-      </c>
-      <c r="D79" s="35" t="s">
-        <v>49</v>
-      </c>
-      <c r="E79" s="35" t="str">
-        <f t="shared" si="3"/>
-        <v>d-com-pe-nsg</v>
-      </c>
       <c r="F79" s="35" t="s">
         <v>49</v>
       </c>
       <c r="G79" s="35" t="s">
-        <v>188</v>
+        <v>57</v>
       </c>
       <c r="H79" s="35" t="s">
-        <v>434</v>
+        <v>156</v>
       </c>
       <c r="I79" s="35"/>
       <c r="J79" s="35"/>
       <c r="K79" s="35"/>
       <c r="L79" s="35" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.3">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A80" s="38"/>
       <c r="B80" s="36" t="s">
         <v>31</v>
       </c>
@@ -16834,7 +16926,7 @@
       </c>
       <c r="E80" s="33" t="str">
         <f t="shared" si="3"/>
-        <v>d-com-db-nsg</v>
+        <v>d-com-pe-nsg</v>
       </c>
       <c r="F80" s="33" t="s">
         <v>49</v>
@@ -16843,29 +16935,30 @@
         <v>188</v>
       </c>
       <c r="H80" s="33" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I80" s="33"/>
       <c r="J80" s="33"/>
       <c r="K80" s="33"/>
       <c r="L80" s="33" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="81" spans="2:12" x14ac:dyDescent="0.3">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A81" s="38"/>
       <c r="B81" s="35" t="s">
         <v>31</v>
       </c>
       <c r="C81" s="35" t="str" cm="1">
         <f t="array" ref="C81">UPPER(INDEX(_xlfn.TEXTSPLIT($E81, "-"), 2))</f>
-        <v>IF</v>
+        <v>COM</v>
       </c>
       <c r="D81" s="35" t="s">
         <v>49</v>
       </c>
       <c r="E81" s="35" t="str">
         <f t="shared" si="3"/>
-        <v>d-if-db-nsg</v>
+        <v>d-com-db-nsg</v>
       </c>
       <c r="F81" s="35" t="s">
         <v>49</v>
@@ -16874,16 +16967,17 @@
         <v>188</v>
       </c>
       <c r="H81" s="35" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="I81" s="35"/>
       <c r="J81" s="35"/>
       <c r="K81" s="35"/>
       <c r="L81" s="35" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="82" spans="2:12" x14ac:dyDescent="0.3">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A82" s="38"/>
       <c r="B82" s="36" t="s">
         <v>31</v>
       </c>
@@ -16896,7 +16990,7 @@
       </c>
       <c r="E82" s="33" t="str">
         <f t="shared" si="3"/>
-        <v>d-if-pe-nsg</v>
+        <v>d-if-db-nsg</v>
       </c>
       <c r="F82" s="33" t="s">
         <v>49</v>
@@ -16905,29 +16999,30 @@
         <v>188</v>
       </c>
       <c r="H82" s="33" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I82" s="33"/>
       <c r="J82" s="33"/>
       <c r="K82" s="33"/>
       <c r="L82" s="33" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="83" spans="2:12" x14ac:dyDescent="0.3">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A83" s="38"/>
       <c r="B83" s="35" t="s">
         <v>31</v>
       </c>
       <c r="C83" s="35" t="str" cm="1">
         <f t="array" ref="C83">UPPER(INDEX(_xlfn.TEXTSPLIT($E83, "-"), 2))</f>
-        <v>CS</v>
+        <v>IF</v>
       </c>
       <c r="D83" s="35" t="s">
         <v>49</v>
       </c>
       <c r="E83" s="35" t="str">
         <f t="shared" si="3"/>
-        <v>d-cs-db-nsg</v>
+        <v>d-if-pe-nsg</v>
       </c>
       <c r="F83" s="35" t="s">
         <v>49</v>
@@ -16936,48 +17031,20 @@
         <v>188</v>
       </c>
       <c r="H83" s="35" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="I83" s="35"/>
       <c r="J83" s="35"/>
       <c r="K83" s="35"/>
       <c r="L83" s="35" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="84" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B84" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="C84" s="36" t="str" cm="1">
-        <f t="array" ref="C84">UPPER(INDEX(_xlfn.TEXTSPLIT($E84, "-"), 2))</f>
-        <v>CS</v>
-      </c>
-      <c r="D84" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="E84" s="33" t="str">
-        <f t="shared" si="3"/>
-        <v>d-cs-pe-nsg</v>
-      </c>
-      <c r="F84" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="G84" s="33" t="s">
-        <v>188</v>
-      </c>
-      <c r="H84" s="33" t="s">
-        <v>439</v>
-      </c>
-      <c r="I84" s="33"/>
-      <c r="J84" s="33"/>
-      <c r="K84" s="33"/>
-      <c r="L84" s="33" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="E2:E83">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -16994,12 +17061,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -17143,6 +17204,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
@@ -17152,22 +17219,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17183,4 +17234,20 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/서버정보/20260422_리소스배포_개발.xlsx
+++ b/서버정보/20260422_리소스배포_개발.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD983E1A-522C-4B4B-BFCE-473DE8282E25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFD0380B-7FA5-4AB6-85D3-F5119F8B1F58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -573,7 +573,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2530" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2529" uniqueCount="435">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1632,482 +1632,466 @@
     <t>hazr-d-dip-web01</t>
   </si>
   <si>
+    <t>hazr-d-if-rg</t>
+  </si>
+  <si>
+    <t>hazr-d-if-gramon01</t>
+  </si>
+  <si>
+    <t>10.156.165.10</t>
+  </si>
+  <si>
+    <t>d-if-ap-sbn</t>
+  </si>
+  <si>
+    <t>hazr-d-doip-rg</t>
+  </si>
+  <si>
+    <t>hazr-d-doip-web01</t>
+  </si>
+  <si>
+    <t>10.156.150.10</t>
+  </si>
+  <si>
+    <t>d-doip-ap-sbn</t>
+  </si>
+  <si>
+    <t>hazr-d-doip-ap01</t>
+  </si>
+  <si>
+    <t>10.156.150.20</t>
+  </si>
+  <si>
+    <t>hazr-d-doip-adm01</t>
+  </si>
+  <si>
+    <t>10.156.150.30</t>
+  </si>
+  <si>
+    <t>hazr-d-bdp-crkweb01</t>
+  </si>
+  <si>
+    <t>10.156.132.10</t>
+  </si>
+  <si>
+    <t>d-bdp-web-sbn</t>
+  </si>
+  <si>
+    <t>hazr-d-bdp-crkap01</t>
+  </si>
+  <si>
+    <t>10.156.156.50</t>
+  </si>
+  <si>
+    <t>hazr-d-bdp-crkml01</t>
+  </si>
+  <si>
+    <t>10.156.156.60</t>
+  </si>
+  <si>
+    <t>StandardSSD_LRS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dip-rg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dip-kfk02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dip-kfk03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dis-dfir01</t>
+  </si>
+  <si>
+    <t>10.156.144.130</t>
+  </si>
+  <si>
+    <t>DIS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DCH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>COM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DOIP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DTG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BDP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PULS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-puls-rg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/Windows_Server_2025_Base_Image/versions/0.0.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hwgiifadmin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VMName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Datadisk1Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Datadisk2Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DataDisk1Type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Datadisk1Size</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DataDisk2Type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Datadisk2Size</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dch-des</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DoubleEncryption</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HostCaching</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DESRG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EnableAcceleratedNetworking</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">UseOsDiskDoubleEncryption </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-bdp-crkap01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dtg-cdsvadm01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-bdp-cxmadm01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.6_nginx_Base_Image/versions/0.0.2</t>
+  </si>
+  <si>
+    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.6_nginx_Base_Image/versions/0.0.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dis-adm01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dis-bbiweb01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dis-cmsadm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dis-cmsweb01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dis-drvcltap01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dis-web01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dis-cmsadm01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dtg-admweb01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dtg-admap01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dtg-tsdb01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dtg-web01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dtg-mdoms01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dtg-diosweb01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dtg-dprweb01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-bdp-airfw01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-bdp-kepler01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-bdp-slap01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dip-adm01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dip-ap01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dip-mqweb01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dip-oms01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dip-web01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-bdp-crkweb01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dis-cmbsap01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>O</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-doip-web01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-doip-adm01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dis-dfir01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dis-bbicltap01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dis-walkap01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dis-drvmsgap01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dtg-ingap01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dtg-extgeoap01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dtg-mq01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dtg-zkp01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dtg-zkp03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dtg-kfk02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dtg-cdstap01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dtg-diosap01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dip-flk01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dip-flk03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-dip-kfk01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>d-dip-ap-sbn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NicRG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>d-dis-db-sbn</t>
+  </si>
+  <si>
+    <t>d-dis-pe-sbn</t>
+  </si>
+  <si>
+    <t>d-puls-db-sbn</t>
+  </si>
+  <si>
+    <t>d-puls-pe-sbn</t>
+  </si>
+  <si>
+    <t>d-doip-db-sbn</t>
+  </si>
+  <si>
+    <t>d-doip-pe-sbn</t>
+  </si>
+  <si>
+    <t>d-ddg-db-sbn</t>
+  </si>
+  <si>
+    <t>d-ddg-pe-sbn</t>
+  </si>
+  <si>
+    <t>d-bdp-db-sbn</t>
+  </si>
+  <si>
+    <t>d-bdp-pe-sbn</t>
+  </si>
+  <si>
+    <t>d-dip-db-sbn</t>
+  </si>
+  <si>
+    <t>d-com-pe-sbn</t>
+  </si>
+  <si>
+    <t>d-com-db-sbn</t>
+  </si>
+  <si>
+    <t>d-if-db-sbn</t>
+  </si>
+  <si>
+    <t>d-if-pe-sbn</t>
+  </si>
+  <si>
+    <t>X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DIP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>d-dip-pe-nsg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-if-auth01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-d-if-proxy01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>10.156.159.90</t>
-  </si>
-  <si>
-    <t>hazr-d-com-rg</t>
-  </si>
-  <si>
-    <t>hazr-d-com-auth01</t>
-  </si>
-  <si>
-    <t>10.156.162.10</t>
-  </si>
-  <si>
-    <t>d-com-ap-sbn</t>
-  </si>
-  <si>
-    <t>hazr-d-com-proxy01</t>
-  </si>
-  <si>
-    <t>10.156.134.10</t>
-  </si>
-  <si>
-    <t>d-com-web-sbn</t>
-  </si>
-  <si>
-    <t>hazr-d-if-rg</t>
-  </si>
-  <si>
-    <t>hazr-d-if-gramon01</t>
-  </si>
-  <si>
-    <t>10.156.165.10</t>
-  </si>
-  <si>
-    <t>d-if-ap-sbn</t>
-  </si>
-  <si>
-    <t>hazr-d-doip-rg</t>
-  </si>
-  <si>
-    <t>hazr-d-doip-web01</t>
-  </si>
-  <si>
-    <t>10.156.150.10</t>
-  </si>
-  <si>
-    <t>d-doip-ap-sbn</t>
-  </si>
-  <si>
-    <t>hazr-d-doip-ap01</t>
-  </si>
-  <si>
-    <t>10.156.150.20</t>
-  </si>
-  <si>
-    <t>hazr-d-doip-adm01</t>
-  </si>
-  <si>
-    <t>10.156.150.30</t>
-  </si>
-  <si>
-    <t>hazr-d-bdp-crkweb01</t>
-  </si>
-  <si>
-    <t>10.156.132.10</t>
-  </si>
-  <si>
-    <t>d-bdp-web-sbn</t>
-  </si>
-  <si>
-    <t>hazr-d-bdp-crkap01</t>
-  </si>
-  <si>
-    <t>10.156.156.50</t>
-  </si>
-  <si>
-    <t>hazr-d-bdp-crkml01</t>
-  </si>
-  <si>
-    <t>10.156.156.60</t>
-  </si>
-  <si>
-    <t>StandardSSD_LRS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dip-rg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dip-kfk02</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dip-kfk03</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dis-dfir01</t>
-  </si>
-  <si>
-    <t>10.156.144.130</t>
-  </si>
-  <si>
-    <t>DIS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DCH</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>COM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DOIP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DTG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>IF</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BDP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PULS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-puls-rg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/Windows_Server_2025_Base_Image/versions/0.0.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Q</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hwgiifadmin</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>VMName</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Zone</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Datadisk1Name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Datadisk2Name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DataDisk1Type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Datadisk1Size</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DataDisk2Type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Datadisk2Size</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dch-des</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DoubleEncryption</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HostCaching</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>None</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DESRG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>EnableAcceleratedNetworking</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">UseOsDiskDoubleEncryption </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-bdp-crkap01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dtg-cdsvadm01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-bdp-cxmadm01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.6_nginx_Base_Image/versions/0.0.2</t>
-  </si>
-  <si>
-    <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.6_nginx_Base_Image/versions/0.0.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dis-adm01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dis-bbiweb01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dis-cmsadm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dis-cmsweb01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dis-drvcltap01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dis-web01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dis-cmsadm01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dtg-admweb01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dtg-admap01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dtg-tsdb01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dtg-web01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dtg-mdoms01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dtg-diosweb01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dtg-dprweb01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-bdp-airfw01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-bdp-kepler01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-bdp-slap01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dip-adm01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dip-ap01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dip-mqweb01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dip-oms01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dip-web01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-com-auth01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-com-proxy01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-bdp-crkweb01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dis-cmbsap01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>O</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-doip-web01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-doip-adm01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dis-dfir01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dis-bbicltap01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dis-walkap01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dis-drvmsgap01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dtg-ingap01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dtg-extgeoap01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dtg-mq01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dtg-zkp01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dtg-zkp03</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dtg-kfk02</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dtg-cdstap01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dtg-diosap01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dip-flk01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dip-flk03</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-d-dip-kfk01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>d-dip-ap-sbn</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NicRG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>d-dis-db-sbn</t>
-  </si>
-  <si>
-    <t>d-dis-pe-sbn</t>
-  </si>
-  <si>
-    <t>d-puls-db-sbn</t>
-  </si>
-  <si>
-    <t>d-puls-pe-sbn</t>
-  </si>
-  <si>
-    <t>d-doip-db-sbn</t>
-  </si>
-  <si>
-    <t>d-doip-pe-sbn</t>
-  </si>
-  <si>
-    <t>d-ddg-db-sbn</t>
-  </si>
-  <si>
-    <t>d-ddg-pe-sbn</t>
-  </si>
-  <si>
-    <t>d-bdp-db-sbn</t>
-  </si>
-  <si>
-    <t>d-bdp-pe-sbn</t>
-  </si>
-  <si>
-    <t>d-dip-db-sbn</t>
-  </si>
-  <si>
-    <t>d-com-pe-sbn</t>
-  </si>
-  <si>
-    <t>d-com-db-sbn</t>
-  </si>
-  <si>
-    <t>d-if-db-sbn</t>
-  </si>
-  <si>
-    <t>d-if-pe-sbn</t>
-  </si>
-  <si>
-    <t>X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DIP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>d-dip-pe-nsg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.156.135.10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.156.165.20</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2351,7 +2335,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2467,6 +2451,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4021,7 +4008,7 @@
         <v>31</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>49</v>
@@ -4037,7 +4024,7 @@
         <v>31</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>50</v>
@@ -4053,7 +4040,7 @@
         <v>31</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>51</v>
@@ -4069,7 +4056,7 @@
         <v>31</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>52</v>
@@ -4085,7 +4072,7 @@
         <v>31</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>53</v>
@@ -4101,7 +4088,7 @@
         <v>31</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>54</v>
@@ -4117,7 +4104,7 @@
         <v>31</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>55</v>
@@ -4133,7 +4120,7 @@
         <v>31</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>184</v>
@@ -4149,10 +4136,10 @@
         <v>31</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>23</v>
@@ -4271,7 +4258,7 @@
         <v>17</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="W1" s="3" t="s">
         <v>18</v>
@@ -4286,10 +4273,10 @@
         <v>20</v>
       </c>
       <c r="AA1" s="3" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="AB1" s="3" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="AC1" s="3" t="s">
         <v>48</v>
@@ -4335,7 +4322,7 @@
         <v>8</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>182</v>
@@ -4354,7 +4341,7 @@
         <v>64</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
@@ -4385,7 +4372,7 @@
         <v>49</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD2" s="1">
         <v>1</v>
@@ -4409,7 +4396,7 @@
         <v>23</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>194</v>
@@ -4424,7 +4411,7 @@
         <v>8</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L3" s="9" t="s">
         <v>182</v>
@@ -4433,7 +4420,7 @@
         <v>191</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="O3" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4443,7 +4430,7 @@
         <v>64</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
@@ -4474,7 +4461,7 @@
         <v>49</v>
       </c>
       <c r="AC3" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD3" s="1">
         <v>1</v>
@@ -4498,7 +4485,7 @@
         <v>23</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>196</v>
@@ -4513,7 +4500,7 @@
         <v>8</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>181</v>
@@ -4522,7 +4509,7 @@
         <v>191</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="O4" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4532,7 +4519,7 @@
         <v>64</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
@@ -4563,7 +4550,7 @@
         <v>49</v>
       </c>
       <c r="AC4" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD4" s="1">
         <v>1</v>
@@ -4602,7 +4589,7 @@
         <v>8</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L5" s="9" t="s">
         <v>181</v>
@@ -4621,7 +4608,7 @@
         <v>64</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
@@ -4652,7 +4639,7 @@
         <v>49</v>
       </c>
       <c r="AC5" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD5" s="1">
         <v>1</v>
@@ -4691,7 +4678,7 @@
         <v>8</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>181</v>
@@ -4710,7 +4697,7 @@
         <v>64</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
@@ -4741,7 +4728,7 @@
         <v>49</v>
       </c>
       <c r="AC6" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD6" s="1">
         <v>1</v>
@@ -4780,7 +4767,7 @@
         <v>8</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L7" s="9" t="s">
         <v>181</v>
@@ -4799,7 +4786,7 @@
         <v>64</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
@@ -4830,7 +4817,7 @@
         <v>49</v>
       </c>
       <c r="AC7" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD7" s="1">
         <v>1</v>
@@ -4869,7 +4856,7 @@
         <v>8</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>181</v>
@@ -4888,7 +4875,7 @@
         <v>64</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
@@ -4919,7 +4906,7 @@
         <v>49</v>
       </c>
       <c r="AC8" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD8" s="1">
         <v>1</v>
@@ -4940,10 +4927,10 @@
         <v>186</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>210</v>
@@ -4958,7 +4945,7 @@
         <v>8</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>181</v>
@@ -4977,7 +4964,7 @@
         <v>64</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
@@ -5008,7 +4995,7 @@
         <v>49</v>
       </c>
       <c r="AC9" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD9" s="1">
         <v>1</v>
@@ -5047,7 +5034,7 @@
         <v>8</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L10" s="9" t="s">
         <v>181</v>
@@ -5056,7 +5043,7 @@
         <v>191</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="O10" s="1" t="str">
         <f t="shared" si="0"/>
@@ -5066,7 +5053,7 @@
         <v>64</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
@@ -5097,7 +5084,7 @@
         <v>49</v>
       </c>
       <c r="AC10" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD10" s="1">
         <v>1</v>
@@ -5136,7 +5123,7 @@
         <v>8</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>181</v>
@@ -5155,7 +5142,7 @@
         <v>64</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
@@ -5186,7 +5173,7 @@
         <v>49</v>
       </c>
       <c r="AC11" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD11" s="1">
         <v>1</v>
@@ -5210,7 +5197,7 @@
         <v>23</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>216</v>
@@ -5225,7 +5212,7 @@
         <v>8</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L12" s="9" t="s">
         <v>181</v>
@@ -5234,7 +5221,7 @@
         <v>191</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="O12" s="1" t="str">
         <f t="shared" si="0"/>
@@ -5244,7 +5231,7 @@
         <v>64</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
@@ -5275,7 +5262,7 @@
         <v>49</v>
       </c>
       <c r="AC12" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD12" s="1">
         <v>1</v>
@@ -5299,7 +5286,7 @@
         <v>23</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>218</v>
@@ -5314,7 +5301,7 @@
         <v>8</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L13" s="1" t="s">
         <v>181</v>
@@ -5323,7 +5310,7 @@
         <v>191</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="O13" s="1" t="str">
         <f t="shared" si="0"/>
@@ -5333,7 +5320,7 @@
         <v>64</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
@@ -5364,7 +5351,7 @@
         <v>49</v>
       </c>
       <c r="AC13" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD13" s="1">
         <v>1</v>
@@ -5403,7 +5390,7 @@
         <v>8</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L14" s="9" t="s">
         <v>181</v>
@@ -5422,7 +5409,7 @@
         <v>64</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
@@ -5453,7 +5440,7 @@
         <v>49</v>
       </c>
       <c r="AC14" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD14" s="1">
         <v>1</v>
@@ -5477,7 +5464,7 @@
         <v>23</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>222</v>
@@ -5492,7 +5479,7 @@
         <v>8</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L15" s="1" t="s">
         <v>181</v>
@@ -5501,7 +5488,7 @@
         <v>191</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="O15" s="1" t="str">
         <f t="shared" si="0"/>
@@ -5511,7 +5498,7 @@
         <v>64</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
@@ -5542,7 +5529,7 @@
         <v>49</v>
       </c>
       <c r="AC15" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD15" s="1">
         <v>1</v>
@@ -5566,7 +5553,7 @@
         <v>23</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>224</v>
@@ -5581,7 +5568,7 @@
         <v>8</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L16" s="9" t="s">
         <v>181</v>
@@ -5600,7 +5587,7 @@
         <v>64</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
@@ -5631,7 +5618,7 @@
         <v>49</v>
       </c>
       <c r="AC16" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD16" s="1">
         <v>1</v>
@@ -5670,7 +5657,7 @@
         <v>8</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L17" s="9" t="s">
         <v>181</v>
@@ -5689,7 +5676,7 @@
         <v>64</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
@@ -5720,7 +5707,7 @@
         <v>49</v>
       </c>
       <c r="AC17" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD17" s="1">
         <v>1</v>
@@ -5759,7 +5746,7 @@
         <v>8</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L18" s="1" t="s">
         <v>181</v>
@@ -5778,7 +5765,7 @@
         <v>64</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
@@ -5809,7 +5796,7 @@
         <v>49</v>
       </c>
       <c r="AC18" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD18" s="1">
         <v>1</v>
@@ -5848,7 +5835,7 @@
         <v>8</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L19" s="9" t="s">
         <v>181</v>
@@ -5867,7 +5854,7 @@
         <v>64</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
@@ -5898,7 +5885,7 @@
         <v>49</v>
       </c>
       <c r="AC19" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD19" s="1">
         <v>1</v>
@@ -5937,7 +5924,7 @@
         <v>8</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L20" s="1" t="s">
         <v>181</v>
@@ -5956,7 +5943,7 @@
         <v>64</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
@@ -5987,7 +5974,7 @@
         <v>49</v>
       </c>
       <c r="AC20" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD20" s="1">
         <v>1</v>
@@ -6026,7 +6013,7 @@
         <v>8</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L21" s="9" t="s">
         <v>181</v>
@@ -6045,7 +6032,7 @@
         <v>64</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
@@ -6076,7 +6063,7 @@
         <v>49</v>
       </c>
       <c r="AC21" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD21" s="1">
         <v>1</v>
@@ -6100,7 +6087,7 @@
         <v>23</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>239</v>
@@ -6115,7 +6102,7 @@
         <v>8</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L22" s="1" t="s">
         <v>181</v>
@@ -6124,7 +6111,7 @@
         <v>191</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="O22" s="1" t="str">
         <f t="shared" si="0"/>
@@ -6134,7 +6121,7 @@
         <v>64</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
@@ -6165,7 +6152,7 @@
         <v>49</v>
       </c>
       <c r="AC22" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD22" s="1">
         <v>1</v>
@@ -6189,7 +6176,7 @@
         <v>23</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>241</v>
@@ -6204,7 +6191,7 @@
         <v>8</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L23" s="9" t="s">
         <v>181</v>
@@ -6213,7 +6200,7 @@
         <v>191</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="O23" s="1" t="str">
         <f t="shared" si="0"/>
@@ -6223,7 +6210,7 @@
         <v>64</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
@@ -6254,7 +6241,7 @@
         <v>49</v>
       </c>
       <c r="AC23" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD23" s="1">
         <v>1</v>
@@ -6293,7 +6280,7 @@
         <v>8</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L24" s="1" t="s">
         <v>181</v>
@@ -6312,7 +6299,7 @@
         <v>64</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
@@ -6343,7 +6330,7 @@
         <v>49</v>
       </c>
       <c r="AC24" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD24" s="1">
         <v>1</v>
@@ -6367,7 +6354,7 @@
         <v>23</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>245</v>
@@ -6382,7 +6369,7 @@
         <v>32</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L25" s="9" t="s">
         <v>181</v>
@@ -6401,7 +6388,7 @@
         <v>64</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
@@ -6432,7 +6419,7 @@
         <v>49</v>
       </c>
       <c r="AC25" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD25" s="1">
         <v>1</v>
@@ -6456,7 +6443,7 @@
         <v>23</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="G26" s="10" t="s">
         <v>249</v>
@@ -6471,7 +6458,7 @@
         <v>8</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L26" s="1" t="s">
         <v>181</v>
@@ -6480,7 +6467,7 @@
         <v>191</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="O26" s="1" t="str">
         <f t="shared" si="0"/>
@@ -6490,7 +6477,7 @@
         <v>64</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
@@ -6521,7 +6508,7 @@
         <v>49</v>
       </c>
       <c r="AC26" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD26" s="1">
         <v>1</v>
@@ -6560,7 +6547,7 @@
         <v>8</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L27" s="9" t="s">
         <v>181</v>
@@ -6579,7 +6566,7 @@
         <v>64</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
@@ -6610,7 +6597,7 @@
         <v>49</v>
       </c>
       <c r="AC27" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD27" s="1">
         <v>1</v>
@@ -6649,7 +6636,7 @@
         <v>8</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L28" s="1" t="s">
         <v>181</v>
@@ -6668,7 +6655,7 @@
         <v>64</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
@@ -6699,7 +6686,7 @@
         <v>49</v>
       </c>
       <c r="AC28" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD28" s="1">
         <v>1</v>
@@ -6738,7 +6725,7 @@
         <v>8</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L29" s="9" t="s">
         <v>181</v>
@@ -6757,7 +6744,7 @@
         <v>64</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
@@ -6788,7 +6775,7 @@
         <v>49</v>
       </c>
       <c r="AC29" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD29" s="1">
         <v>1</v>
@@ -6827,7 +6814,7 @@
         <v>8</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L30" s="1" t="s">
         <v>181</v>
@@ -6846,7 +6833,7 @@
         <v>64</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
@@ -6877,7 +6864,7 @@
         <v>49</v>
       </c>
       <c r="AC30" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD30" s="1">
         <v>1</v>
@@ -6916,7 +6903,7 @@
         <v>8</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L31" s="9" t="s">
         <v>181</v>
@@ -6935,7 +6922,7 @@
         <v>64</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
@@ -6966,7 +6953,7 @@
         <v>49</v>
       </c>
       <c r="AC31" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD31" s="1">
         <v>1</v>
@@ -7005,7 +6992,7 @@
         <v>8</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L32" s="1" t="s">
         <v>181</v>
@@ -7024,7 +7011,7 @@
         <v>64</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
@@ -7055,7 +7042,7 @@
         <v>49</v>
       </c>
       <c r="AC32" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD32" s="1">
         <v>1</v>
@@ -7079,7 +7066,7 @@
         <v>23</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>263</v>
@@ -7094,7 +7081,7 @@
         <v>8</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L33" s="9" t="s">
         <v>181</v>
@@ -7103,7 +7090,7 @@
         <v>191</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="O33" s="1" t="str">
         <f t="shared" ref="O33:O61" si="2">SUBSTITUTE(F33,"hazr-","")&amp;"-osdisk"</f>
@@ -7113,7 +7100,7 @@
         <v>64</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
@@ -7144,7 +7131,7 @@
         <v>49</v>
       </c>
       <c r="AC33" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD33" s="1">
         <v>1</v>
@@ -7183,7 +7170,7 @@
         <v>8</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L34" s="1" t="s">
         <v>181</v>
@@ -7202,7 +7189,7 @@
         <v>64</v>
       </c>
       <c r="Q34" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
@@ -7233,7 +7220,7 @@
         <v>49</v>
       </c>
       <c r="AC34" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD34" s="1">
         <v>1</v>
@@ -7272,7 +7259,7 @@
         <v>8</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L35" s="9" t="s">
         <v>181</v>
@@ -7291,7 +7278,7 @@
         <v>64</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R35" s="1"/>
       <c r="S35" s="1"/>
@@ -7322,7 +7309,7 @@
         <v>49</v>
       </c>
       <c r="AC35" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD35" s="1">
         <v>1</v>
@@ -7346,7 +7333,7 @@
         <v>23</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>268</v>
@@ -7361,7 +7348,7 @@
         <v>8</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L36" s="1" t="s">
         <v>181</v>
@@ -7370,7 +7357,7 @@
         <v>191</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="O36" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7380,7 +7367,7 @@
         <v>64</v>
       </c>
       <c r="Q36" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
@@ -7411,7 +7398,7 @@
         <v>49</v>
       </c>
       <c r="AC36" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD36" s="1">
         <v>1</v>
@@ -7450,7 +7437,7 @@
         <v>8</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L37" s="9" t="s">
         <v>181</v>
@@ -7469,7 +7456,7 @@
         <v>64</v>
       </c>
       <c r="Q37" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R37" s="1"/>
       <c r="S37" s="1"/>
@@ -7500,7 +7487,7 @@
         <v>49</v>
       </c>
       <c r="AC37" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD37" s="1">
         <v>1</v>
@@ -7524,7 +7511,7 @@
         <v>23</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>272</v>
@@ -7539,7 +7526,7 @@
         <v>8</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L38" s="1" t="s">
         <v>181</v>
@@ -7548,7 +7535,7 @@
         <v>191</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="O38" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7558,7 +7545,7 @@
         <v>64</v>
       </c>
       <c r="Q38" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R38" s="1"/>
       <c r="S38" s="1"/>
@@ -7589,7 +7576,7 @@
         <v>49</v>
       </c>
       <c r="AC38" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD38" s="1">
         <v>1</v>
@@ -7613,7 +7600,7 @@
         <v>23</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>274</v>
@@ -7628,7 +7615,7 @@
         <v>8</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L39" s="9" t="s">
         <v>181</v>
@@ -7637,7 +7624,7 @@
         <v>191</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="O39" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7647,7 +7634,7 @@
         <v>64</v>
       </c>
       <c r="Q39" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R39" s="1"/>
       <c r="S39" s="1"/>
@@ -7678,7 +7665,7 @@
         <v>49</v>
       </c>
       <c r="AC39" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD39" s="1">
         <v>1</v>
@@ -7717,7 +7704,7 @@
         <v>8</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L40" s="1" t="s">
         <v>181</v>
@@ -7736,7 +7723,7 @@
         <v>64</v>
       </c>
       <c r="Q40" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R40" s="1"/>
       <c r="S40" s="1"/>
@@ -7767,7 +7754,7 @@
         <v>49</v>
       </c>
       <c r="AC40" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD40" s="1">
         <v>1</v>
@@ -7791,7 +7778,7 @@
         <v>23</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>279</v>
@@ -7806,7 +7793,7 @@
         <v>8</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L41" s="9" t="s">
         <v>181</v>
@@ -7815,7 +7802,7 @@
         <v>191</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="O41" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7825,7 +7812,7 @@
         <v>64</v>
       </c>
       <c r="Q41" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R41" s="1"/>
       <c r="S41" s="1"/>
@@ -7856,7 +7843,7 @@
         <v>49</v>
       </c>
       <c r="AC41" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD41" s="1">
         <v>1</v>
@@ -7880,7 +7867,7 @@
         <v>23</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>282</v>
@@ -7895,7 +7882,7 @@
         <v>8</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L42" s="1" t="s">
         <v>181</v>
@@ -7904,7 +7891,7 @@
         <v>191</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="O42" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7914,7 +7901,7 @@
         <v>64</v>
       </c>
       <c r="Q42" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R42" s="1"/>
       <c r="S42" s="1"/>
@@ -7945,7 +7932,7 @@
         <v>49</v>
       </c>
       <c r="AC42" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD42" s="1">
         <v>1</v>
@@ -7969,7 +7956,7 @@
         <v>23</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>283</v>
@@ -7984,7 +7971,7 @@
         <v>8</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L43" s="9" t="s">
         <v>181</v>
@@ -7993,7 +7980,7 @@
         <v>191</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="O43" s="1" t="str">
         <f t="shared" si="2"/>
@@ -8003,7 +7990,7 @@
         <v>64</v>
       </c>
       <c r="Q43" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R43" s="1"/>
       <c r="S43" s="1"/>
@@ -8034,7 +8021,7 @@
         <v>49</v>
       </c>
       <c r="AC43" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD43" s="1">
         <v>1</v>
@@ -8058,7 +8045,7 @@
         <v>23</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>285</v>
@@ -8073,7 +8060,7 @@
         <v>8</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L44" s="1" t="s">
         <v>181</v>
@@ -8082,7 +8069,7 @@
         <v>191</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="O44" s="1" t="str">
         <f t="shared" si="2"/>
@@ -8092,7 +8079,7 @@
         <v>64</v>
       </c>
       <c r="Q44" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
@@ -8123,7 +8110,7 @@
         <v>49</v>
       </c>
       <c r="AC44" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD44" s="1">
         <v>1</v>
@@ -8141,13 +8128,13 @@
         <v>DIP</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>287</v>
@@ -8162,7 +8149,7 @@
         <v>8</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L45" s="9" t="s">
         <v>181</v>
@@ -8171,7 +8158,7 @@
         <v>191</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="O45" s="1" t="str">
         <f t="shared" si="2"/>
@@ -8181,7 +8168,7 @@
         <v>64</v>
       </c>
       <c r="Q45" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R45" s="1"/>
       <c r="S45" s="1"/>
@@ -8212,7 +8199,7 @@
         <v>49</v>
       </c>
       <c r="AC45" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD45" s="1">
         <v>1</v>
@@ -8230,13 +8217,13 @@
         <v>DIP</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>290</v>
@@ -8251,7 +8238,7 @@
         <v>8</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L46" s="1" t="s">
         <v>181</v>
@@ -8260,7 +8247,7 @@
         <v>191</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="O46" s="1" t="str">
         <f t="shared" si="2"/>
@@ -8270,7 +8257,7 @@
         <v>64</v>
       </c>
       <c r="Q46" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R46" s="1"/>
       <c r="S46" s="1"/>
@@ -8301,7 +8288,7 @@
         <v>49</v>
       </c>
       <c r="AC46" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD46" s="1">
         <v>1</v>
@@ -8319,7 +8306,7 @@
         <v>DIP</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>23</v>
@@ -8340,7 +8327,7 @@
         <v>8</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L47" s="9" t="s">
         <v>181</v>
@@ -8359,7 +8346,7 @@
         <v>64</v>
       </c>
       <c r="Q47" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R47" s="1"/>
       <c r="S47" s="1"/>
@@ -8390,7 +8377,7 @@
         <v>49</v>
       </c>
       <c r="AC47" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD47" s="1">
         <v>1</v>
@@ -8408,7 +8395,7 @@
         <v>DIP</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>23</v>
@@ -8429,7 +8416,7 @@
         <v>8</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L48" s="1" t="s">
         <v>181</v>
@@ -8448,7 +8435,7 @@
         <v>64</v>
       </c>
       <c r="Q48" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R48" s="1"/>
       <c r="S48" s="1"/>
@@ -8479,7 +8466,7 @@
         <v>49</v>
       </c>
       <c r="AC48" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD48" s="1">
         <v>1</v>
@@ -8497,7 +8484,7 @@
         <v>DIP</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>23</v>
@@ -8518,7 +8505,7 @@
         <v>8</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L49" s="9" t="s">
         <v>181</v>
@@ -8537,7 +8524,7 @@
         <v>64</v>
       </c>
       <c r="Q49" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R49" s="1"/>
       <c r="S49" s="1"/>
@@ -8568,7 +8555,7 @@
         <v>49</v>
       </c>
       <c r="AC49" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD49" s="1">
         <v>1</v>
@@ -8586,7 +8573,7 @@
         <v>DIP</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>23</v>
@@ -8607,7 +8594,7 @@
         <v>8</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L50" s="1" t="s">
         <v>181</v>
@@ -8626,7 +8613,7 @@
         <v>64</v>
       </c>
       <c r="Q50" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R50" s="1"/>
       <c r="S50" s="1"/>
@@ -8657,7 +8644,7 @@
         <v>49</v>
       </c>
       <c r="AC50" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD50" s="1">
         <v>1</v>
@@ -8675,7 +8662,7 @@
         <v>DIP</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>23</v>
@@ -8696,7 +8683,7 @@
         <v>8</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L51" s="9" t="s">
         <v>181</v>
@@ -8715,7 +8702,7 @@
         <v>64</v>
       </c>
       <c r="Q51" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R51" s="1"/>
       <c r="S51" s="1"/>
@@ -8746,7 +8733,7 @@
         <v>49</v>
       </c>
       <c r="AC51" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD51" s="1">
         <v>1</v>
@@ -8764,13 +8751,13 @@
         <v>DIP</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>301</v>
@@ -8785,7 +8772,7 @@
         <v>8</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L52" s="1" t="s">
         <v>181</v>
@@ -8804,7 +8791,7 @@
         <v>64</v>
       </c>
       <c r="Q52" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R52" s="1"/>
       <c r="S52" s="1"/>
@@ -8835,7 +8822,7 @@
         <v>49</v>
       </c>
       <c r="AC52" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD52" s="1">
         <v>1</v>
@@ -8853,13 +8840,13 @@
         <v>DIP</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>302</v>
@@ -8874,7 +8861,7 @@
         <v>8</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L53" s="9" t="s">
         <v>181</v>
@@ -8893,7 +8880,7 @@
         <v>64</v>
       </c>
       <c r="Q53" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R53" s="1"/>
       <c r="S53" s="1"/>
@@ -8924,7 +8911,7 @@
         <v>49</v>
       </c>
       <c r="AC53" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD53" s="1">
         <v>1</v>
@@ -8942,7 +8929,7 @@
         <v>DIP</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>23</v>
@@ -8963,7 +8950,7 @@
         <v>8</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L54" s="1" t="s">
         <v>181</v>
@@ -8982,13 +8969,11 @@
         <v>64</v>
       </c>
       <c r="Q54" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R54" s="1"/>
       <c r="S54" s="1"/>
-      <c r="T54" s="1" t="s">
-        <v>354</v>
-      </c>
+      <c r="T54" s="1"/>
       <c r="U54" s="1" t="str">
         <f t="shared" si="3"/>
         <v>d-dip-mqap01-nic</v>
@@ -9015,7 +9000,7 @@
         <v>49</v>
       </c>
       <c r="AC54" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD54" s="1">
         <v>1</v>
@@ -9033,13 +9018,13 @@
         <v>DIP</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>306</v>
@@ -9054,7 +9039,7 @@
         <v>8</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L55" s="9" t="s">
         <v>181</v>
@@ -9063,7 +9048,7 @@
         <v>191</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="O55" s="1" t="str">
         <f t="shared" si="2"/>
@@ -9073,7 +9058,7 @@
         <v>64</v>
       </c>
       <c r="Q55" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R55" s="1"/>
       <c r="S55" s="1"/>
@@ -9104,7 +9089,7 @@
         <v>49</v>
       </c>
       <c r="AC55" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD55" s="1">
         <v>1</v>
@@ -9122,13 +9107,13 @@
         <v>DIP</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>308</v>
@@ -9143,7 +9128,7 @@
         <v>8</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L56" s="1" t="s">
         <v>181</v>
@@ -9152,7 +9137,7 @@
         <v>191</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="O56" s="1" t="str">
         <f t="shared" si="2"/>
@@ -9162,12 +9147,9 @@
         <v>64</v>
       </c>
       <c r="Q56" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="R56" s="1" cm="1">
-        <f t="array" aca="1" ref="R56" ca="1">+R55:TP56</f>
-        <v>0</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="R56" s="1"/>
       <c r="S56" s="1"/>
       <c r="T56" s="1"/>
       <c r="U56" s="1" t="str">
@@ -9196,7 +9178,7 @@
         <v>49</v>
       </c>
       <c r="AC56" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD56" s="1">
         <v>1</v>
@@ -9214,16 +9196,16 @@
         <v>DIP</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>310</v>
+        <v>432</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>197</v>
@@ -9235,7 +9217,7 @@
         <v>8</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L57" s="9" t="s">
         <v>181</v>
@@ -9244,7 +9226,7 @@
         <v>191</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="O57" s="1" t="str">
         <f t="shared" si="2"/>
@@ -9254,7 +9236,7 @@
         <v>64</v>
       </c>
       <c r="Q57" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R57" s="1"/>
       <c r="S57" s="1"/>
@@ -9285,7 +9267,7 @@
         <v>49</v>
       </c>
       <c r="AC57" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD57" s="1">
         <v>1</v>
@@ -9300,19 +9282,19 @@
       </c>
       <c r="C58" s="1" t="str" cm="1">
         <f t="array" ref="C58">UPPER(INDEX(_xlfn.TEXTSPLIT($D58, "-"), 3))</f>
-        <v>COM</v>
+        <v>IF</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>311</v>
+        <v>55</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>399</v>
+        <v>430</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>313</v>
+        <v>434</v>
       </c>
       <c r="H58" s="10" t="s">
         <v>197</v>
@@ -9324,7 +9306,7 @@
         <v>8</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L58" s="1" t="s">
         <v>181</v>
@@ -9333,24 +9315,24 @@
         <v>191</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="O58" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>d-com-auth01-osdisk</v>
+        <v>d-if-auth01-osdisk</v>
       </c>
       <c r="P58" s="1">
         <v>64</v>
       </c>
       <c r="Q58" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R58" s="1"/>
       <c r="S58" s="1"/>
       <c r="T58" s="1"/>
       <c r="U58" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v>d-com-auth01-nic</v>
+        <f>SUBSTITUTE(F58,"hazr-","")&amp;"-nic"</f>
+        <v>d-if-auth01-nic</v>
       </c>
       <c r="V58" s="1" t="b">
         <v>1</v>
@@ -9365,7 +9347,7 @@
         <v>188</v>
       </c>
       <c r="Z58" s="1" t="s">
-        <v>314</v>
+        <v>166</v>
       </c>
       <c r="AA58" s="1" t="b">
         <v>1</v>
@@ -9374,7 +9356,7 @@
         <v>49</v>
       </c>
       <c r="AC58" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD58" s="1">
         <v>1</v>
@@ -9389,19 +9371,19 @@
       </c>
       <c r="C59" s="1" t="str" cm="1">
         <f t="array" ref="C59">UPPER(INDEX(_xlfn.TEXTSPLIT($D59, "-"), 3))</f>
-        <v>COM</v>
+        <v>IF</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>311</v>
+        <v>55</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>316</v>
+        <v>431</v>
+      </c>
+      <c r="G59" s="39" t="s">
+        <v>433</v>
       </c>
       <c r="H59" s="10" t="s">
         <v>197</v>
@@ -9413,7 +9395,7 @@
         <v>8</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L59" s="9" t="s">
         <v>181</v>
@@ -9422,24 +9404,24 @@
         <v>191</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="O59" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>d-com-proxy01-osdisk</v>
+        <v>d-if-proxy01-osdisk</v>
       </c>
       <c r="P59" s="1">
         <v>64</v>
       </c>
       <c r="Q59" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R59" s="1"/>
       <c r="S59" s="1"/>
       <c r="T59" s="1"/>
       <c r="U59" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>d-com-proxy01-nic</v>
+        <v>d-if-proxy01-nic</v>
       </c>
       <c r="V59" s="1" t="b">
         <v>1</v>
@@ -9454,7 +9436,7 @@
         <v>199</v>
       </c>
       <c r="Z59" s="1" t="s">
-        <v>317</v>
+        <v>84</v>
       </c>
       <c r="AA59" s="1" t="b">
         <v>1</v>
@@ -9463,7 +9445,7 @@
         <v>49</v>
       </c>
       <c r="AC59" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD59" s="1">
         <v>1</v>
@@ -9481,16 +9463,16 @@
         <v>IF</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>197</v>
@@ -9502,7 +9484,7 @@
         <v>8</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L60" s="1" t="s">
         <v>181</v>
@@ -9521,7 +9503,7 @@
         <v>64</v>
       </c>
       <c r="Q60" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R60" s="1"/>
       <c r="S60" s="1"/>
@@ -9543,7 +9525,7 @@
         <v>188</v>
       </c>
       <c r="Z60" s="1" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="AA60" s="1" t="b">
         <v>1</v>
@@ -9552,7 +9534,7 @@
         <v>49</v>
       </c>
       <c r="AC60" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD60" s="1">
         <v>1</v>
@@ -9570,16 +9552,16 @@
         <v>DOIP</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="H61" s="10" t="s">
         <v>197</v>
@@ -9591,7 +9573,7 @@
         <v>8</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L61" s="1" t="s">
         <v>181</v>
@@ -9610,7 +9592,7 @@
         <v>64</v>
       </c>
       <c r="Q61" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R61" s="1"/>
       <c r="S61" s="1"/>
@@ -9632,7 +9614,7 @@
         <v>188</v>
       </c>
       <c r="Z61" s="1" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="AA61" s="1" t="b">
         <v>1</v>
@@ -9641,7 +9623,7 @@
         <v>49</v>
       </c>
       <c r="AC61" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD61" s="1">
         <v>1</v>
@@ -9659,16 +9641,16 @@
         <v>DOIP</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="H62" s="10" t="s">
         <v>197</v>
@@ -9680,7 +9662,7 @@
         <v>8</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L62" s="9" t="s">
         <v>181</v>
@@ -9699,7 +9681,7 @@
         <v>64</v>
       </c>
       <c r="Q62" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R62" s="1"/>
       <c r="S62" s="1"/>
@@ -9721,7 +9703,7 @@
         <v>188</v>
       </c>
       <c r="Z62" s="1" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="AA62" s="1" t="b">
         <v>1</v>
@@ -9730,7 +9712,7 @@
         <v>49</v>
       </c>
       <c r="AC62" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD62" s="1">
         <v>1</v>
@@ -9748,16 +9730,16 @@
         <v>DOIP</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="H63" s="1" t="s">
         <v>197</v>
@@ -9769,7 +9751,7 @@
         <v>8</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L63" s="1" t="s">
         <v>181</v>
@@ -9788,7 +9770,7 @@
         <v>64</v>
       </c>
       <c r="Q63" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R63" s="1"/>
       <c r="S63" s="1"/>
@@ -9810,7 +9792,7 @@
         <v>188</v>
       </c>
       <c r="Z63" s="1" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="AA63" s="1" t="b">
         <v>1</v>
@@ -9819,7 +9801,7 @@
         <v>49</v>
       </c>
       <c r="AC63" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD63" s="1">
         <v>1</v>
@@ -9843,10 +9825,10 @@
         <v>23</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="H64" s="10" t="s">
         <v>197</v>
@@ -9858,7 +9840,7 @@
         <v>8</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L64" s="9" t="s">
         <v>181</v>
@@ -9867,7 +9849,7 @@
         <v>191</v>
       </c>
       <c r="N64" s="1" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="O64" s="1" t="str">
         <f t="shared" si="4"/>
@@ -9877,7 +9859,7 @@
         <v>64</v>
       </c>
       <c r="Q64" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R64" s="1"/>
       <c r="S64" s="1"/>
@@ -9899,7 +9881,7 @@
         <v>199</v>
       </c>
       <c r="Z64" s="1" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="AA64" s="1" t="b">
         <v>1</v>
@@ -9908,7 +9890,7 @@
         <v>49</v>
       </c>
       <c r="AC64" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD64" s="1">
         <v>1</v>
@@ -9932,10 +9914,10 @@
         <v>23</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="H65" s="10" t="s">
         <v>197</v>
@@ -9947,7 +9929,7 @@
         <v>8</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L65" s="1" t="s">
         <v>181</v>
@@ -9966,7 +9948,7 @@
         <v>64</v>
       </c>
       <c r="Q65" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R65" s="1"/>
       <c r="S65" s="1"/>
@@ -9997,7 +9979,7 @@
         <v>49</v>
       </c>
       <c r="AC65" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD65" s="1">
         <v>1</v>
@@ -10021,10 +10003,10 @@
         <v>23</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="H66" s="1" t="s">
         <v>197</v>
@@ -10036,7 +10018,7 @@
         <v>8</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L66" s="9" t="s">
         <v>181</v>
@@ -10055,7 +10037,7 @@
         <v>64</v>
       </c>
       <c r="Q66" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R66" s="1"/>
       <c r="S66" s="1"/>
@@ -10086,7 +10068,7 @@
         <v>49</v>
       </c>
       <c r="AC66" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD66" s="1">
         <v>1</v>
@@ -10110,10 +10092,10 @@
         <v>23</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="H67" s="10" t="s">
         <v>197</v>
@@ -10125,7 +10107,7 @@
         <v>8</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L67" s="1" t="s">
         <v>181</v>
@@ -10134,7 +10116,7 @@
         <v>183</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="O67" s="1" t="str">
         <f t="shared" si="4"/>
@@ -10144,7 +10126,7 @@
         <v>128</v>
       </c>
       <c r="Q67" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R67" s="1"/>
       <c r="S67" s="1"/>
@@ -10175,7 +10157,7 @@
         <v>49</v>
       </c>
       <c r="AC67" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="AD67" s="1">
         <v>1</v>
@@ -10230,40 +10212,40 @@
         <v>3</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="H1" s="15" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="I1" s="15" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="J1" s="15" t="s">
+        <v>350</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>353</v>
+      </c>
+      <c r="L1" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="M1" s="15" t="s">
+        <v>348</v>
+      </c>
+      <c r="N1" s="15" t="s">
+        <v>357</v>
+      </c>
+      <c r="O1" s="15" t="s">
         <v>359</v>
-      </c>
-      <c r="K1" s="15" t="s">
-        <v>362</v>
-      </c>
-      <c r="L1" s="15" t="s">
-        <v>363</v>
-      </c>
-      <c r="M1" s="15" t="s">
-        <v>357</v>
-      </c>
-      <c r="N1" s="15" t="s">
-        <v>366</v>
-      </c>
-      <c r="O1" s="15" t="s">
-        <v>368</v>
       </c>
       <c r="P1" s="15" t="s">
         <v>48</v>
       </c>
       <c r="Q1" s="15" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="R1" s="7" t="s">
         <v>30</v>
@@ -10292,7 +10274,7 @@
         <v>d-dis-ap01-disk01</v>
       </c>
       <c r="H2" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I2" s="16">
         <v>64</v>
@@ -10302,7 +10284,7 @@
         <v>d-dis-ap01-disk02</v>
       </c>
       <c r="K2" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L2" s="16">
         <v>64</v>
@@ -10311,13 +10293,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="16" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O2" s="16" t="s">
         <v>49</v>
       </c>
       <c r="P2" s="16" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q2" s="16" t="b">
         <v>1</v>
@@ -10347,7 +10329,7 @@
         <v>d-dis-adm01-disk01</v>
       </c>
       <c r="H3" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I3" s="17">
         <v>64</v>
@@ -10357,7 +10339,7 @@
         <v>d-dis-adm01-disk02</v>
       </c>
       <c r="K3" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L3" s="17">
         <v>64</v>
@@ -10366,13 +10348,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="17" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O3" s="17" t="s">
         <v>49</v>
       </c>
       <c r="P3" s="17" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q3" s="17" t="b">
         <v>1</v>
@@ -10402,7 +10384,7 @@
         <v>d-dis-bbiweb01-disk01</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I4" s="16">
         <v>64</v>
@@ -10412,7 +10394,7 @@
         <v>d-dis-bbiweb01-disk02</v>
       </c>
       <c r="K4" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L4" s="16">
         <v>64</v>
@@ -10421,13 +10403,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="16" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O4" s="16" t="s">
         <v>49</v>
       </c>
       <c r="P4" s="16" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q4" s="16" t="b">
         <v>1</v>
@@ -10457,7 +10439,7 @@
         <v>d-dis-bbicltap01-disk01</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I5" s="17">
         <v>64</v>
@@ -10467,7 +10449,7 @@
         <v>d-dis-bbicltap01-disk02</v>
       </c>
       <c r="K5" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L5" s="17">
         <v>64</v>
@@ -10476,13 +10458,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="17" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O5" s="17" t="s">
         <v>49</v>
       </c>
       <c r="P5" s="17" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q5" s="17" t="b">
         <v>1</v>
@@ -10512,7 +10494,7 @@
         <v>d-dis-bbimsgap01-disk01</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I6" s="16">
         <v>64</v>
@@ -10522,7 +10504,7 @@
         <v>d-dis-bbimsgap01-disk02</v>
       </c>
       <c r="K6" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L6" s="16">
         <v>64</v>
@@ -10531,13 +10513,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="16" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O6" s="16" t="s">
         <v>49</v>
       </c>
       <c r="P6" s="16" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q6" s="16" t="b">
         <v>1</v>
@@ -10567,7 +10549,7 @@
         <v>d-dis-walkap01-disk01</v>
       </c>
       <c r="H7" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I7" s="17">
         <v>64</v>
@@ -10577,7 +10559,7 @@
         <v>d-dis-walkap01-disk02</v>
       </c>
       <c r="K7" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L7" s="17">
         <v>64</v>
@@ -10586,13 +10568,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="17" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O7" s="17" t="s">
         <v>49</v>
       </c>
       <c r="P7" s="17" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q7" s="17" t="b">
         <v>1</v>
@@ -10622,7 +10604,7 @@
         <v>d-dis-bat01-disk01</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I8" s="16">
         <v>64</v>
@@ -10632,7 +10614,7 @@
         <v>d-dis-bat01-disk02</v>
       </c>
       <c r="K8" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L8" s="16">
         <v>64</v>
@@ -10641,13 +10623,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="16" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O8" s="16" t="s">
         <v>49</v>
       </c>
       <c r="P8" s="16" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q8" s="16" t="b">
         <v>1</v>
@@ -10677,7 +10659,7 @@
         <v>d-dis-drvcltap01-disk01</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I9" s="16">
         <v>64</v>
@@ -10687,7 +10669,7 @@
         <v>d-dis-drvcltap01-disk02</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L9" s="16">
         <v>64</v>
@@ -10696,13 +10678,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="16" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O9" s="16" t="s">
         <v>49</v>
       </c>
       <c r="P9" s="16" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q9" s="16" t="b">
         <v>1</v>
@@ -10732,7 +10714,7 @@
         <v>d-dis-walkweb01-disk01</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I10" s="17">
         <v>64</v>
@@ -10742,7 +10724,7 @@
         <v>d-dis-walkweb01-disk02</v>
       </c>
       <c r="K10" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L10" s="17">
         <v>64</v>
@@ -10751,13 +10733,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O10" s="17" t="s">
         <v>49</v>
       </c>
       <c r="P10" s="17" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q10" s="17" t="b">
         <v>1</v>
@@ -10787,7 +10769,7 @@
         <v>d-dis-drvmsgap01-disk01</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I11" s="16">
         <v>64</v>
@@ -10797,7 +10779,7 @@
         <v>d-dis-drvmsgap01-disk02</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L11" s="16">
         <v>64</v>
@@ -10806,13 +10788,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="16" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O11" s="16" t="s">
         <v>49</v>
       </c>
       <c r="P11" s="16" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q11" s="16" t="b">
         <v>1</v>
@@ -10842,7 +10824,7 @@
         <v>d-dis-web01-disk01</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I12" s="17">
         <v>64</v>
@@ -10852,7 +10834,7 @@
         <v>d-dis-web01-disk02</v>
       </c>
       <c r="K12" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L12" s="17">
         <v>64</v>
@@ -10861,13 +10843,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O12" s="17" t="s">
         <v>49</v>
       </c>
       <c r="P12" s="17" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q12" s="17" t="b">
         <v>1</v>
@@ -10897,7 +10879,7 @@
         <v>d-dis-cmsadm01-disk01</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I13" s="16">
         <v>64</v>
@@ -10907,7 +10889,7 @@
         <v>d-dis-cmsadm01-disk02</v>
       </c>
       <c r="K13" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L13" s="16">
         <v>64</v>
@@ -10916,13 +10898,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="16" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O13" s="16" t="s">
         <v>49</v>
       </c>
       <c r="P13" s="16" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q13" s="16" t="b">
         <v>1</v>
@@ -10952,7 +10934,7 @@
         <v>d-dis-cmsap01-disk01</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I14" s="17">
         <v>64</v>
@@ -10962,7 +10944,7 @@
         <v>d-dis-cmsap01-disk02</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L14" s="17">
         <v>64</v>
@@ -10971,13 +10953,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O14" s="17" t="s">
         <v>49</v>
       </c>
       <c r="P14" s="17" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q14" s="17" t="b">
         <v>1</v>
@@ -11007,7 +10989,7 @@
         <v>d-dis-cmsweb01-disk01</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I15" s="16">
         <v>64</v>
@@ -11017,7 +10999,7 @@
         <v>d-dis-cmsweb01-disk02</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L15" s="16">
         <v>64</v>
@@ -11026,13 +11008,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="16" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O15" s="16" t="s">
         <v>49</v>
       </c>
       <c r="P15" s="16" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q15" s="16" t="b">
         <v>1</v>
@@ -11062,7 +11044,7 @@
         <v>d-dis-cmbsap01-disk01</v>
       </c>
       <c r="H16" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I16" s="17">
         <v>64</v>
@@ -11072,7 +11054,7 @@
         <v>d-dis-cmbsap01-disk02</v>
       </c>
       <c r="K16" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L16" s="17">
         <v>64</v>
@@ -11081,13 +11063,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O16" s="17" t="s">
         <v>49</v>
       </c>
       <c r="P16" s="17" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q16" s="17" t="b">
         <v>1</v>
@@ -11117,7 +11099,7 @@
         <v>d-dtg-ingap01-disk01</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I17" s="16">
         <v>64</v>
@@ -11127,7 +11109,7 @@
         <v>d-dtg-ingap01-disk02</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L17" s="16">
         <v>64</v>
@@ -11136,13 +11118,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="16" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O17" s="16" t="s">
         <v>49</v>
       </c>
       <c r="P17" s="16" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q17" s="16" t="b">
         <v>1</v>
@@ -11172,7 +11154,7 @@
         <v>d-dtg-ap01-disk01</v>
       </c>
       <c r="H18" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I18" s="17">
         <v>64</v>
@@ -11182,7 +11164,7 @@
         <v>d-dtg-ap01-disk02</v>
       </c>
       <c r="K18" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L18" s="17">
         <v>64</v>
@@ -11191,13 +11173,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O18" s="17" t="s">
         <v>49</v>
       </c>
       <c r="P18" s="17" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q18" s="17" t="b">
         <v>1</v>
@@ -11227,7 +11209,7 @@
         <v>d-dtg-extgeoap01-disk01</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I19" s="16">
         <v>64</v>
@@ -11237,7 +11219,7 @@
         <v>d-dtg-extgeoap01-disk02</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L19" s="16">
         <v>64</v>
@@ -11246,13 +11228,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="16" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O19" s="16" t="s">
         <v>49</v>
       </c>
       <c r="P19" s="16" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q19" s="16" t="b">
         <v>1</v>
@@ -11282,7 +11264,7 @@
         <v>d-dtg-geoap01-disk01</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I20" s="17">
         <v>64</v>
@@ -11292,7 +11274,7 @@
         <v>d-dtg-geoap01-disk02</v>
       </c>
       <c r="K20" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L20" s="17">
         <v>64</v>
@@ -11301,13 +11283,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O20" s="17" t="s">
         <v>49</v>
       </c>
       <c r="P20" s="17" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q20" s="17" t="b">
         <v>1</v>
@@ -11337,7 +11319,7 @@
         <v>d-dtg-mq01-disk01</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I21" s="16">
         <v>64</v>
@@ -11347,7 +11329,7 @@
         <v>d-dtg-mq01-disk02</v>
       </c>
       <c r="K21" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L21" s="16">
         <v>64</v>
@@ -11356,13 +11338,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="16" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O21" s="16" t="s">
         <v>49</v>
       </c>
       <c r="P21" s="16" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q21" s="16" t="b">
         <v>1</v>
@@ -11392,7 +11374,7 @@
         <v>d-dtg-admweb01-disk01</v>
       </c>
       <c r="H22" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I22" s="17">
         <v>64</v>
@@ -11402,7 +11384,7 @@
         <v>d-dtg-admweb01-disk02</v>
       </c>
       <c r="K22" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L22" s="17">
         <v>64</v>
@@ -11411,13 +11393,13 @@
         <v>1</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O22" s="17" t="s">
         <v>49</v>
       </c>
       <c r="P22" s="17" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q22" s="17" t="b">
         <v>1</v>
@@ -11447,7 +11429,7 @@
         <v>d-dtg-admap01-disk01</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I23" s="16">
         <v>64</v>
@@ -11457,7 +11439,7 @@
         <v>d-dtg-admap01-disk02</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L23" s="16">
         <v>64</v>
@@ -11466,13 +11448,13 @@
         <v>1</v>
       </c>
       <c r="N23" s="16" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O23" s="16" t="s">
         <v>49</v>
       </c>
       <c r="P23" s="16" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q23" s="16" t="b">
         <v>1</v>
@@ -11502,7 +11484,7 @@
         <v>d-dtg-dtoms01-disk01</v>
       </c>
       <c r="H24" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I24" s="17">
         <v>64</v>
@@ -11512,7 +11494,7 @@
         <v>d-dtg-dtoms01-disk02</v>
       </c>
       <c r="K24" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L24" s="17">
         <v>64</v>
@@ -11521,13 +11503,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O24" s="17" t="s">
         <v>49</v>
       </c>
       <c r="P24" s="17" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q24" s="17" t="b">
         <v>1</v>
@@ -11557,7 +11539,7 @@
         <v>d-dtg-tsdb01-disk01</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I25" s="16">
         <v>256</v>
@@ -11567,7 +11549,7 @@
         <v>d-dtg-tsdb01-disk02</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L25" s="16">
         <v>256</v>
@@ -11576,13 +11558,13 @@
         <v>1</v>
       </c>
       <c r="N25" s="16" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O25" s="16" t="s">
         <v>49</v>
       </c>
       <c r="P25" s="16" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q25" s="16" t="b">
         <v>1</v>
@@ -11612,7 +11594,7 @@
         <v>d-dtg-web01-disk01</v>
       </c>
       <c r="H26" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I26" s="17">
         <v>64</v>
@@ -11622,7 +11604,7 @@
         <v>d-dtg-web01-disk02</v>
       </c>
       <c r="K26" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L26" s="17">
         <v>64</v>
@@ -11631,13 +11613,13 @@
         <v>1</v>
       </c>
       <c r="N26" s="17" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O26" s="17" t="s">
         <v>49</v>
       </c>
       <c r="P26" s="17" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q26" s="17" t="b">
         <v>1</v>
@@ -11667,7 +11649,7 @@
         <v>d-dtg-zkp01-disk01</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I27" s="16">
         <v>64</v>
@@ -11677,7 +11659,7 @@
         <v>d-dtg-zkp01-disk02</v>
       </c>
       <c r="K27" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L27" s="16">
         <v>64</v>
@@ -11686,13 +11668,13 @@
         <v>1</v>
       </c>
       <c r="N27" s="16" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O27" s="16" t="s">
         <v>49</v>
       </c>
       <c r="P27" s="16" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q27" s="16" t="b">
         <v>1</v>
@@ -11722,7 +11704,7 @@
         <v>d-dtg-zkp02-disk01</v>
       </c>
       <c r="H28" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I28" s="17">
         <v>64</v>
@@ -11732,7 +11714,7 @@
         <v>d-dtg-zkp02-disk02</v>
       </c>
       <c r="K28" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L28" s="17">
         <v>64</v>
@@ -11741,13 +11723,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="17" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O28" s="17" t="s">
         <v>49</v>
       </c>
       <c r="P28" s="17" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q28" s="17" t="b">
         <v>1</v>
@@ -11777,7 +11759,7 @@
         <v>d-dtg-zkp03-disk01</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I29" s="16">
         <v>64</v>
@@ -11787,7 +11769,7 @@
         <v>d-dtg-zkp03-disk02</v>
       </c>
       <c r="K29" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L29" s="16">
         <v>64</v>
@@ -11796,13 +11778,13 @@
         <v>1</v>
       </c>
       <c r="N29" s="16" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O29" s="16" t="s">
         <v>49</v>
       </c>
       <c r="P29" s="16" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q29" s="16" t="b">
         <v>1</v>
@@ -11832,7 +11814,7 @@
         <v>d-dtg-kfk01-disk01</v>
       </c>
       <c r="H30" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I30" s="17">
         <v>64</v>
@@ -11842,7 +11824,7 @@
         <v>d-dtg-kfk01-disk02</v>
       </c>
       <c r="K30" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L30" s="17">
         <v>64</v>
@@ -11851,13 +11833,13 @@
         <v>1</v>
       </c>
       <c r="N30" s="17" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O30" s="17" t="s">
         <v>49</v>
       </c>
       <c r="P30" s="17" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q30" s="17" t="b">
         <v>1</v>
@@ -11887,7 +11869,7 @@
         <v>d-dtg-kfk02-disk01</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I31" s="16">
         <v>64</v>
@@ -11897,7 +11879,7 @@
         <v>d-dtg-kfk02-disk02</v>
       </c>
       <c r="K31" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L31" s="16">
         <v>64</v>
@@ -11906,13 +11888,13 @@
         <v>1</v>
       </c>
       <c r="N31" s="16" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O31" s="16" t="s">
         <v>49</v>
       </c>
       <c r="P31" s="16" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q31" s="16" t="b">
         <v>1</v>
@@ -11942,7 +11924,7 @@
         <v>d-dtg-kfk03-disk01</v>
       </c>
       <c r="H32" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I32" s="17">
         <v>64</v>
@@ -11952,7 +11934,7 @@
         <v>d-dtg-kfk03-disk02</v>
       </c>
       <c r="K32" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L32" s="17">
         <v>64</v>
@@ -11961,13 +11943,13 @@
         <v>1</v>
       </c>
       <c r="N32" s="17" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O32" s="17" t="s">
         <v>49</v>
       </c>
       <c r="P32" s="17" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q32" s="17" t="b">
         <v>1</v>
@@ -11997,7 +11979,7 @@
         <v>d-dtg-mdoms01-disk01</v>
       </c>
       <c r="H33" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I33" s="16">
         <v>64</v>
@@ -12007,7 +11989,7 @@
         <v>d-dtg-mdoms01-disk02</v>
       </c>
       <c r="K33" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L33" s="16">
         <v>64</v>
@@ -12016,13 +11998,13 @@
         <v>1</v>
       </c>
       <c r="N33" s="16" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O33" s="16" t="s">
         <v>49</v>
       </c>
       <c r="P33" s="16" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q33" s="16" t="b">
         <v>1</v>
@@ -12052,7 +12034,7 @@
         <v>d-dtg-cdmlap01-disk01</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I34" s="17">
         <v>64</v>
@@ -12062,7 +12044,7 @@
         <v>d-dtg-cdmlap01-disk02</v>
       </c>
       <c r="K34" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L34" s="17">
         <v>64</v>
@@ -12071,13 +12053,13 @@
         <v>1</v>
       </c>
       <c r="N34" s="17" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O34" s="17" t="s">
         <v>49</v>
       </c>
       <c r="P34" s="17" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q34" s="17" t="b">
         <v>1</v>
@@ -12107,7 +12089,7 @@
         <v>d-dtg-cdstap01-disk01</v>
       </c>
       <c r="H35" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I35" s="16">
         <v>64</v>
@@ -12117,7 +12099,7 @@
         <v>d-dtg-cdstap01-disk02</v>
       </c>
       <c r="K35" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L35" s="16">
         <v>64</v>
@@ -12126,13 +12108,13 @@
         <v>1</v>
       </c>
       <c r="N35" s="16" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O35" s="16" t="s">
         <v>49</v>
       </c>
       <c r="P35" s="16" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q35" s="16" t="b">
         <v>1</v>
@@ -12155,14 +12137,14 @@
         <v>23</v>
       </c>
       <c r="F36" s="17" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="G36" s="17" t="str">
         <f t="shared" si="0"/>
         <v>d-dtg-cdsvadm01-disk01</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I36" s="17">
         <v>64</v>
@@ -12172,7 +12154,7 @@
         <v>d-dtg-cdsvadm01-disk02</v>
       </c>
       <c r="K36" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L36" s="17">
         <v>64</v>
@@ -12181,13 +12163,13 @@
         <v>1</v>
       </c>
       <c r="N36" s="17" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O36" s="17" t="s">
         <v>49</v>
       </c>
       <c r="P36" s="17" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q36" s="17" t="b">
         <v>1</v>
@@ -12217,7 +12199,7 @@
         <v>d-dtg-diosap01-disk01</v>
       </c>
       <c r="H37" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I37" s="16">
         <v>64</v>
@@ -12227,7 +12209,7 @@
         <v>d-dtg-diosap01-disk02</v>
       </c>
       <c r="K37" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L37" s="16">
         <v>64</v>
@@ -12236,13 +12218,13 @@
         <v>1</v>
       </c>
       <c r="N37" s="16" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O37" s="16" t="s">
         <v>49</v>
       </c>
       <c r="P37" s="16" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q37" s="16" t="b">
         <v>1</v>
@@ -12272,7 +12254,7 @@
         <v>d-dtg-diosweb01-disk01</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I38" s="17">
         <v>64</v>
@@ -12282,7 +12264,7 @@
         <v>d-dtg-diosweb01-disk02</v>
       </c>
       <c r="K38" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L38" s="17">
         <v>64</v>
@@ -12291,13 +12273,13 @@
         <v>1</v>
       </c>
       <c r="N38" s="17" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O38" s="17" t="s">
         <v>49</v>
       </c>
       <c r="P38" s="17" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q38" s="17" t="b">
         <v>1</v>
@@ -12327,7 +12309,7 @@
         <v>d-dtg-dprweb01-disk01</v>
       </c>
       <c r="H39" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I39" s="16">
         <v>64</v>
@@ -12337,7 +12319,7 @@
         <v>d-dtg-dprweb01-disk02</v>
       </c>
       <c r="K39" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L39" s="16">
         <v>64</v>
@@ -12346,13 +12328,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="16" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O39" s="16" t="s">
         <v>49</v>
       </c>
       <c r="P39" s="16" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q39" s="16" t="b">
         <v>1</v>
@@ -12382,7 +12364,7 @@
         <v>d-dtg-dprap01-disk01</v>
       </c>
       <c r="H40" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I40" s="17">
         <v>64</v>
@@ -12392,7 +12374,7 @@
         <v>d-dtg-dprap01-disk02</v>
       </c>
       <c r="K40" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L40" s="17">
         <v>64</v>
@@ -12401,13 +12383,13 @@
         <v>1</v>
       </c>
       <c r="N40" s="17" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O40" s="17" t="s">
         <v>49</v>
       </c>
       <c r="P40" s="17" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q40" s="17" t="b">
         <v>1</v>
@@ -12437,7 +12419,7 @@
         <v>d-bdp-airfw01-disk01</v>
       </c>
       <c r="H41" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I41" s="16">
         <v>64</v>
@@ -12447,7 +12429,7 @@
         <v>d-bdp-airfw01-disk02</v>
       </c>
       <c r="K41" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L41" s="16">
         <v>64</v>
@@ -12456,13 +12438,13 @@
         <v>1</v>
       </c>
       <c r="N41" s="16" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O41" s="16" t="s">
         <v>49</v>
       </c>
       <c r="P41" s="16" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q41" s="16" t="b">
         <v>1</v>
@@ -12492,7 +12474,7 @@
         <v>d-bdp-kepler01-disk01</v>
       </c>
       <c r="H42" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I42" s="17">
         <v>64</v>
@@ -12502,7 +12484,7 @@
         <v>d-bdp-kepler01-disk02</v>
       </c>
       <c r="K42" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L42" s="17">
         <v>64</v>
@@ -12511,13 +12493,13 @@
         <v>1</v>
       </c>
       <c r="N42" s="17" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O42" s="17" t="s">
         <v>49</v>
       </c>
       <c r="P42" s="17" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q42" s="17" t="b">
         <v>1</v>
@@ -12540,14 +12522,14 @@
         <v>23</v>
       </c>
       <c r="F43" s="16" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="G43" s="16" t="str">
         <f t="shared" si="0"/>
         <v>d-bdp-cxmadm01-disk01</v>
       </c>
       <c r="H43" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I43" s="16">
         <v>64</v>
@@ -12557,7 +12539,7 @@
         <v>d-bdp-cxmadm01-disk02</v>
       </c>
       <c r="K43" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L43" s="16">
         <v>64</v>
@@ -12566,13 +12548,13 @@
         <v>1</v>
       </c>
       <c r="N43" s="16" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O43" s="16" t="s">
         <v>49</v>
       </c>
       <c r="P43" s="16" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q43" s="16" t="b">
         <v>1</v>
@@ -12602,7 +12584,7 @@
         <v>d-bdp-slap01-disk01</v>
       </c>
       <c r="H44" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I44" s="17">
         <v>64</v>
@@ -12612,7 +12594,7 @@
         <v>d-bdp-slap01-disk02</v>
       </c>
       <c r="K44" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L44" s="17">
         <v>64</v>
@@ -12621,13 +12603,13 @@
         <v>1</v>
       </c>
       <c r="N44" s="17" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O44" s="17" t="s">
         <v>49</v>
       </c>
       <c r="P44" s="17" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q44" s="17" t="b">
         <v>1</v>
@@ -12644,7 +12626,7 @@
         <v>DIP</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E45" s="22" t="s">
         <v>23</v>
@@ -12657,7 +12639,7 @@
         <v>d-dip-adm01-disk01</v>
       </c>
       <c r="H45" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I45" s="16">
         <v>64</v>
@@ -12667,7 +12649,7 @@
         <v>d-dip-adm01-disk02</v>
       </c>
       <c r="K45" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L45" s="16">
         <v>64</v>
@@ -12676,13 +12658,13 @@
         <v>1</v>
       </c>
       <c r="N45" s="16" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O45" s="16" t="s">
         <v>49</v>
       </c>
       <c r="P45" s="16" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q45" s="16" t="b">
         <v>1</v>
@@ -12699,7 +12681,7 @@
         <v>DIP</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E46" s="24" t="s">
         <v>23</v>
@@ -12712,7 +12694,7 @@
         <v>d-dip-ap01-disk01</v>
       </c>
       <c r="H46" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I46" s="17">
         <v>64</v>
@@ -12722,7 +12704,7 @@
         <v>d-dip-ap01-disk02</v>
       </c>
       <c r="K46" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L46" s="17">
         <v>64</v>
@@ -12731,13 +12713,13 @@
         <v>1</v>
       </c>
       <c r="N46" s="17" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O46" s="17" t="s">
         <v>49</v>
       </c>
       <c r="P46" s="17" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q46" s="17" t="b">
         <v>1</v>
@@ -12754,7 +12736,7 @@
         <v>DIP</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E47" s="22" t="s">
         <v>23</v>
@@ -12767,7 +12749,7 @@
         <v>d-dip-flk01-disk01</v>
       </c>
       <c r="H47" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I47" s="16">
         <v>64</v>
@@ -12777,7 +12759,7 @@
         <v>d-dip-flk01-disk02</v>
       </c>
       <c r="K47" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L47" s="16">
         <v>64</v>
@@ -12786,13 +12768,13 @@
         <v>1</v>
       </c>
       <c r="N47" s="16" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O47" s="16" t="s">
         <v>49</v>
       </c>
       <c r="P47" s="16" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q47" s="16" t="b">
         <v>1</v>
@@ -12809,7 +12791,7 @@
         <v>DIP</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E48" s="24" t="s">
         <v>23</v>
@@ -12822,7 +12804,7 @@
         <v>d-dip-flk02-disk01</v>
       </c>
       <c r="H48" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I48" s="17">
         <v>64</v>
@@ -12832,7 +12814,7 @@
         <v>d-dip-flk02-disk02</v>
       </c>
       <c r="K48" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L48" s="17">
         <v>64</v>
@@ -12841,13 +12823,13 @@
         <v>1</v>
       </c>
       <c r="N48" s="17" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O48" s="17" t="s">
         <v>49</v>
       </c>
       <c r="P48" s="17" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q48" s="17" t="b">
         <v>1</v>
@@ -12864,7 +12846,7 @@
         <v>DIP</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E49" s="22" t="s">
         <v>23</v>
@@ -12877,7 +12859,7 @@
         <v>d-dip-flk03-disk01</v>
       </c>
       <c r="H49" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I49" s="16">
         <v>64</v>
@@ -12887,7 +12869,7 @@
         <v>d-dip-flk03-disk02</v>
       </c>
       <c r="K49" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L49" s="16">
         <v>64</v>
@@ -12896,13 +12878,13 @@
         <v>1</v>
       </c>
       <c r="N49" s="16" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O49" s="16" t="s">
         <v>49</v>
       </c>
       <c r="P49" s="16" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q49" s="16" t="b">
         <v>1</v>
@@ -12919,7 +12901,7 @@
         <v>DIP</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E50" s="24" t="s">
         <v>23</v>
@@ -12932,7 +12914,7 @@
         <v>d-dip-geoap01-disk01</v>
       </c>
       <c r="H50" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I50" s="17">
         <v>64</v>
@@ -12942,7 +12924,7 @@
         <v>d-dip-geoap01-disk02</v>
       </c>
       <c r="K50" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L50" s="17">
         <v>64</v>
@@ -12951,13 +12933,13 @@
         <v>1</v>
       </c>
       <c r="N50" s="17" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O50" s="17" t="s">
         <v>49</v>
       </c>
       <c r="P50" s="17" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q50" s="17" t="b">
         <v>1</v>
@@ -12974,7 +12956,7 @@
         <v>DIP</v>
       </c>
       <c r="D51" s="16" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E51" s="22" t="s">
         <v>23</v>
@@ -12987,7 +12969,7 @@
         <v>d-dip-kfk01-disk01</v>
       </c>
       <c r="H51" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I51" s="16">
         <v>64</v>
@@ -12997,7 +12979,7 @@
         <v>d-dip-kfk01-disk02</v>
       </c>
       <c r="K51" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L51" s="16">
         <v>64</v>
@@ -13006,13 +12988,13 @@
         <v>1</v>
       </c>
       <c r="N51" s="16" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O51" s="16" t="s">
         <v>49</v>
       </c>
       <c r="P51" s="16" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q51" s="16" t="b">
         <v>1</v>
@@ -13029,20 +13011,20 @@
         <v>DIP</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E52" s="24" t="s">
         <v>23</v>
       </c>
       <c r="F52" s="17" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="G52" s="17" t="str">
         <f t="shared" si="0"/>
         <v>d-dip-kfk02-disk01</v>
       </c>
       <c r="H52" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I52" s="17">
         <v>64</v>
@@ -13052,7 +13034,7 @@
         <v>d-dip-kfk02-disk02</v>
       </c>
       <c r="K52" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L52" s="17">
         <v>64</v>
@@ -13061,13 +13043,13 @@
         <v>1</v>
       </c>
       <c r="N52" s="17" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O52" s="17" t="s">
         <v>49</v>
       </c>
       <c r="P52" s="17" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q52" s="17" t="b">
         <v>1</v>
@@ -13084,20 +13066,20 @@
         <v>DIP</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E53" s="22" t="s">
         <v>23</v>
       </c>
       <c r="F53" s="16" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="G53" s="16" t="str">
         <f t="shared" si="0"/>
         <v>d-dip-kfk03-disk01</v>
       </c>
       <c r="H53" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I53" s="16">
         <v>64</v>
@@ -13107,7 +13089,7 @@
         <v>d-dip-kfk03-disk02</v>
       </c>
       <c r="K53" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L53" s="16">
         <v>64</v>
@@ -13116,13 +13098,13 @@
         <v>1</v>
       </c>
       <c r="N53" s="16" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O53" s="16" t="s">
         <v>49</v>
       </c>
       <c r="P53" s="16" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q53" s="16" t="b">
         <v>1</v>
@@ -13139,7 +13121,7 @@
         <v>DIP</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E54" s="24" t="s">
         <v>23</v>
@@ -13152,7 +13134,7 @@
         <v>d-dip-mqap01-disk01</v>
       </c>
       <c r="H54" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I54" s="17">
         <v>64</v>
@@ -13162,7 +13144,7 @@
         <v>d-dip-mqap01-disk02</v>
       </c>
       <c r="K54" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L54" s="17">
         <v>64</v>
@@ -13171,13 +13153,13 @@
         <v>1</v>
       </c>
       <c r="N54" s="17" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O54" s="17" t="s">
         <v>49</v>
       </c>
       <c r="P54" s="17" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q54" s="17" t="b">
         <v>1</v>
@@ -13194,7 +13176,7 @@
         <v>DIP</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E55" s="22" t="s">
         <v>23</v>
@@ -13207,7 +13189,7 @@
         <v>d-dip-mqweb01-disk01</v>
       </c>
       <c r="H55" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I55" s="16">
         <v>64</v>
@@ -13217,7 +13199,7 @@
         <v>d-dip-mqweb01-disk02</v>
       </c>
       <c r="K55" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L55" s="16">
         <v>64</v>
@@ -13226,13 +13208,13 @@
         <v>1</v>
       </c>
       <c r="N55" s="16" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O55" s="16" t="s">
         <v>49</v>
       </c>
       <c r="P55" s="16" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q55" s="16" t="b">
         <v>1</v>
@@ -13249,7 +13231,7 @@
         <v>DIP</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E56" s="24" t="s">
         <v>23</v>
@@ -13262,7 +13244,7 @@
         <v>d-dip-oms01-disk01</v>
       </c>
       <c r="H56" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I56" s="17">
         <v>64</v>
@@ -13272,7 +13254,7 @@
         <v>d-dip-oms01-disk02</v>
       </c>
       <c r="K56" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L56" s="17">
         <v>64</v>
@@ -13281,13 +13263,13 @@
         <v>1</v>
       </c>
       <c r="N56" s="17" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O56" s="17" t="s">
         <v>49</v>
       </c>
       <c r="P56" s="17" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q56" s="17" t="b">
         <v>1</v>
@@ -13304,7 +13286,7 @@
         <v>DIP</v>
       </c>
       <c r="D57" s="16" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="E57" s="22" t="s">
         <v>23</v>
@@ -13317,7 +13299,7 @@
         <v>d-dip-web01-disk01</v>
       </c>
       <c r="H57" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I57" s="16">
         <v>64</v>
@@ -13327,7 +13309,7 @@
         <v>d-dip-web01-disk02</v>
       </c>
       <c r="K57" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L57" s="16">
         <v>64</v>
@@ -13336,13 +13318,13 @@
         <v>1</v>
       </c>
       <c r="N57" s="16" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O57" s="16" t="s">
         <v>49</v>
       </c>
       <c r="P57" s="16" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q57" s="16" t="b">
         <v>1</v>
@@ -13356,33 +13338,33 @@
       </c>
       <c r="C58" s="17" t="str" cm="1">
         <f t="array" ref="C58">UPPER(INDEX(_xlfn.TEXTSPLIT($D58, "-"), 3))</f>
-        <v>COM</v>
+        <v>IF</v>
       </c>
       <c r="D58" s="17" t="s">
-        <v>311</v>
+        <v>55</v>
       </c>
       <c r="E58" s="24" t="s">
         <v>23</v>
       </c>
       <c r="F58" s="17" t="s">
-        <v>312</v>
+        <v>430</v>
       </c>
       <c r="G58" s="17" t="str">
         <f t="shared" si="0"/>
-        <v>d-com-auth01-disk01</v>
+        <v>d-if-auth01-disk01</v>
       </c>
       <c r="H58" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I58" s="17">
         <v>64</v>
       </c>
       <c r="J58" s="17" t="str">
         <f t="shared" si="1"/>
-        <v>d-com-auth01-disk02</v>
+        <v>d-if-auth01-disk02</v>
       </c>
       <c r="K58" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L58" s="17">
         <v>64</v>
@@ -13391,13 +13373,13 @@
         <v>1</v>
       </c>
       <c r="N58" s="17" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O58" s="17" t="s">
         <v>49</v>
       </c>
       <c r="P58" s="17" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q58" s="17" t="b">
         <v>1</v>
@@ -13411,33 +13393,33 @@
       </c>
       <c r="C59" s="16" t="str" cm="1">
         <f t="array" ref="C59">UPPER(INDEX(_xlfn.TEXTSPLIT($D59, "-"), 3))</f>
-        <v>COM</v>
+        <v>IF</v>
       </c>
       <c r="D59" s="16" t="s">
-        <v>311</v>
+        <v>55</v>
       </c>
       <c r="E59" s="22" t="s">
         <v>23</v>
       </c>
       <c r="F59" s="16" t="s">
-        <v>315</v>
+        <v>431</v>
       </c>
       <c r="G59" s="16" t="str">
         <f t="shared" si="0"/>
-        <v>d-com-proxy01-disk01</v>
+        <v>d-if-proxy01-disk01</v>
       </c>
       <c r="H59" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I59" s="16">
         <v>64</v>
       </c>
       <c r="J59" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>d-com-proxy01-disk02</v>
+        <v>d-if-proxy01-disk02</v>
       </c>
       <c r="K59" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L59" s="16">
         <v>64</v>
@@ -13446,13 +13428,13 @@
         <v>1</v>
       </c>
       <c r="N59" s="16" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O59" s="16" t="s">
         <v>49</v>
       </c>
       <c r="P59" s="16" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q59" s="16" t="b">
         <v>1</v>
@@ -13469,20 +13451,20 @@
         <v>IF</v>
       </c>
       <c r="D60" s="17" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E60" s="24" t="s">
         <v>23</v>
       </c>
       <c r="F60" s="17" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="G60" s="17" t="str">
         <f t="shared" si="0"/>
         <v>d-if-gramon01-disk01</v>
       </c>
       <c r="H60" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I60" s="17">
         <v>64</v>
@@ -13492,7 +13474,7 @@
         <v>d-if-gramon01-disk02</v>
       </c>
       <c r="K60" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L60" s="17">
         <v>64</v>
@@ -13501,13 +13483,13 @@
         <v>1</v>
       </c>
       <c r="N60" s="17" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O60" s="17" t="s">
         <v>49</v>
       </c>
       <c r="P60" s="17" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q60" s="17" t="b">
         <v>1</v>
@@ -13524,20 +13506,20 @@
         <v>DOIP</v>
       </c>
       <c r="D61" s="17" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="E61" s="24" t="s">
         <v>23</v>
       </c>
       <c r="F61" s="17" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="G61" s="17" t="str">
         <f t="shared" si="0"/>
         <v>d-doip-web01-disk01</v>
       </c>
       <c r="H61" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I61" s="17">
         <v>64</v>
@@ -13547,7 +13529,7 @@
         <v>d-doip-web01-disk02</v>
       </c>
       <c r="K61" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L61" s="17">
         <v>64</v>
@@ -13556,13 +13538,13 @@
         <v>1</v>
       </c>
       <c r="N61" s="17" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O61" s="17" t="s">
         <v>49</v>
       </c>
       <c r="P61" s="17" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q61" s="17" t="b">
         <v>1</v>
@@ -13579,20 +13561,20 @@
         <v>DOIP</v>
       </c>
       <c r="D62" s="16" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="E62" s="22" t="s">
         <v>23</v>
       </c>
       <c r="F62" s="16" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="G62" s="16" t="str">
         <f t="shared" si="0"/>
         <v>d-doip-ap01-disk01</v>
       </c>
       <c r="H62" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I62" s="16">
         <v>64</v>
@@ -13602,7 +13584,7 @@
         <v>d-doip-ap01-disk02</v>
       </c>
       <c r="K62" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L62" s="16">
         <v>64</v>
@@ -13611,13 +13593,13 @@
         <v>1</v>
       </c>
       <c r="N62" s="16" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O62" s="16" t="s">
         <v>49</v>
       </c>
       <c r="P62" s="16" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q62" s="16" t="b">
         <v>1</v>
@@ -13634,20 +13616,20 @@
         <v>DOIP</v>
       </c>
       <c r="D63" s="17" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="E63" s="24" t="s">
         <v>23</v>
       </c>
       <c r="F63" s="17" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="G63" s="17" t="str">
         <f>SUBSTITUTE($F63,"hazr-","")&amp;"-disk01"</f>
         <v>d-doip-adm01-disk01</v>
       </c>
       <c r="H63" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I63" s="17">
         <v>64</v>
@@ -13657,7 +13639,7 @@
         <v>d-doip-adm01-disk02</v>
       </c>
       <c r="K63" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L63" s="17">
         <v>64</v>
@@ -13666,13 +13648,13 @@
         <v>1</v>
       </c>
       <c r="N63" s="17" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O63" s="17" t="s">
         <v>49</v>
       </c>
       <c r="P63" s="17" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q63" s="17" t="b">
         <v>1</v>
@@ -13695,14 +13677,14 @@
         <v>23</v>
       </c>
       <c r="F64" s="16" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="G64" s="16" t="str">
         <f>SUBSTITUTE($F64,"hazr-","")&amp;"-disk01"</f>
         <v>d-bdp-crkweb01-disk01</v>
       </c>
       <c r="H64" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I64" s="16">
         <v>64</v>
@@ -13712,7 +13694,7 @@
         <v>d-bdp-crkweb01-disk02</v>
       </c>
       <c r="K64" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L64" s="16">
         <v>64</v>
@@ -13721,13 +13703,13 @@
         <v>1</v>
       </c>
       <c r="N64" s="16" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O64" s="16" t="s">
         <v>49</v>
       </c>
       <c r="P64" s="16" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q64" s="16" t="b">
         <v>1</v>
@@ -13750,14 +13732,14 @@
         <v>23</v>
       </c>
       <c r="F65" s="17" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="G65" s="17" t="str">
         <f>SUBSTITUTE($F65,"hazr-","")&amp;"-disk01"</f>
         <v>d-bdp-crkap01-disk01</v>
       </c>
       <c r="H65" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I65" s="17">
         <v>64</v>
@@ -13767,7 +13749,7 @@
         <v>d-bdp-crkap01-disk02</v>
       </c>
       <c r="K65" s="17" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L65" s="17">
         <v>64</v>
@@ -13776,13 +13758,13 @@
         <v>1</v>
       </c>
       <c r="N65" s="17" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O65" s="17" t="s">
         <v>49</v>
       </c>
       <c r="P65" s="17" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q65" s="17" t="b">
         <v>1</v>
@@ -13805,14 +13787,14 @@
         <v>23</v>
       </c>
       <c r="F66" s="16" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="G66" s="16" t="str">
         <f>SUBSTITUTE($F66,"hazr-","")&amp;"-disk01"</f>
         <v>d-bdp-crkml01-disk01</v>
       </c>
       <c r="H66" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="I66" s="16">
         <v>64</v>
@@ -13822,7 +13804,7 @@
         <v>d-bdp-crkml01-disk02</v>
       </c>
       <c r="K66" s="16" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="L66" s="16">
         <v>64</v>
@@ -13831,13 +13813,13 @@
         <v>1</v>
       </c>
       <c r="N66" s="16" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="O66" s="16" t="s">
         <v>49</v>
       </c>
       <c r="P66" s="16" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="Q66" s="16" t="b">
         <v>1</v>
@@ -13860,40 +13842,40 @@
         <v>23</v>
       </c>
       <c r="F67" s="17" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="G67" s="17" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="H67" s="17" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="I67" s="17" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="J67" s="17" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="K67" s="17" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="L67" s="17" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="M67" s="17" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="N67" s="17" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="O67" s="17" t="s">
         <v>49</v>
       </c>
       <c r="P67" s="17" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="Q67" s="17" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="R67" s="8"/>
     </row>
@@ -13944,10 +13926,10 @@
         <v>47</v>
       </c>
       <c r="I1" s="31" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="J1" s="31" t="s">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="K1" s="31" t="s">
         <v>26</v>
@@ -13992,7 +13974,7 @@
         <v>d-dis-ap01-nic</v>
       </c>
       <c r="L2" s="34" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -14021,7 +14003,7 @@
         <v>91</v>
       </c>
       <c r="I3" s="24" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="J3" s="17" t="s">
         <v>52</v>
@@ -14031,7 +14013,7 @@
         <v>d-dis-adm01-nic</v>
       </c>
       <c r="L3" s="37" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -14060,7 +14042,7 @@
         <v>59</v>
       </c>
       <c r="I4" s="22" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="J4" s="16" t="s">
         <v>52</v>
@@ -14070,7 +14052,7 @@
         <v>d-dis-bbiweb01-nic</v>
       </c>
       <c r="L4" s="34" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
@@ -14099,7 +14081,7 @@
         <v>91</v>
       </c>
       <c r="I5" s="24" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="J5" s="17" t="s">
         <v>52</v>
@@ -14109,7 +14091,7 @@
         <v>d-dis-bbicltap01-nic</v>
       </c>
       <c r="L5" s="37" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
@@ -14148,7 +14130,7 @@
         <v>d-dis-bbimsgap01-nic</v>
       </c>
       <c r="L6" s="34" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
@@ -14177,7 +14159,7 @@
         <v>91</v>
       </c>
       <c r="I7" s="24" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="J7" s="17" t="s">
         <v>52</v>
@@ -14187,7 +14169,7 @@
         <v>d-dis-walkap01-nic</v>
       </c>
       <c r="L7" s="37" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
@@ -14226,7 +14208,7 @@
         <v>d-dis-bat01-nic</v>
       </c>
       <c r="L8" s="34" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
@@ -14255,7 +14237,7 @@
         <v>91</v>
       </c>
       <c r="I9" s="24" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="J9" s="17" t="s">
         <v>52</v>
@@ -14265,7 +14247,7 @@
         <v>d-dis-drvcltap01-nic</v>
       </c>
       <c r="L9" s="37" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
@@ -14304,7 +14286,7 @@
         <v>d-dis-walkweb01-nic</v>
       </c>
       <c r="L10" s="34" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
@@ -14333,7 +14315,7 @@
         <v>91</v>
       </c>
       <c r="I11" s="24" t="s">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="J11" s="17" t="s">
         <v>52</v>
@@ -14343,7 +14325,7 @@
         <v>d-dis-drvmsgap01-nic</v>
       </c>
       <c r="L11" s="37" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
@@ -14372,7 +14354,7 @@
         <v>59</v>
       </c>
       <c r="I12" s="22" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="J12" s="16" t="s">
         <v>52</v>
@@ -14382,7 +14364,7 @@
         <v>d-dis-web01-nic</v>
       </c>
       <c r="L12" s="34" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -14411,7 +14393,7 @@
         <v>91</v>
       </c>
       <c r="I13" s="24" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="J13" s="17" t="s">
         <v>52</v>
@@ -14421,7 +14403,7 @@
         <v>d-dis-cmsadm01-nic</v>
       </c>
       <c r="L13" s="37" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -14460,7 +14442,7 @@
         <v>d-dis-cmsap01-nic</v>
       </c>
       <c r="L14" s="34" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
@@ -14489,7 +14471,7 @@
         <v>59</v>
       </c>
       <c r="I15" s="24" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="J15" s="17" t="s">
         <v>52</v>
@@ -14499,7 +14481,7 @@
         <v>d-dis-cmsweb01-nic</v>
       </c>
       <c r="L15" s="37" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -14528,7 +14510,7 @@
         <v>91</v>
       </c>
       <c r="I16" s="22" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="J16" s="16" t="s">
         <v>52</v>
@@ -14538,7 +14520,7 @@
         <v>d-dis-cmbsap01-nic</v>
       </c>
       <c r="L16" s="34" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
@@ -14567,7 +14549,7 @@
         <v>119</v>
       </c>
       <c r="I17" s="24" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="J17" s="17" t="s">
         <v>54</v>
@@ -14577,7 +14559,7 @@
         <v>d-dtg-ingap01-nic</v>
       </c>
       <c r="L17" s="37" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
@@ -14616,7 +14598,7 @@
         <v>d-dtg-ap01-nic</v>
       </c>
       <c r="L18" s="34" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
@@ -14645,7 +14627,7 @@
         <v>119</v>
       </c>
       <c r="I19" s="24" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="J19" s="17" t="s">
         <v>54</v>
@@ -14655,7 +14637,7 @@
         <v>d-dtg-extgeoap01-nic</v>
       </c>
       <c r="L19" s="37" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
@@ -14694,7 +14676,7 @@
         <v>d-dtg-geoap01-nic</v>
       </c>
       <c r="L20" s="34" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
@@ -14723,7 +14705,7 @@
         <v>76</v>
       </c>
       <c r="I21" s="24" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="J21" s="17" t="s">
         <v>54</v>
@@ -14733,7 +14715,7 @@
         <v>d-dtg-mq01-nic</v>
       </c>
       <c r="L21" s="37" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
@@ -14762,7 +14744,7 @@
         <v>119</v>
       </c>
       <c r="I22" s="22" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="J22" s="16" t="s">
         <v>54</v>
@@ -14772,7 +14754,7 @@
         <v>d-dtg-admweb01-nic</v>
       </c>
       <c r="L22" s="34" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
@@ -14801,7 +14783,7 @@
         <v>119</v>
       </c>
       <c r="I23" s="24" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="J23" s="17" t="s">
         <v>54</v>
@@ -14811,7 +14793,7 @@
         <v>d-dtg-admap01-nic</v>
       </c>
       <c r="L23" s="37" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
@@ -14850,7 +14832,7 @@
         <v>d-dtg-dtoms01-nic</v>
       </c>
       <c r="L24" s="34" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
@@ -14879,7 +14861,7 @@
         <v>120</v>
       </c>
       <c r="I25" s="24" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="J25" s="17" t="s">
         <v>54</v>
@@ -14889,7 +14871,7 @@
         <v>d-dtg-tsdb01-nic</v>
       </c>
       <c r="L25" s="37" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
@@ -14918,7 +14900,7 @@
         <v>76</v>
       </c>
       <c r="I26" s="22" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="J26" s="16" t="s">
         <v>54</v>
@@ -14928,7 +14910,7 @@
         <v>d-dtg-web01-nic</v>
       </c>
       <c r="L26" s="34" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
@@ -14957,7 +14939,7 @@
         <v>119</v>
       </c>
       <c r="I27" s="24" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="J27" s="17" t="s">
         <v>54</v>
@@ -14967,7 +14949,7 @@
         <v>d-dtg-zkp01-nic</v>
       </c>
       <c r="L27" s="37" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
@@ -15006,7 +14988,7 @@
         <v>d-dtg-zkp02-nic</v>
       </c>
       <c r="L28" s="34" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
@@ -15035,7 +15017,7 @@
         <v>119</v>
       </c>
       <c r="I29" s="24" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="J29" s="17" t="s">
         <v>54</v>
@@ -15045,7 +15027,7 @@
         <v>d-dtg-zkp03-nic</v>
       </c>
       <c r="L29" s="37" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
@@ -15084,7 +15066,7 @@
         <v>d-dtg-kfk01-nic</v>
       </c>
       <c r="L30" s="34" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
@@ -15113,7 +15095,7 @@
         <v>119</v>
       </c>
       <c r="I31" s="24" t="s">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="J31" s="17" t="s">
         <v>54</v>
@@ -15123,7 +15105,7 @@
         <v>d-dtg-kfk02-nic</v>
       </c>
       <c r="L31" s="37" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
@@ -15162,7 +15144,7 @@
         <v>d-dtg-kfk03-nic</v>
       </c>
       <c r="L32" s="34" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
@@ -15191,7 +15173,7 @@
         <v>119</v>
       </c>
       <c r="I33" s="24" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="J33" s="17" t="s">
         <v>54</v>
@@ -15201,7 +15183,7 @@
         <v>d-dtg-mdoms01-nic</v>
       </c>
       <c r="L33" s="37" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
@@ -15240,7 +15222,7 @@
         <v>d-dtg-cdmlap01-nic</v>
       </c>
       <c r="L34" s="34" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
@@ -15269,7 +15251,7 @@
         <v>119</v>
       </c>
       <c r="I35" s="24" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="J35" s="17" t="s">
         <v>54</v>
@@ -15279,7 +15261,7 @@
         <v>d-dtg-cdstap01-nic</v>
       </c>
       <c r="L35" s="37" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
@@ -15308,7 +15290,7 @@
         <v>119</v>
       </c>
       <c r="I36" s="22" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="J36" s="16" t="s">
         <v>54</v>
@@ -15318,7 +15300,7 @@
         <v>d-dtg-cdsvadm01-nic</v>
       </c>
       <c r="L36" s="34" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
@@ -15347,7 +15329,7 @@
         <v>119</v>
       </c>
       <c r="I37" s="24" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="J37" s="17" t="s">
         <v>54</v>
@@ -15357,7 +15339,7 @@
         <v>d-dtg-diosap01-nic</v>
       </c>
       <c r="L37" s="37" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
@@ -15386,7 +15368,7 @@
         <v>119</v>
       </c>
       <c r="I38" s="22" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="J38" s="16" t="s">
         <v>54</v>
@@ -15396,7 +15378,7 @@
         <v>d-dtg-diosweb01-nic</v>
       </c>
       <c r="L38" s="34" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
@@ -15425,7 +15407,7 @@
         <v>76</v>
       </c>
       <c r="I39" s="24" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="J39" s="17" t="s">
         <v>54</v>
@@ -15435,7 +15417,7 @@
         <v>d-dtg-dprweb01-nic</v>
       </c>
       <c r="L39" s="37" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
@@ -15474,7 +15456,7 @@
         <v>d-dtg-dprap01-nic</v>
       </c>
       <c r="L40" s="34" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
@@ -15503,7 +15485,7 @@
         <v>127</v>
       </c>
       <c r="I41" s="24" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="J41" s="17" t="s">
         <v>184</v>
@@ -15513,7 +15495,7 @@
         <v>d-bdp-airfw01-nic</v>
       </c>
       <c r="L41" s="37" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
@@ -15542,7 +15524,7 @@
         <v>127</v>
       </c>
       <c r="I42" s="22" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="J42" s="16" t="s">
         <v>184</v>
@@ -15552,7 +15534,7 @@
         <v>d-bdp-kepler01-nic</v>
       </c>
       <c r="L42" s="34" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
@@ -15581,7 +15563,7 @@
         <v>127</v>
       </c>
       <c r="I43" s="24" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="J43" s="17" t="s">
         <v>184</v>
@@ -15591,7 +15573,7 @@
         <v>d-bdp-cxmadm01-nic</v>
       </c>
       <c r="L43" s="37" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
@@ -15620,7 +15602,7 @@
         <v>127</v>
       </c>
       <c r="I44" s="22" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="J44" s="16" t="s">
         <v>184</v>
@@ -15630,7 +15612,7 @@
         <v>d-bdp-slap01-nic</v>
       </c>
       <c r="L44" s="34" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
@@ -15656,20 +15638,20 @@
         <v>57</v>
       </c>
       <c r="H45" s="35" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="I45" s="24" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="J45" s="17" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="K45" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-adm01-nic</v>
       </c>
       <c r="L45" s="37" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
@@ -15695,20 +15677,20 @@
         <v>57</v>
       </c>
       <c r="H46" s="33" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="I46" s="22" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="J46" s="16" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="K46" s="33" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-ap01-nic</v>
       </c>
       <c r="L46" s="34" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
@@ -15734,20 +15716,20 @@
         <v>57</v>
       </c>
       <c r="H47" s="35" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="I47" s="24" t="s">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="J47" s="17" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="K47" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-flk01-nic</v>
       </c>
       <c r="L47" s="37" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
@@ -15773,20 +15755,20 @@
         <v>57</v>
       </c>
       <c r="H48" s="33" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="I48" s="22" t="s">
         <v>293</v>
       </c>
       <c r="J48" s="16" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="K48" s="33" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-flk02-nic</v>
       </c>
       <c r="L48" s="34" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
@@ -15812,20 +15794,20 @@
         <v>57</v>
       </c>
       <c r="H49" s="35" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="I49" s="24" t="s">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="J49" s="17" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="K49" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-flk03-nic</v>
       </c>
       <c r="L49" s="37" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
@@ -15851,20 +15833,20 @@
         <v>57</v>
       </c>
       <c r="H50" s="33" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="I50" s="22" t="s">
         <v>297</v>
       </c>
       <c r="J50" s="16" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="K50" s="33" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-geoap01-nic</v>
       </c>
       <c r="L50" s="34" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
@@ -15890,20 +15872,20 @@
         <v>57</v>
       </c>
       <c r="H51" s="35" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="I51" s="24" t="s">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="J51" s="17" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="K51" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-kfk01-nic</v>
       </c>
       <c r="L51" s="37" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
@@ -15929,20 +15911,20 @@
         <v>57</v>
       </c>
       <c r="H52" s="33" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="I52" s="22" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="J52" s="16" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="K52" s="33" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-kfk02-nic</v>
       </c>
       <c r="L52" s="34" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
@@ -15968,20 +15950,20 @@
         <v>57</v>
       </c>
       <c r="H53" s="35" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="I53" s="24" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="J53" s="17" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="K53" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-kfk03-nic</v>
       </c>
       <c r="L53" s="37" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
@@ -16007,20 +15989,20 @@
         <v>57</v>
       </c>
       <c r="H54" s="33" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="I54" s="22" t="s">
         <v>303</v>
       </c>
       <c r="J54" s="16" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="K54" s="33" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-mqap01-nic</v>
       </c>
       <c r="L54" s="34" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
@@ -16046,20 +16028,20 @@
         <v>57</v>
       </c>
       <c r="H55" s="35" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="I55" s="24" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="J55" s="17" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="K55" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-mqweb01-nic</v>
       </c>
       <c r="L55" s="37" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
@@ -16085,20 +16067,20 @@
         <v>57</v>
       </c>
       <c r="H56" s="33" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="I56" s="22" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="J56" s="16" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="K56" s="33" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-oms01-nic</v>
       </c>
       <c r="L56" s="34" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
@@ -16124,20 +16106,20 @@
         <v>57</v>
       </c>
       <c r="H57" s="35" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="I57" s="24" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="J57" s="17" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="K57" s="35" t="str">
         <f t="shared" si="1"/>
         <v>d-dip-web01-nic</v>
       </c>
       <c r="L57" s="37" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
@@ -16147,14 +16129,14 @@
       </c>
       <c r="C58" s="33" t="str" cm="1">
         <f t="array" ref="C58">UPPER(INDEX(_xlfn.TEXTSPLIT($I58, "-"), 3))</f>
-        <v>COM</v>
+        <v>IF</v>
       </c>
       <c r="D58" s="33" t="s">
         <v>49</v>
       </c>
       <c r="E58" s="33" t="str">
         <f t="shared" si="2"/>
-        <v>d-com-auth01-nsg</v>
+        <v>d-if-auth01-nsg</v>
       </c>
       <c r="F58" s="33" t="s">
         <v>49</v>
@@ -16163,20 +16145,20 @@
         <v>57</v>
       </c>
       <c r="H58" s="33" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="I58" s="22" t="s">
-        <v>399</v>
+        <v>430</v>
       </c>
       <c r="J58" s="16" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="K58" s="33" t="str">
         <f t="shared" si="1"/>
-        <v>d-com-auth01-nic</v>
+        <v>d-if-auth01-nic</v>
       </c>
       <c r="L58" s="34" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
@@ -16186,14 +16168,14 @@
       </c>
       <c r="C59" s="35" t="str" cm="1">
         <f t="array" ref="C59">UPPER(INDEX(_xlfn.TEXTSPLIT($I59, "-"), 3))</f>
-        <v>COM</v>
+        <v>IF</v>
       </c>
       <c r="D59" s="35" t="s">
         <v>49</v>
       </c>
       <c r="E59" s="35" t="str">
         <f t="shared" si="2"/>
-        <v>d-com-proxy01-nsg</v>
+        <v>d-if-proxy01-nsg</v>
       </c>
       <c r="F59" s="35" t="s">
         <v>49</v>
@@ -16202,20 +16184,20 @@
         <v>56</v>
       </c>
       <c r="H59" s="35" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I59" s="24" t="s">
-        <v>400</v>
+        <v>431</v>
       </c>
       <c r="J59" s="17" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="K59" s="35" t="str">
         <f t="shared" si="1"/>
-        <v>d-com-proxy01-nic</v>
+        <v>d-if-proxy01-nic</v>
       </c>
       <c r="L59" s="37" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
@@ -16244,7 +16226,7 @@
         <v>166</v>
       </c>
       <c r="I60" s="22" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="J60" s="16" t="s">
         <v>55</v>
@@ -16254,7 +16236,7 @@
         <v>d-if-gramon01-nic</v>
       </c>
       <c r="L60" s="34" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
@@ -16283,7 +16265,7 @@
         <v>104</v>
       </c>
       <c r="I61" s="24" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="J61" s="17" t="s">
         <v>53</v>
@@ -16293,7 +16275,7 @@
         <v>d-doip-web01-nic</v>
       </c>
       <c r="L61" s="37" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
@@ -16322,7 +16304,7 @@
         <v>104</v>
       </c>
       <c r="I62" s="22" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="J62" s="16" t="s">
         <v>53</v>
@@ -16332,7 +16314,7 @@
         <v>d-doip-ap01-nic</v>
       </c>
       <c r="L62" s="34" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
@@ -16361,7 +16343,7 @@
         <v>104</v>
       </c>
       <c r="I63" s="24" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="J63" s="17" t="s">
         <v>53</v>
@@ -16371,7 +16353,7 @@
         <v>d-doip-adm01-nic</v>
       </c>
       <c r="L63" s="37" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
@@ -16400,7 +16382,7 @@
         <v>78</v>
       </c>
       <c r="I64" s="22" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="J64" s="16" t="s">
         <v>184</v>
@@ -16410,7 +16392,7 @@
         <v>d-bdp-crkweb01-nic</v>
       </c>
       <c r="L64" s="34" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
@@ -16439,7 +16421,7 @@
         <v>127</v>
       </c>
       <c r="I65" s="24" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="J65" s="17" t="s">
         <v>184</v>
@@ -16449,7 +16431,7 @@
         <v>d-bdp-crkap01-nic</v>
       </c>
       <c r="L65" s="37" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
@@ -16478,7 +16460,7 @@
         <v>127</v>
       </c>
       <c r="I66" s="22" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="J66" s="16" t="s">
         <v>184</v>
@@ -16488,7 +16470,7 @@
         <v>d-bdp-crkml01-nic</v>
       </c>
       <c r="L66" s="34" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
@@ -16517,7 +16499,7 @@
         <v>91</v>
       </c>
       <c r="I67" s="24" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="J67" s="17" t="s">
         <v>52</v>
@@ -16527,7 +16509,7 @@
         <v>d-dis-dfir01-nic</v>
       </c>
       <c r="L67" s="37" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.3">
@@ -16553,13 +16535,13 @@
         <v>188</v>
       </c>
       <c r="H68" s="33" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="I68" s="33"/>
       <c r="J68" s="33"/>
       <c r="K68" s="33"/>
       <c r="L68" s="33" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.3">
@@ -16585,13 +16567,13 @@
         <v>188</v>
       </c>
       <c r="H69" s="35" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="I69" s="35"/>
       <c r="J69" s="35"/>
       <c r="K69" s="35"/>
       <c r="L69" s="35" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.3">
@@ -16617,13 +16599,13 @@
         <v>188</v>
       </c>
       <c r="H70" s="33" t="s">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="I70" s="33"/>
       <c r="J70" s="33"/>
       <c r="K70" s="33"/>
       <c r="L70" s="33" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
@@ -16649,13 +16631,13 @@
         <v>188</v>
       </c>
       <c r="H71" s="35" t="s">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="I71" s="35"/>
       <c r="J71" s="35"/>
       <c r="K71" s="35"/>
       <c r="L71" s="35" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.3">
@@ -16681,13 +16663,13 @@
         <v>188</v>
       </c>
       <c r="H72" s="33" t="s">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="I72" s="33"/>
       <c r="J72" s="33"/>
       <c r="K72" s="33"/>
       <c r="L72" s="33" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
@@ -16713,13 +16695,13 @@
         <v>188</v>
       </c>
       <c r="H73" s="35" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="I73" s="35"/>
       <c r="J73" s="35"/>
       <c r="K73" s="35"/>
       <c r="L73" s="35" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
@@ -16745,13 +16727,13 @@
         <v>188</v>
       </c>
       <c r="H74" s="33" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="I74" s="33"/>
       <c r="J74" s="33"/>
       <c r="K74" s="33"/>
       <c r="L74" s="33" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.3">
@@ -16777,13 +16759,13 @@
         <v>188</v>
       </c>
       <c r="H75" s="35" t="s">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="I75" s="35"/>
       <c r="J75" s="35"/>
       <c r="K75" s="35"/>
       <c r="L75" s="35" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.3">
@@ -16809,13 +16791,13 @@
         <v>188</v>
       </c>
       <c r="H76" s="33" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="I76" s="33"/>
       <c r="J76" s="33"/>
       <c r="K76" s="33"/>
       <c r="L76" s="33" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.3">
@@ -16841,13 +16823,13 @@
         <v>188</v>
       </c>
       <c r="H77" s="35" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="I77" s="35"/>
       <c r="J77" s="35"/>
       <c r="K77" s="35"/>
       <c r="L77" s="35" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.3">
@@ -16873,13 +16855,13 @@
         <v>188</v>
       </c>
       <c r="H78" s="33" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="I78" s="33"/>
       <c r="J78" s="33"/>
       <c r="K78" s="33"/>
       <c r="L78" s="33" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.3">
@@ -16888,13 +16870,13 @@
         <v>31</v>
       </c>
       <c r="C79" s="35" t="s">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="D79" s="35" t="s">
         <v>49</v>
       </c>
       <c r="E79" s="35" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="F79" s="35" t="s">
         <v>49</v>
@@ -16909,7 +16891,7 @@
       <c r="J79" s="35"/>
       <c r="K79" s="35"/>
       <c r="L79" s="35" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.3">
@@ -16935,13 +16917,13 @@
         <v>188</v>
       </c>
       <c r="H80" s="33" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="I80" s="33"/>
       <c r="J80" s="33"/>
       <c r="K80" s="33"/>
       <c r="L80" s="33" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.3">
@@ -16967,13 +16949,13 @@
         <v>188</v>
       </c>
       <c r="H81" s="35" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="I81" s="35"/>
       <c r="J81" s="35"/>
       <c r="K81" s="35"/>
       <c r="L81" s="35" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.3">
@@ -16999,13 +16981,13 @@
         <v>188</v>
       </c>
       <c r="H82" s="33" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="I82" s="33"/>
       <c r="J82" s="33"/>
       <c r="K82" s="33"/>
       <c r="L82" s="33" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.3">
@@ -17031,13 +17013,13 @@
         <v>188</v>
       </c>
       <c r="H83" s="35" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="I83" s="35"/>
       <c r="J83" s="35"/>
       <c r="K83" s="35"/>
       <c r="L83" s="35" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
     </row>
   </sheetData>
